--- a/gemini_comparison_report.xlsx
+++ b/gemini_comparison_report.xlsx
@@ -38,16 +38,16 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="002F5496"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="009C6500"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="009C0006"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002F5496"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="9">
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,13 +144,20 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,7 +530,7 @@
     <col width="54" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="54" customWidth="1" min="8" max="8"/>
@@ -571,10 +578,10 @@
     <col width="28" customWidth="1" min="50" max="50"/>
     <col width="33" customWidth="1" min="51" max="51"/>
     <col width="54" customWidth="1" min="52" max="52"/>
-    <col width="25" customWidth="1" min="53" max="53"/>
+    <col width="28" customWidth="1" min="53" max="53"/>
     <col width="26" customWidth="1" min="54" max="54"/>
     <col width="32" customWidth="1" min="55" max="55"/>
-    <col width="54" customWidth="1" min="56" max="56"/>
+    <col width="49" customWidth="1" min="56" max="56"/>
     <col width="26" customWidth="1" min="57" max="57"/>
     <col width="21" customWidth="1" min="58" max="58"/>
     <col width="25" customWidth="1" min="59" max="59"/>
@@ -604,7 +611,7 @@
     <col width="24" customWidth="1" min="83" max="83"/>
     <col width="26" customWidth="1" min="84" max="84"/>
     <col width="23" customWidth="1" min="85" max="85"/>
-    <col width="17" customWidth="1" min="86" max="86"/>
+    <col width="54" customWidth="1" min="86" max="86"/>
     <col width="26" customWidth="1" min="87" max="87"/>
     <col width="25" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
@@ -1102,7 +1109,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>audio_test_1_retry_afdfd01b</t>
+          <t>gemini_cmp_1_d61539e4</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -1110,7 +1117,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr"/>
+      <c r="G2" s="5" t="n">
+        <v>292.3</v>
+      </c>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="5" t="inlineStr"/>
       <c r="J2" s="5" t="inlineStr"/>
@@ -1150,38 +1159,51 @@
       <c r="AR2" s="5" t="inlineStr"/>
       <c r="AS2" s="5" t="inlineStr">
         <is>
-          <t>Travis (customer rep) called Joy to provide an update and said he was able to get someone dispatched who is on the way, with an estimated arrival window between 4:00 and 4:30. Joy expressed frustration about the late timing because it is an owner-occupied house and her clients are already there, and she does not want to wait around; she said if it ends up being too late she may need to reschedule and would take the blame. Joy said she needs to see what she can do and will let Travis know, and the call ended without a confirmed appointment time.</t>
+          <t>The representative, Joyce, called Travis to inform him that a technician was on the way and would arrive between 4:00 PM and 4:30 PM. Travis, who was already at the owner-occupied property with his clients, stated he could not wait another hour and requested to reschedule the appointment. Travis took full responsibility for the scheduling conflict, and Joyce agreed to look into other scheduling options and follow up with him.</t>
         </is>
       </c>
       <c r="AT2" s="5" t="inlineStr">
         <is>
-          <t>Rep (Travis) scheduled someone who is on the way with an ETA between 4:00 and 4:30.
-Customer (Joy) said the house is owner-occupied and her clients are already there, making the late afternoon window inconvenient.
-Customer may reschedule if the arrival is late and said she will let the rep know after she figures out what she can do.</t>
-        </is>
-      </c>
-      <c r="AU2" s="5" t="inlineStr"/>
+          <t>Joyce notified Travis that a technician was scheduled to arrive at the property between 4:00 PM and 4:30 PM.
+Travis requested to reschedule the appointment because he was already at the owner-occupied house with his clients and could not wait another hour.
+Travis explicitly took the blame for the scheduling conflict and the need to reschedule.</t>
+        </is>
+      </c>
+      <c r="AU2" s="5" t="inlineStr">
+        <is>
+          <t>Joyce must review the schedule to find an alternative appointment time and contact Travis to reschedule the visit.
+Follow up with the customer regarding available schedule options</t>
+        </is>
+      </c>
       <c r="AV2" s="5" t="inlineStr">
         <is>
-          <t>Customer to decide whether she can accommodate the 4:00–4:30 visit window and inform Travis.
-If the time does not work, reschedule the visit for a different time.</t>
+          <t>Joyce will check the schedule for availability.
+Joyce will follow up with Travis to establish a new appointment time.</t>
         </is>
       </c>
       <c r="AW2" s="5" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="AX2" s="5" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
       <c r="AY2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" s="5" t="inlineStr"/>
-      <c r="BA2" s="5" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AZ2" s="5" t="inlineStr">
+        <is>
+          <t>[follow_up_call] Follow up with the customer regarding available schedule options (owner: customer_rep, due: None)</t>
+        </is>
+      </c>
+      <c r="BA2" s="5" t="inlineStr">
+        <is>
+          <t>Travis</t>
+        </is>
+      </c>
       <c r="BB2" s="5" t="inlineStr"/>
       <c r="BC2" s="5" t="inlineStr">
         <is>
-          <t>unqualified</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="BD2" s="5" t="n"/>
@@ -1202,7 +1224,7 @@
       </c>
       <c r="BH2" s="5" t="inlineStr">
         <is>
-          <t>unqualified</t>
+          <t>qualified_but_unbooked</t>
         </is>
       </c>
       <c r="BI2" s="5" t="b">
@@ -1210,35 +1232,35 @@
       </c>
       <c r="BJ2" s="5" t="n"/>
       <c r="BK2" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL2" s="5" t="inlineStr">
         <is>
-          <t>OUT_OF_SCOPE</t>
+          <t>IN_SCOPE</t>
         </is>
       </c>
       <c r="BM2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="BN2" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BO2" s="5" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="BP2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ2" s="5" t="n">
-        <v>0</v>
+        <v>0.575</v>
       </c>
       <c r="BR2" s="5" t="n"/>
       <c r="BS2" s="5" t="inlineStr"/>
       <c r="BT2" s="5" t="n">
-        <v>0.52</v>
+        <v>0.25</v>
       </c>
       <c r="BU2" s="5" t="n">
-        <v>0.52</v>
+        <v>0.25</v>
       </c>
       <c r="BV2" s="5" t="inlineStr">
         <is>
@@ -1247,22 +1269,25 @@
       </c>
       <c r="BW2" s="5" t="inlineStr">
         <is>
-          <t>Greeting &amp; Identification, Answer Questions (if any), Close Professionally</t>
+          <t>Greeting &amp; Identification, Answer Questions, Close Professionally</t>
         </is>
       </c>
       <c r="BX2" s="5" t="inlineStr">
         <is>
-          <t>[medium] The rep opened with an informal greeting and did not state the company name, confirm the customer's name, or verify contact details before discussing the appointment. | Fix: Use a standard confirmation opener: company name, rep name, confirm who you're speaking with, and confirm the address/phone for the appointment before giving timing updates.
-[high] When the homeowner expressed frustration about waiting and hinted they may need to reschedule, the rep did not acknowledge the concern, offer options, or attempt to confirm a plan; he simply ended the call. | Fix: Acknowledge the inconvenience, clarify the latest expected arrival time, and offer concrete alternatives (reschedule windows, callback/text updates, or dispatch check). Then confirm the chosen next step.
-[medium] The rep did not close professionally by confirming next steps (who will follow up, when, and via what channel) or providing a way to reach the company if the customer needs to change plans. | Fix: End with a clear confirmation and contingency: confirm the current plan, set a follow-up time, and provide contact instructions.</t>
+          <t>[medium] Rep opened the call by greeting the customer with the wrong name ('Hey Joyce') and completely omitted the professional greeting and company name. | Fix: Always use a standard professional greeting that includes your name, the company name, and verifies the caller's identity before diving into appointment details.
+[high] When the customer stated they had a conflict and needed to reschedule, the rep ended the call with 'Let me see what I can do' without actually securing a new appointment time. | Fix: Capitalize on the fact that the customer is currently on the phone. Take immediate ownership of the schedule and offer alternative time slots right then and there.</t>
         </is>
       </c>
       <c r="BY2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" s="5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="BZ2" s="5" t="inlineStr">
+        <is>
+          <t>[Scheduling Conflicts] "Oh my God Well it's a you know it's an owner occupied house I hate it and My clients are already here so but four thirty to five is off I was like I gotta sit around for another hour now. So I can reschedule. I mean, put all the blame on me because it is my fault. So I just gotta figure out another time. I'm gonna just like and I gotta meet them out here and just so." (Unresolved, severity=medium)</t>
+        </is>
+      </c>
       <c r="CA2" s="5" t="n">
-        <v>814</v>
+        <v>745</v>
       </c>
       <c r="CB2" s="5" t="n">
         <v>6</v>
@@ -1326,7 +1351,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>staging_run_fb9742d73dab</t>
+          <t>gemini_cmp_2_d4879ffd</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -1334,7 +1359,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="n">
+        <v>49.6</v>
+      </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
           <t>The homeowner called Arizona Roofers to ask about certified shingle roof installation and to get an estimate because their shingle roof is leaking and they are considering replacing it. The representative confirmed the roof type, collected the customer’s address, name, phone number, permission to send text updates, and email for sending a written proposal. The homeowner stated the roof was originally a 30-year roof and is now about 20 years old, and confirmed there are no solar panels (but mentioned an air conditioning unit on the roof). The rep asked about HOA status (homeowner said “as I know, okay,” indicating uncertainty) and scheduled an on-site visit for Thursday, February 12th from 1–3 PM, explaining the customer would receive a confirmation text and a 30-minute pre-arrival call/text from the technician. The homeowner expressed concern about prior workmanship and requested a certified technician; the rep reassured them that leaks after 15–20 years can be normal for shingle roofs and that the company’s team is certified and established, then confirmed the appointment.</t>
@@ -1487,33 +1514,31 @@
       </c>
       <c r="AS3" s="5" t="inlineStr">
         <is>
-          <t>The homeowner called Arizona Roofers to ask about pricing and to schedule an on-site estimate for replacing an older shingle roof that is leaking despite having been patched before. The representative confirmed the roof type (shingle), collected the property address, name, phone number, permission to send text updates, and an email for sending a written proposal, and noted the roof is around 20 years old with no solar panels (customer mentioned an air conditioner on the roof). The customer expressed concern about prior poor installation and requested certified technicians; the representative reassured them that shingle roofs commonly begin leaking around 15–20 years and that the company’s team is certified and licensed. An appointment was booked for Thursday from 1–3 PM, with confirmation and pre-arrival communication via text/phone.</t>
+          <t>The homeowner called Arizona Roofers to request an estimate for replacing their 20-year-old shingle roof, which is currently leaking despite prior repairs. The representative collected necessary property details, confirming the home is in an HOA community and does not have solar panels. The customer expressed concern over installation quality and specifically requested a certified technician to evaluate the roof, which the representative reassured them would be provided. An inspection appointment was successfully scheduled for Thursday at 1:00 PM.</t>
         </is>
       </c>
       <c r="AT3" s="5" t="inlineStr">
         <is>
-          <t>Customer has a shingle roof and is requesting an estimate for a roof replacement due to leaking; they mentioned the roof is around 20 years old and has been patched before.
-Property details captured: address provided (1301 West El Nary/Elmarae Street, unit/apt details unclear), homeowner confirmed they are the owner, best contact is the current phone number, text updates approved, and email provided for the written proposal.
-Customer stated there are no solar panels and mentioned an air conditioner on the roof; they also emphasized wanting a certified technician because a prior roof installation began leaking within about five years.</t>
-        </is>
-      </c>
-      <c r="AU3" s="5" t="inlineStr">
-        <is>
-          <t>Send appointment confirmation text and provide day-of text/phone notification about 30 minutes before technician arrival.
-Prepare to email the written proposal/estimate to the customer after the on-site visit.</t>
-        </is>
-      </c>
+          <t>The caller is the homeowner and is requesting an estimate for a roof replacement due to ongoing leaks.
+The property features a 20-year-old shingle roof, is located in an HOA community, and does not have solar panels.
+The customer emphasized the need for a certified technician to ensure high-quality installation and prevent future issues.
+The homeowner opted in to receive text message updates and provided their email address to receive the written proposal.
+An inspection appointment was booked for Thursday between 1:00 PM and 3:00 PM.</t>
+        </is>
+      </c>
+      <c r="AU3" s="5" t="inlineStr"/>
       <c r="AV3" s="5" t="inlineStr">
         <is>
-          <t>Technician to visit the property on Thursday from 1–3 PM to inspect the shingle roof and provide a replacement estimate.
-After inspection, deliver the written proposal to the customer via email and follow up as needed to proceed with replacement.</t>
+          <t>Send an automated confirmation text to the customer with the appointment details.
+Technician to send a text or call the customer 30 minutes before arriving at the property on Thursday.
+Technician to inspect the roof and send a written proposal to the customer's email.</t>
         </is>
       </c>
       <c r="AW3" s="5" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="AX3" s="5" t="n">
-        <v>0.78</v>
+        <v>0.85</v>
       </c>
       <c r="AY3" s="5" t="n">
         <v>0</v>
@@ -1521,7 +1546,7 @@
       <c r="AZ3" s="5" t="inlineStr"/>
       <c r="BA3" s="5" t="inlineStr">
         <is>
-          <t>Chinh</t>
+          <t>Sichaienna Sich Farm Phi</t>
         </is>
       </c>
       <c r="BB3" s="5" t="inlineStr"/>
@@ -1532,7 +1557,7 @@
       </c>
       <c r="BD3" s="5" t="inlineStr">
         <is>
-          <t>Roof inspection and estimate for shingle roof leak and possible roof replacement</t>
+          <t>Roof leak inspection and replacement estimate</t>
         </is>
       </c>
       <c r="BE3" s="5" t="inlineStr">
@@ -1547,7 +1572,7 @@
       </c>
       <c r="BG3" s="5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Existing</t>
         </is>
       </c>
       <c r="BH3" s="5" t="inlineStr">
@@ -1566,7 +1591,11 @@
       <c r="BK3" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="BL3" s="5" t="n"/>
+      <c r="BL3" s="5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
       <c r="BM3" s="5" t="n">
         <v>0.5</v>
       </c>
@@ -1574,81 +1603,81 @@
         <v>1</v>
       </c>
       <c r="BO3" s="5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="BP3" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="BQ3" s="5" t="n">
-        <v>0.775</v>
+        <v>0.825</v>
       </c>
       <c r="BR3" s="5" t="n"/>
       <c r="BS3" s="5" t="inlineStr"/>
       <c r="BT3" s="5" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="BU3" s="5" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="BV3" s="5" t="inlineStr">
         <is>
-          <t>Greeting &amp; Identification, Scheduling, Setting Expectations, Close &amp; Confirmation</t>
+          <t>Greeting &amp; Identification, Needs Discovery, Scheduling, Setting Expectations, Objection Handling, Close &amp; Confirmation</t>
         </is>
       </c>
       <c r="BW3" s="5" t="inlineStr">
         <is>
-          <t>Needs Discovery, Qualifying (BANT), Objection Handling</t>
+          <t>Qualifying (BANT)</t>
         </is>
       </c>
       <c r="BX3" s="5" t="inlineStr">
         <is>
-          <t>[medium] After the customer said they have leaking and want an estimate to replace the roof, the rep moved quickly into intake and scheduling without clarifying the problem details (how long leaking has been happening, whether there is active water intrusion/damage, where the leak is, and what prior repairs were attempted). | Fix: Before scheduling, ask 3–5 targeted discovery questions to assess urgency and scope (duration, active leak, interior damage, prior patch/inspection, roof type/sections affected). Then route appropriately (standard inspection vs. urgent leak service).
-[medium] The rep did not complete BANT-style qualifying beyond confirming homeowner status; they did not ask about timeline/urgency for replacement, whether the customer is comparing other bids, or any budget/financing considerations. | Fix: Add quick qualifying questions after identifying the need and before locking the appointment: timeline, decision process, and whether they’re getting other quotes; optionally mention financing if appropriate.
-[high] When the customer raised a trust/certification concern, the rep responded with potentially inaccurate reassurance (“totally normal… to start leaking after about 15 to 20 years”) and vague credibility claims (“licensed under the bbb”), without empathizing or clearly explaining certifications, licensing, and what the inspection will verify. | Fix: Acknowledge the concern, clarify what ‘certified’ means (manufacturer certifications, state license, insurance), and set expectations that the technician will document findings and explain options. Avoid absolute claims; use verifiable facts and offer to provide license numbers/links.</t>
+          <t>[high] After the customer stated they had a leaking 20-year-old roof, the rep immediately moved on to asking about HOA communities without assessing the severity or urgency of the leak. | Fix: Pause to assess the severity of the leak before moving into standard property qualification questions like HOA or solar panels. Determine if the customer needs emergency tarping or priority scheduling.
+[medium] The rep did not ask any qualifying questions regarding the customer's timeline to complete the repair or their budget/financing needs. | Fix: Incorporate a soft timeline and budget question before finalizing the appointment to gauge buyer readiness.</t>
         </is>
       </c>
       <c r="BY3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ3" s="5" t="inlineStr"/>
+      <c r="CA3" s="5" t="n">
+        <v>3195</v>
+      </c>
+      <c r="CB3" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="CC3" s="5" t="inlineStr">
+        <is>
+          <t>customer_rep, home_owner</t>
+        </is>
+      </c>
+      <c r="CD3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="CE3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="BZ3" s="5" t="inlineStr">
-        <is>
-          <t>[Insurance Related] "I have a question, ma'. Am. I like to have recorded the lock tie before you do the roof. I don't know, you do something wrong or what. So I need to certify the technician to install to take a look and see what he suggest. I don't want that have problem again." (Unresolved, severity=medium)
-[In-Person Estimates Only] "So I want to know this. How much cost? Can somebody can stop by and take a look to see how much cost?" (Unresolved, severity=low)
-[Service Fee Concerns] "I already have a pack over but I want to estimate if good deal." (Unresolved, severity=low)</t>
-        </is>
-      </c>
-      <c r="CA3" s="5" t="n">
-        <v>3775</v>
-      </c>
-      <c r="CB3" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="CC3" s="5" t="inlineStr">
-        <is>
-          <t>customer_rep, home_owner</t>
-        </is>
-      </c>
-      <c r="CD3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF3" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="CG3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH3" s="5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="CH3" s="5" t="inlineStr">
+        <is>
+          <t>[Low] Customer Type: Mismatch — PROD='new' STAGING='existing'
+[Medium] Scope Classification: Mismatch — PROD='none' STAGING='in_scope'
+[Medium] Objections Count: Missing in Staging — Present in PROD but missing/empty in STAGING
+[Medium] Objections Count: Count Delta — PROD=4 STAGING=0 delta=4</t>
+        </is>
+      </c>
       <c r="CI3" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="CJ3" s="5" t="n">
         <v>0.02</v>
       </c>
-      <c r="CJ3" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="CK3" s="5" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="CL3" s="5" t="inlineStr"/>
       <c r="CM3" s="8" t="inlineStr">
@@ -1661,9 +1690,9 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="CO3" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="CO3" s="9" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1717,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>audio_test_3_c37e5d95</t>
+          <t>gemini_cmp_3_f8eebd74</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1696,7 +1725,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="n">
+        <v>82.2</v>
+      </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Cindy Hannah called Arizona Roofers to return a call from Kate. Bronte informed her that Kate was not in yet but said she would let Kate know that Cindy called. The call ended politely without discussing any roofing issue, property details, or scheduling.</t>
@@ -1823,28 +1854,23 @@
       </c>
       <c r="AS4" s="5" t="inlineStr">
         <is>
-          <t>Cindy (Hannah) called Arizona Roofers to return a call from Kate. Bronte informed her that Kate was not in yet and said she would let Kate know that Cindy called when she arrived. The call ended politely without discussing any roofing issues, property details, or scheduling.</t>
+          <t>Customer Cindy Hannah called to return a previous call from an employee named Kate. The representative, Broughte, informed the customer that Kate was not in the office yet but took a message and promised to notify Kate to return the call once she arrives.</t>
         </is>
       </c>
       <c r="AT4" s="5" t="inlineStr">
         <is>
-          <t>Caller identified herself as Cindy (Hannah) and said she was returning Kate's call.
-Customer rep Bronte stated Kate was not in yet.
-Bronte said she would let Kate know the caller returned her call when Kate arrived.</t>
+          <t>Customer Cindy Hannah called to return a missed call from Kate.
+Kate was unavailable at the time of the call.
+The representative took a message to pass along to Kate.</t>
         </is>
       </c>
       <c r="AU4" s="5" t="inlineStr"/>
-      <c r="AV4" s="5" t="inlineStr">
-        <is>
-          <t>Kate to follow up with Cindy (Hannah) after receiving the message.
-Cindy (Hannah) to wait for Kate's return call.</t>
-        </is>
-      </c>
+      <c r="AV4" s="5" t="inlineStr"/>
       <c r="AW4" s="5" t="n">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="AX4" s="5" t="n">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="AY4" s="5" t="n">
         <v>0</v>
@@ -1860,7 +1886,7 @@
       <c r="BD4" s="5" t="n"/>
       <c r="BE4" s="5" t="inlineStr">
         <is>
-          <t>not_booked</t>
+          <t>booked</t>
         </is>
       </c>
       <c r="BF4" s="5" t="inlineStr">
@@ -1908,10 +1934,10 @@
       <c r="BR4" s="5" t="n"/>
       <c r="BS4" s="5" t="inlineStr"/>
       <c r="BT4" s="5" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="BU4" s="5" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="BV4" s="5" t="inlineStr">
         <is>
@@ -1920,14 +1946,13 @@
       </c>
       <c r="BW4" s="5" t="inlineStr">
         <is>
-          <t>Confirm Project Details, Set Expectations for Next Steps, Address Questions/Concerns</t>
+          <t>Confirm Project Details, Address Questions/Concerns, Set Expectations for Next Steps</t>
         </is>
       </c>
       <c r="BX4" s="5" t="inlineStr">
         <is>
-          <t>[medium] After the homeowner said they were returning Kate's call, the rep only stated Kate wasn't in yet and said they would let her know, without confirming the caller's identity details or the related project/job. | Fix: Acknowledge the callback, then capture/confirm key details: caller name (spelled), best callback number, address, and what the call is regarding (project stage or question).
-[medium] The rep did not set any expectation for when Kate would be available or when the customer should expect a return call, and did not offer an alternative (e.g., another team member) if urgent. | Fix: Provide a timeframe and a clear next step, and offer escalation if time-sensitive.
-[low] The rep ended the call without asking if the homeowner had any questions or needed help with anything else while waiting for Kate. | Fix: Before closing, invite questions and offer immediate assistance within scope.</t>
+          <t>[medium] When the customer stated they were returning Kate's call, the rep immediately offered to take a message without asking if they could look up the account or assist the customer themselves. | Fix: Always offer to pull up the customer's file and assist them in the other representative's absence before resorting to taking a message.
+[medium] The rep took a message without verifying the customer's phone number or providing an expectation of when Kate would return. | Fix: Confirm the best callback number and give a general timeframe for when the requested representative will be available.</t>
         </is>
       </c>
       <c r="BY4" s="5" t="n">
@@ -1935,7 +1960,7 @@
       </c>
       <c r="BZ4" s="5" t="inlineStr"/>
       <c r="CA4" s="5" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="CB4" s="5" t="n">
         <v>6</v>
@@ -1946,10 +1971,10 @@
         </is>
       </c>
       <c r="CD4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF4" s="5" t="n">
         <v>0</v>
@@ -1957,30 +1982,34 @@
       <c r="CG4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CH4" s="5" t="inlineStr"/>
+      <c r="CH4" s="5" t="inlineStr">
+        <is>
+          <t>[High] Booking Status: Mismatch — PROD='not_booked' STAGING='booked'</t>
+        </is>
+      </c>
       <c r="CI4" s="5" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="CJ4" s="5" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="CK4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="CL4" s="5" t="inlineStr"/>
-      <c r="CM4" s="8" t="inlineStr">
+      <c r="CM4" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CN4" s="8" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
       </c>
-      <c r="CN4" s="8" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="CO4" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="CO4" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2034,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>audio_test_4_d8091a92</t>
+          <t>gemini_cmp_4_da5ef94f</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2013,7 +2042,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="n">
+        <v>195.2</v>
+      </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Alshiana, a real estate agent in Arizona, called on behalf of a client who is under contract to purchase a property and wants a quote because the roof is in rough condition. Steve confirmed they can provide an estimate and asked about the transaction stage and timeline; Alshiana said they need it as soon as possible. Steve explained that for real estate transactions there is a one-time $399 fee for a technician to come out and provide a full estimate and report with 15–100 photos, and that the fee is applied toward any repairs or replacement if they choose to use the company. Alshiana said she needs to check with her clients about the fee since they would pay it, and she will call back; no appointment was scheduled.</t>
@@ -2163,44 +2194,37 @@
       </c>
       <c r="AS5" s="5" t="inlineStr">
         <is>
-          <t>Alshiana, a real estate agent in Arizona, called on behalf of a client who is under contract to purchase a property and wants a quote because the roof is in rough condition. Steve confirmed they can provide an estimate and asked about the transaction stage and timeline; Alshiana said they need it as soon as possible. Steve explained that for real estate transactions there is a one-time $399 fee for a technician to come out and provide a full estimate and report with 15–100 photos, and that the fee is applied toward any repairs or replacement if they choose to use the company. Alshiana said she needs to check with her clients about the fee since they would pay it, and she will call back; no appointment was scheduled.</t>
+          <t>A real estate agent named Alshiana called on behalf of clients who are under contract to purchase a property. She requested a repair quote because the roof is in rough condition, noting that they are on a timeline. The representative explained that real estate transaction estimates require a $399 fee, which includes a comprehensive report with photos and is credited toward any eventual repairs or replacements. The agent declined to schedule immediately, stating she needs to confirm with her clients if they are willing to pay the fee, and promised to call back with their decision.</t>
         </is>
       </c>
       <c r="AT5" s="5" t="inlineStr">
         <is>
-          <t>Caller is a real estate agent (Alshiana) calling for a client who is under contract to purchase a property and wants a roof quote due to the roof being in rough condition.
-Customer requested the estimate/quote as soon as the company can do it (ASAP).
-Rep stated real estate transaction estimates require a one-time $399 fee for a technician to provide a full estimate/report with 15–100 photos, and the fee goes toward repairs/replacement if they proceed; caller will check with the client and call back, so no scheduling occurred.</t>
-        </is>
-      </c>
-      <c r="AU5" s="5" t="inlineStr">
-        <is>
-          <t>Confirm with their clients whether they approve and will pay the $300 inspection fee, then notify the company of the decision</t>
-        </is>
-      </c>
+          <t>The caller is a real estate agent requesting a roof repair quote for clients who are currently under contract to purchase a home.
+The property's roof is described as being in rough condition and the buyers are on a timeline.
+Arizona Roofers charges a $399 fee for real estate transaction estimates, which includes a full report and photos, but is applied toward future repairs.
+No appointment was scheduled on the call because the agent needs her clients' approval to pay the $399 inspection fee.</t>
+        </is>
+      </c>
+      <c r="AU5" s="5" t="inlineStr"/>
       <c r="AV5" s="5" t="inlineStr">
         <is>
-          <t>Caller (Alshiana) will confirm with her client whether they approve the $399 fee.
-Caller will contact the company again to schedule the technician visit if the client agrees.</t>
+          <t>The real estate agent will discuss the $399 inspection fee with her clients.
+The real estate agent will contact Arizona Roofers back if the clients agree to proceed with the paid estimate.</t>
         </is>
       </c>
       <c r="AW5" s="5" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AX5" s="5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AY5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ5" s="5" t="inlineStr">
-        <is>
-          <t>[get_approval] Confirm with their clients whether they approve and will pay the $300 inspection fee, then notify the company of the decision (owner: customer name, due: None)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="5" t="inlineStr"/>
       <c r="BA5" s="5" t="inlineStr">
         <is>
-          <t>alshiana</t>
+          <t>Alshiana</t>
         </is>
       </c>
       <c r="BB5" s="5" t="inlineStr"/>
@@ -2211,7 +2235,7 @@
       </c>
       <c r="BD5" s="5" t="inlineStr">
         <is>
-          <t>Roof inspection/estimate for real estate transaction (quote with full report/photos)</t>
+          <t>Roof estimate</t>
         </is>
       </c>
       <c r="BE5" s="5" t="inlineStr">
@@ -2256,52 +2280,48 @@
         <v>0.8</v>
       </c>
       <c r="BP5" s="5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="BQ5" s="5" t="n">
-        <v>0.575</v>
+        <v>0.65</v>
       </c>
       <c r="BR5" s="5" t="n"/>
       <c r="BS5" s="5" t="inlineStr"/>
       <c r="BT5" s="5" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="BU5" s="5" t="n">
-        <v>0.42</v>
+        <v>0.5</v>
       </c>
       <c r="BV5" s="5" t="inlineStr">
         <is>
-          <t>Greeting &amp; Identification, Qualifying (partial)</t>
+          <t>Greeting &amp; Identification, Qualifying, Setting Expectations</t>
         </is>
       </c>
       <c r="BW5" s="5" t="inlineStr">
         <is>
-          <t>Needs Discovery, Scheduling, Setting Expectations, Close &amp; Confirmation, Objection Handling</t>
+          <t>Needs Discovery, Objection Handling, Close &amp; Confirmation</t>
         </is>
       </c>
       <c r="BX5" s="5" t="inlineStr">
         <is>
-          <t>[medium] After the caller explained the roof is in rough condition and they want a quote, the rep moved quickly to contract stage/timeline and then to the $399 fee without asking basic diagnostic questions (roof type, size, age, specific issues, access, address). | Fix: Run a short discovery sequence before pricing: confirm property address, roof type/material, approximate age, visible damage/leaks, and whether an inspection report exists. Then tie the fee to their specific situation and the value of the deliverable.
-[high] The rep did not verify decision-maker/payment authority and treated the real estate agent as if they could approve the $399 fee, even though the caller later stated the client would need to pay/approve it. | Fix: Early in the call, confirm who the homeowner/buyer is, who will authorize the inspection fee, and the best way to reach them. If the agent is calling, ask to loop in the buyer/seller or get permission to contact them directly.
-[high] When the caller hesitated on the $399 fee and said they would get back to the company, the rep did not attempt to overcome the objection, offer alternatives, or set a concrete follow-up plan (date/time to call back). | Fix: Acknowledge the concern, reinforce value, explore options (e.g., credit applied to work, limited-time scheduling, speaking directly with the client), and lock a follow-up time or offer to tentatively hold an appointment pending client approval.
-[high] The rep did not proceed to scheduling by offering specific appointment windows or collecting access details (who will be present, gate codes, pets, HOA) and did not confirm contact/address information. | Fix: Transition from qualification to scheduling with two concrete options and collect required logistics and contact verification.
-[medium] The call ended without a proper close/confirmation: no recap, no next steps, no promise of a confirmation text/email, and no agreed follow-up time. | Fix: Close with a clear next step even if not booked: confirm you’ll follow up at a specific time, provide a direct callback number, and offer to send fee details via text/email.</t>
+          <t>[high] The rep allowed the caller to end the call to 'check with clients' without gathering any contact information or setting a structured follow-up. | Fix: Before letting the caller off the phone, ask for their direct contact information and set a specific time to follow up.
+[medium] The rep jumped straight into scheduling and quoting the inspection fee without asking for the property address or details about the roof's condition. | Fix: After identifying they need a quote, ask for the property address and a brief description of the issues.</t>
         </is>
       </c>
       <c r="BY5" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BZ5" s="5" t="inlineStr">
         <is>
-          <t>[Service Fee Concerns] "Okay. get that scheduled for you? Um, I'll have to check up my clients to see if they're okay with the $300 fee, cause it'll be them that had to take care of it." (Unresolved, severity=medium)
-[Customer Needs Time to Decide] "Yeah, I'll get back to you guys." (Unresolved, severity=low)</t>
+          <t>[Service Fee Concerns] "Okay. I'll have to check up my clients to see if they're okay with the three hundred dollar fee because it will be them that have to take care of it." (Unresolved, severity=medium)</t>
         </is>
       </c>
       <c r="CA5" s="5" t="n">
-        <v>1725</v>
+        <v>1790</v>
       </c>
       <c r="CB5" s="5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="CC5" s="5" t="inlineStr">
         <is>
@@ -2309,26 +2329,30 @@
         </is>
       </c>
       <c r="CD5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="CF5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CH5" s="5" t="inlineStr"/>
+      <c r="CH5" s="5" t="inlineStr">
+        <is>
+          <t>[Medium] BANT Timeline: Score Delta — PROD=0.5 STAGING=0.8 delta=0.300 (threshold=0.2)</t>
+        </is>
+      </c>
       <c r="CI5" s="5" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="CJ5" s="5" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="CK5" s="5" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="CL5" s="5" t="inlineStr"/>
       <c r="CM5" s="8" t="inlineStr">
@@ -2368,7 +2392,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>test-fix-flores-001</t>
+          <t>gemini_cmp_5_76f5b613</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -2376,7 +2400,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="n">
+        <v>1.2</v>
+      </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Cindy Hannah called Arizona Roofers to return a call from Kate. Bronte informed Cindy that Kate was not in yet and said she would let Kate know that Cindy called when she arrived. The call ended politely without discussing any roofing issue, property details, or scheduling.</t>
@@ -2499,28 +2525,23 @@
       </c>
       <c r="AS6" s="5" t="inlineStr">
         <is>
-          <t>Cindy Hannah called Arizona Roofers to return a call from Kate. Bronte informed Cindy that Kate was not in yet and said she would let Kate know that Cindy called when she arrived. The call ended politely without discussing any roofing issue, property details, or scheduling.</t>
+          <t>Cindy Hannah called Arizona Refers to return a previous call from a female representative who was not currently in the office. The customer service representative, Broughte, took the message and assured Cindy that her colleague would be notified to call her back upon her arrival.</t>
         </is>
       </c>
       <c r="AT6" s="5" t="inlineStr">
         <is>
-          <t>Caller identified herself as Cindy Hannah and said she was returning Kate's call.
-Customer rep Bronte stated Kate was not in yet.
-Bronte said she would let Kate know Cindy called when Kate is there; no appointment or service details were discussed.</t>
+          <t>Caller Cindy Hannah is returning a missed call from a specific female representative.
+The requested representative was not in the office at the time of the call.
+Broughte promised to relay the message to the representative once she arrives.</t>
         </is>
       </c>
       <c r="AU6" s="5" t="inlineStr"/>
-      <c r="AV6" s="5" t="inlineStr">
-        <is>
-          <t>Kate to follow up with Cindy Hannah after receiving the message.
-If needed, Kate to clarify the reason for the call and determine whether any roofing service is requested.</t>
-        </is>
-      </c>
+      <c r="AV6" s="5" t="inlineStr"/>
       <c r="AW6" s="5" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AX6" s="5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AY6" s="5" t="n">
         <v>0</v>
@@ -2536,15 +2557,19 @@
       <c r="BD6" s="5" t="n"/>
       <c r="BE6" s="5" t="inlineStr">
         <is>
-          <t>not_booked</t>
+          <t>booked</t>
         </is>
       </c>
       <c r="BF6" s="5" t="inlineStr">
         <is>
-          <t>fresh_sales</t>
-        </is>
-      </c>
-      <c r="BG6" s="5" t="inlineStr"/>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="BG6" s="5" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
       <c r="BH6" s="5" t="inlineStr">
         <is>
           <t>unqualified</t>
@@ -2580,26 +2605,25 @@
       <c r="BR6" s="5" t="n"/>
       <c r="BS6" s="5" t="inlineStr"/>
       <c r="BT6" s="5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="BU6" s="5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="BV6" s="5" t="inlineStr">
         <is>
-          <t>Greeting &amp; Identification</t>
+          <t>Greeting &amp; Identification, Close Professionally</t>
         </is>
       </c>
       <c r="BW6" s="5" t="inlineStr">
         <is>
-          <t>Needs Discovery, Qualifying (BANT), Scheduling, Setting Expectations, Close &amp; Confirmation</t>
+          <t>Confirm Project Details, Set Expectations for Next Steps, Address Questions/Concerns</t>
         </is>
       </c>
       <c r="BX6" s="5" t="inlineStr">
         <is>
-          <t>[high] When the caller said they were returning Kate's call, the rep only stated Kate wasn't in and ended the call without gathering a callback number, email, or details about what Kate called about. | Fix: Use a brief message-taking workflow: confirm the caller’s full name, best callback number, address (if relevant), and what the call is regarding; then confirm when/ how Kate will return the call.
-[medium] After learning the requested person was unavailable, the rep did not offer any alternative path (transfer to another rep, scheduling an appointment, or taking a detailed message with a promised callback window). | Fix: Offer immediate alternatives: check if another team member can assist, offer to schedule an inspection/estimate, or set a specific callback time window.
-[medium] The call ended without confirming next steps (who will call back, expected timing, and confirmation of the caller’s contact method). | Fix: Close with a clear commitment and confirmation: restate the action, timeframe, and how the customer will be contacted; confirm the best number.</t>
+          <t>[medium] When the customer stated they were returning a call for another rep, the current rep simply took a message without attempting to look up the account or ask what the call was regarding. | Fix: Always offer to help the customer before defaulting to taking a message. Ask for their phone number or address to locate their file.
+[medium] The rep agreed to pass on the message but did not verify the caller's phone number or give any indication of when the original rep would call back. | Fix: Verify the best callback number and set clear expectations for when the call will be returned.</t>
         </is>
       </c>
       <c r="BY6" s="5" t="n">
@@ -2618,10 +2642,10 @@
         </is>
       </c>
       <c r="CD6" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE6" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CF6" s="5" t="n">
         <v>0</v>
@@ -2629,30 +2653,35 @@
       <c r="CG6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CH6" s="5" t="inlineStr"/>
+      <c r="CH6" s="5" t="inlineStr">
+        <is>
+          <t>[High] Booking Status: Mismatch — PROD='not_booked' STAGING='booked'
+[High] Call Type: Mismatch — PROD='fresh_sales' STAGING='follow_up'</t>
+        </is>
+      </c>
       <c r="CI6" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="CJ6" s="5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="CK6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="CL6" s="5" t="inlineStr"/>
-      <c r="CM6" s="8" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="CN6" s="8" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="CO6" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="CM6" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CN6" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CO6" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2677,15 +2706,17 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>test-fix-sandiego-002</t>
+          <t>gemini_cmp_6_9a526ced</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>614.8</v>
+      </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
           <t>The caller asked to speak with the owner or marketing manager to discuss a deal with the company. The representative (Nika) did not transfer the call and instead requested that the caller send an email. The caller acknowledged the request but paused the conversation with “wait, hold on,” and the call ended without any service details, scheduling, or resolution.</t>
@@ -2807,27 +2838,23 @@
       </c>
       <c r="AS7" s="5" t="inlineStr">
         <is>
-          <t>The caller asked to speak with the owner or marketing manager to discuss a deal with the company. The representative (Nika) did not transfer the call and instead requested that the caller send an email. The caller acknowledged the request but paused the conversation with “wait, hold on,” and the call ended without any service details, scheduling, or resolution.</t>
+          <t>The caller contacted Arizona Roofers requesting to speak with the owner or marketing manager to discuss a business deal. The representative declined to transfer the call and instead asked the caller to send an email with their proposal. The caller initially agreed but then abruptly asked the representative to wait and hold as the transcript ended.</t>
         </is>
       </c>
       <c r="AT7" s="5" t="inlineStr">
         <is>
-          <t>Caller asked if they were speaking with the owner or marketing manager.
-Caller stated they wanted to discuss a deal with the company.
-Representative asked the caller to send an email instead of continuing on the phone; no appointment or service request was made.</t>
+          <t>The caller requested to speak directly with the owner or marketing manager.
+The caller's stated purpose was to discuss a deal with the company, indicating a likely B2B solicitation.
+The representative directed the caller to send an email instead of transferring the call.</t>
         </is>
       </c>
       <c r="AU7" s="5" t="inlineStr"/>
-      <c r="AV7" s="5" t="inlineStr">
-        <is>
-          <t>Caller to email the company with details about the proposed deal.</t>
-        </is>
-      </c>
+      <c r="AV7" s="5" t="inlineStr"/>
       <c r="AW7" s="5" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AX7" s="5" t="n">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="AY7" s="5" t="n">
         <v>0</v>
@@ -2851,7 +2878,11 @@
           <t>new_inquiry</t>
         </is>
       </c>
-      <c r="BG7" s="5" t="inlineStr"/>
+      <c r="BG7" s="5" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
       <c r="BH7" s="5" t="inlineStr">
         <is>
           <t>unqualified</t>
@@ -2887,26 +2918,25 @@
       <c r="BR7" s="5" t="n"/>
       <c r="BS7" s="5" t="inlineStr"/>
       <c r="BT7" s="5" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="BU7" s="5" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="BV7" s="5" t="inlineStr">
         <is>
-          <t>Greeting &amp; Identification (partial)</t>
+          <t>Greeting &amp; Identification</t>
         </is>
       </c>
       <c r="BW7" s="5" t="inlineStr">
         <is>
-          <t>Needs Discovery, Qualifying (BANT), Scheduling, Setting Expectations, Close &amp; Confirmation</t>
+          <t>Needs Discovery, Qualifying, Setting Expectations, Close &amp; Confirmation</t>
         </is>
       </c>
       <c r="BX7" s="5" t="inlineStr">
         <is>
-          <t>[high] After the caller asked, "is this the owner or marketing manager?" the rep responded unclearly ("Uh, we know the reason why.") and then quickly pushed the caller to email ("can you just kindly, uh, send us over an email instead?") without clarifying the request or offering to connect/route them. | Fix: Acknowledge the request, clarify what they need, and offer a clear routing path. Collect name, company, callback/email, and set an expectation for who will respond and when. If you must redirect to email, provide the exact address and confirm you’ll forward it internally.
-[medium] The rep did not complete Greeting &amp; Identification beyond a first name/location and did not ask for the caller’s name or any contact details before ending the interaction. | Fix: Immediately after the greeting, ask for the caller’s name and best callback/email, then confirm it back. Even for non-service inquiries, capture contact details before transferring or redirecting.
-[medium] No close and confirmation occurred: the rep did not provide an email address, did not confirm what to include in the email, and did not set a follow-up timeframe; the caller ended with hesitation ("wait, hold on"). | Fix: Summarize the request, give the exact next step (email/transfer), confirm the details to include, and set a response SLA. Ask if there’s anything else before ending.</t>
+          <t>[high] After the caller asked if they were speaking to the owner or marketing manager, the rep bluntly demanded 'I need the reason why' instead of professionally discovering the caller's needs. | Fix: Use a professional, polite probing question to understand the purpose of the call before routing or handling the request.
+[medium] The rep abruptly dismissed the caller by telling them to send an email, without actually providing the company email address or properly concluding the conversation. | Fix: Politely provide the exact email address the caller should use, and formally close the call.</t>
         </is>
       </c>
       <c r="BY7" s="5" t="n">
@@ -2914,7 +2944,7 @@
       </c>
       <c r="BZ7" s="5" t="inlineStr"/>
       <c r="CA7" s="5" t="n">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="CB7" s="5" t="n">
         <v>6</v>
@@ -2938,10 +2968,10 @@
       </c>
       <c r="CH7" s="5" t="inlineStr"/>
       <c r="CI7" s="5" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="CJ7" s="5" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="CK7" s="5" t="n">
         <v>0</v>
@@ -2984,15 +3014,17 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>NOT SUBMITTED</t>
+          <t>gemini_cmp_7_6551909f</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>667</v>
+      </c>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr"/>
@@ -3030,43 +3062,121 @@
       <c r="AP8" s="5" t="inlineStr"/>
       <c r="AQ8" s="5" t="inlineStr"/>
       <c r="AR8" s="5" t="inlineStr"/>
-      <c r="AS8" s="5" t="inlineStr"/>
-      <c r="AT8" s="5" t="inlineStr"/>
+      <c r="AS8" s="5" t="inlineStr">
+        <is>
+          <t>Ash spoke with a representative at Arizona Reapers to confirm details before moving a roof installation project into the scheduling phase. The representative verified Ash's contact information and address in Gilbert, and outlined the upcoming processes, including material delivery, the 1-3 day installation timeline, and requirements for keeping the driveway clear. Ash emphasized wanting the project to start as soon as possible. The representative also explained the final walkthrough process for warranty release and informed Ash about a standard, non-actionable pre-lien notice they would receive from Titan Lien Services. Critically, Ash requested that the assigned Project Manager coordinate with Will regarding a specific attic area repair outlined in the initial contract to ensure there are no surprises during the installation.</t>
+        </is>
+      </c>
+      <c r="AT8" s="5" t="inlineStr">
+        <is>
+          <t>Customer's property is located at 585 East Constitution Drive in Gilbert, 85296.
+Customer expressed high urgency for the roof installation, stating it needs to be done as soon as possible because 'it's already been too late'.
+Customer specifically requested that the Project Manager review the site and coordinate with Will regarding an attic area repair that was included in the initial contract.
+Customer was instructed to keep the driveway clear for material delivery (roof loading) and during the 1-3 day installation period to accommodate a dumpster.
+Customer was notified to expect a standard pre-lien notice from Titan Lien Services via mail, which does not require a signature or return action.</t>
+        </is>
+      </c>
       <c r="AU8" s="5" t="inlineStr"/>
       <c r="AV8" s="5" t="inlineStr"/>
-      <c r="AW8" s="5" t="inlineStr"/>
-      <c r="AX8" s="5" t="inlineStr"/>
-      <c r="AY8" s="5" t="inlineStr"/>
+      <c r="AW8" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX8" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AY8" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ8" s="5" t="inlineStr"/>
-      <c r="BA8" s="5" t="inlineStr"/>
+      <c r="BA8" s="5" t="n"/>
       <c r="BB8" s="5" t="inlineStr"/>
-      <c r="BC8" s="5" t="inlineStr"/>
-      <c r="BD8" s="5" t="inlineStr"/>
-      <c r="BE8" s="5" t="inlineStr"/>
-      <c r="BF8" s="5" t="inlineStr"/>
-      <c r="BG8" s="5" t="inlineStr"/>
-      <c r="BH8" s="5" t="inlineStr"/>
-      <c r="BI8" s="5" t="inlineStr"/>
-      <c r="BJ8" s="5" t="inlineStr"/>
-      <c r="BK8" s="5" t="inlineStr"/>
-      <c r="BL8" s="5" t="inlineStr"/>
-      <c r="BM8" s="5" t="inlineStr"/>
-      <c r="BN8" s="5" t="inlineStr"/>
-      <c r="BO8" s="5" t="inlineStr"/>
-      <c r="BP8" s="5" t="inlineStr"/>
-      <c r="BQ8" s="5" t="inlineStr"/>
-      <c r="BR8" s="5" t="inlineStr"/>
+      <c r="BC8" s="5" t="inlineStr">
+        <is>
+          <t>unqualified</t>
+        </is>
+      </c>
+      <c r="BD8" s="5" t="n"/>
+      <c r="BE8" s="5" t="inlineStr">
+        <is>
+          <t>not_booked</t>
+        </is>
+      </c>
+      <c r="BF8" s="5" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="BG8" s="5" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="BH8" s="5" t="inlineStr">
+        <is>
+          <t>unqualified</t>
+        </is>
+      </c>
+      <c r="BI8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ8" s="5" t="n"/>
+      <c r="BK8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL8" s="5" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="BM8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" s="5" t="n"/>
       <c r="BS8" s="5" t="inlineStr"/>
-      <c r="BT8" s="5" t="inlineStr"/>
-      <c r="BU8" s="5" t="inlineStr"/>
-      <c r="BV8" s="5" t="inlineStr"/>
+      <c r="BT8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV8" s="5" t="inlineStr">
+        <is>
+          <t>Greeting &amp; Identification, Confirm Project Details, Set Expectations for Next Steps, Address Questions/Concerns, Close Professionally</t>
+        </is>
+      </c>
       <c r="BW8" s="5" t="inlineStr"/>
-      <c r="BX8" s="5" t="inlineStr"/>
-      <c r="BY8" s="5" t="inlineStr"/>
+      <c r="BX8" s="5" t="inlineStr">
+        <is>
+          <t>[low] When the customer explained their specific concern about an attic repair being properly communicated to the project manager, the rep admitted to missing the first part of the explanation and had to ask the customer to repeat it. | Fix: Practice active listening and take continuous notes when a customer brings up a custom detail. If you need them to clarify, frame it positively as making sure you have the exact details for the project manager rather than admitting you missed it.</t>
+        </is>
+      </c>
+      <c r="BY8" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="BZ8" s="5" t="inlineStr"/>
-      <c r="CA8" s="5" t="inlineStr"/>
-      <c r="CB8" s="5" t="inlineStr"/>
-      <c r="CC8" s="5" t="inlineStr"/>
+      <c r="CA8" s="5" t="n">
+        <v>6818</v>
+      </c>
+      <c r="CB8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CC8" s="5" t="inlineStr">
+        <is>
+          <t>customer_rep</t>
+        </is>
+      </c>
       <c r="CD8" s="5" t="n">
         <v>0</v>
       </c>
@@ -3084,14 +3194,14 @@
       <c r="CJ8" s="5" t="inlineStr"/>
       <c r="CK8" s="5" t="inlineStr"/>
       <c r="CL8" s="5" t="inlineStr"/>
-      <c r="CM8" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="CN8" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="CM8" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CN8" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="CO8" s="7" t="inlineStr">
@@ -3121,7 +3231,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>audio_test_8_5067ce6c</t>
+          <t>gemini_cmp_8_261ad6c4</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3129,7 +3239,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="n">
+        <v>1.1</v>
+      </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Phil, a sales rep, called trying to reach Jada because he needed to help a customer (Michael Badel) who had questions related to a large job and a gutter scheduled to be installed tomorrow (2026-03-06). The customer service rep, Diva, said she was not in the office and asked if Phil had a direct line; Phil explained he had tried WhatsApp and calling different people but couldn’t reach anyone. Diva offered to provide Jada’s direct phone number, gave it to Phil (602-545-6385), and Phil thanked her before ending the call.</t>
@@ -3256,28 +3368,24 @@
       </c>
       <c r="AS9" s="5" t="inlineStr">
         <is>
-          <t>Phil, a sales rep, called trying to reach Jada because he needed to help a customer (Michael Badel) who had questions related to a large job and a gutter scheduled to be installed tomorrow (2026-03-06). The customer service rep, Diva, said she was not in the office and asked if Phil had a direct line; Phil explained he had tried WhatsApp and calling different people but couldn’t reach anyone. Diva offered to provide Jada’s direct phone number, gave it to Phil (602-545-6385), and Phil thanked her before ending the call.</t>
+          <t>Internal sales representative Joe called the office seeking a direct line for a colleague named Jade. He needed to speak with her urgently regarding a large project for a customer named Michael Beedle, who has questions about a gutter installation scheduled for the next day. The customer service representative, Diva, successfully provided Jade's direct phone number to facilitate the connection.</t>
         </is>
       </c>
       <c r="AT9" s="5" t="inlineStr">
         <is>
-          <t>Caller Phil identified himself as a sales rep and asked if Jada was available.
-Phil said they have a big job with Michael Badel, who had questions, and mentioned a gutter going in tomorrow (2026-03-06).
-Rep Diva was not in the office and provided Jada’s direct phone number (602-545-6385) so Phil could reach her.</t>
+          <t>The caller, Joe, is an internal sales rep trying to reach a colleague named Jade after failing to connect via WhatsApp and other numbers.
+The call concerns a customer named Michael Beedle who has a large job involving a gutter installation scheduled for tomorrow (2026-03-27).
+Michael Beedle has pending questions about the upcoming gutter installation that need to be addressed.
+The customer service rep provided Jade's direct phone number to Joe.</t>
         </is>
       </c>
       <c r="AU9" s="5" t="inlineStr"/>
-      <c r="AV9" s="5" t="inlineStr">
-        <is>
-          <t>Phil to contact Jada directly at 602-545-6385 to address Michael Badel’s questions.
-Coordinate guidance for the gutter installation scheduled for 2026-03-06.</t>
-        </is>
-      </c>
+      <c r="AV9" s="5" t="inlineStr"/>
       <c r="AW9" s="5" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="AX9" s="5" t="n">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="AY9" s="5" t="n">
         <v>0</v>
@@ -3341,10 +3449,10 @@
       <c r="BR9" s="5" t="n"/>
       <c r="BS9" s="5" t="inlineStr"/>
       <c r="BT9" s="5" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BU9" s="5" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BV9" s="5" t="inlineStr">
         <is>
@@ -3353,14 +3461,13 @@
       </c>
       <c r="BW9" s="5" t="inlineStr">
         <is>
-          <t>Confirm Project Details, Set Expectations for Next Steps, Close Professionally</t>
+          <t>Close Professionally</t>
         </is>
       </c>
       <c r="BX9" s="5" t="inlineStr">
         <is>
-          <t>[medium] After the caller said they were a sales rep and needed help for 'a big job' (Michael Badel), the rep immediately offered and provided Jada’s direct phone number without verifying the caller’s identity, role, or authorization tied to that project. | Fix: Before sharing direct numbers, verify the caller and confirm the project details. If verification is unclear, offer to take a message and route it internally or initiate an approved callback workflow.
-[high] When the caller explained the situation (customer has questions; gutter going in tomorrow; can’t reach anyone), the rep did not confirm key project details (customer name, address, scheduled date/time, nature of questions) and did not attempt to resolve or route the issue beyond giving a number. | Fix: Use a quick confirm-and-capture step: confirm the customer/project identifiers, capture the exact questions, and provide a clear next step (message relay, ticket, escalation, or callback commitment).
-[low] The rep did not close professionally by confirming the next step, offering additional help, or providing a support contact; the call ended with a brief send-off. | Fix: Close with a confirmation and support offer: restate what was provided, confirm what will happen next, and invite further questions with a main line or escalation option.</t>
+          <t>[medium] When providing Jade's direct line, the rep read off a highly confused and jumbled string of numbers and corrected herself multiple times without doing a clean, full read-back. | Fix: Read phone numbers slowly in standard segments (e.g., Area Code, Prefix, Line Number). After making a mistake, pause, apologize, and repeat the entire number cleanly. Ask the caller to confirm they wrote it down correctly.
+[low] The rep closed the call abruptly with just 'No problem' after the caller said 'Perfect Thank you'. | Fix: Always offer further assistance before disconnecting, ensuring all needs have been met, even on quick internal calls.</t>
         </is>
       </c>
       <c r="BY9" s="5" t="n">
@@ -3368,10 +3475,10 @@
       </c>
       <c r="BZ9" s="5" t="inlineStr"/>
       <c r="CA9" s="5" t="n">
-        <v>978</v>
+        <v>910</v>
       </c>
       <c r="CB9" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="CC9" s="5" t="inlineStr">
         <is>
@@ -3392,10 +3499,10 @@
       </c>
       <c r="CH9" s="5" t="inlineStr"/>
       <c r="CI9" s="5" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="CJ9" s="5" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="CK9" s="5" t="n">
         <v>0</v>
@@ -3446,7 +3553,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
+      <c r="G10" s="5" t="n">
+        <v>1.1</v>
+      </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Selena (homeowner) returned a call to Raven at Arizona Roofers to discuss next steps for an upcoming roof installation at 133 E Indigo St, Mesa, AZ 85201. Raven confirmed the customer’s contact details and explained the installation process: materials drop-off can occur between 6am–6pm with no one required to be home as long as the driveway is clear; installation typically takes 1–3 days; a project manager will contact them before or the morning of installation and will schedule a final walkthrough and job completion form (email option if not onsite). Selena clarified the property is a rental and requested scheduling be coordinated with the tenant, Wacey Wey, providing his phone number (505-614-9250) and noting he works night shift; she also asked to be notified once scheduling is set so she can remind the tenant. Raven also explained a pre-lien notice will be mailed as a standard Arizona legal notice and does not need to be signed, and Raven stated she will contact the tenant to gather availability and that scheduling typically takes about a week, with an email and call to follow.</t>
@@ -3744,15 +3853,17 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>audio_test_10_56469bfa</t>
+          <t>gemini_cmp_10_797392b8</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>741.8</v>
+      </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
           <t>The homeowner called Arizona Roofers to ask whether the company provides free estimates for roof repairs and whether an estimate could be based on a buyer-provided report for a property currently in escrow. Maddie confirmed free estimates for homeowners but explained that an on-site roof inspection is still required. After clarifying they are beyond the 10-day inspection period and in escrow, Maddie checked availability and offered the soonest appointment as next Monday, 2026-03-09. The homeowner asked if anything sooner was available, but Maddie said they were booked for the rest of the week, and the call ended without scheduling an appointment.</t>
@@ -3889,28 +4000,29 @@
       </c>
       <c r="AS11" s="5" t="inlineStr">
         <is>
-          <t>The homeowner called Arizona Rooters to ask if the company provides free estimates for roof repair and whether an estimate could be based on a buyer-provided report. The representative confirmed free estimates for homeowners but explained an on-site roof inspection would still be required, and asked about the 10-day inspection period; the caller said they were past it. The homeowner asked how quickly someone could come out, and the representative offered the soonest availability as next Monday, 2026-03-09, with nothing sooner due to being booked the rest of the week. The caller declined to schedule and ended the call after hearing the earliest date.</t>
+          <t>A homeowner called to request a free roof repair estimate based on a buyer's inspection report, noting they are selling the property and are past their 10-day inspection period. The representative explained that an in-person inspection is required to provide an estimate but could not schedule a visit until the following Monday due to the team being fully booked for the week. Consequently, the homeowner decided not to schedule an appointment.</t>
         </is>
       </c>
       <c r="AT11" s="5" t="inlineStr">
         <is>
-          <t>Customer requested a free estimate for roof repair.
-Customer asked if they could send a buyer report for an estimate, but the rep said an inspection would still be required.
-Rep’s soonest availability was next Monday (2026-03-09); customer asked for something sooner, was told no, and did not book an appointment.</t>
+          <t>The homeowner requested a free roof repair estimate based on an existing buyer's inspection report.
+The customer explicitly mentioned they are past their 10-day inspection period and have already received a BINSR (Buyer's Inspection Notice and Seller's Response).
+The representative clarified that an in-person inspection is mandatory to provide an estimate.
+The earliest available appointment offered was for the following Monday (the 9th), as the company was fully booked with several staff members out.
+The call concluded without booking, as the homeowner declined to schedule due to the timeline.</t>
         </is>
       </c>
       <c r="AU11" s="5" t="inlineStr"/>
       <c r="AV11" s="5" t="inlineStr">
         <is>
-          <t>If the customer calls back, offer to schedule the roof inspection for 2026-03-09 or the next available slot.
-If the customer wants, have them send the buyer report to reference alongside the on-site inspection.</t>
+          <t>No further steps are required as the homeowner chose not to proceed with booking an appointment.</t>
         </is>
       </c>
       <c r="AW11" s="5" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AX11" s="5" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="AY11" s="5" t="n">
         <v>0</v>
@@ -3920,12 +4032,12 @@
       <c r="BB11" s="5" t="inlineStr"/>
       <c r="BC11" s="5" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="BD11" s="5" t="inlineStr">
         <is>
-          <t>Roof repair estimate / roof inspection (free estimate)</t>
+          <t>roof repairs</t>
         </is>
       </c>
       <c r="BE11" s="5" t="inlineStr">
@@ -3953,7 +4065,7 @@
       </c>
       <c r="BJ11" s="5" t="n"/>
       <c r="BK11" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL11" s="5" t="inlineStr">
         <is>
@@ -3967,86 +4079,79 @@
         <v>1</v>
       </c>
       <c r="BO11" s="5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="BP11" s="5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="BQ11" s="5" t="n">
-        <v>0.7</v>
+        <v>0.825</v>
       </c>
       <c r="BR11" s="5" t="n"/>
       <c r="BS11" s="5" t="inlineStr"/>
       <c r="BT11" s="5" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="BU11" s="5" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="BV11" s="5" t="inlineStr">
         <is>
-          <t>Greeting &amp; Identification</t>
+          <t>Greeting &amp; Identification, Qualifying</t>
         </is>
       </c>
       <c r="BW11" s="5" t="inlineStr">
         <is>
-          <t>Needs Discovery, Qualifying (BANT), Scheduling (if applicable), Setting Expectations, Close &amp; Confirmation</t>
+          <t>Needs Discovery, Objection Handling, Scheduling, Setting Expectations, Close &amp; Confirmation</t>
         </is>
       </c>
       <c r="BX11" s="5" t="inlineStr">
         <is>
-          <t>[high] After the caller asked about a free roof repair estimate and mentioned having a buyer report, the rep did not ask any questions about the roof problem (type of repair needed, severity, leaks, timeline) and moved quickly toward scheduling/availability. | Fix: Before quoting availability, ask 3–5 quick discovery questions to assess urgency and scope, then position the soonest option appropriately (or escalate if emergency).
-[high] The rep did not collect the caller’s name, phone number, email, or confirm the address; the call ended right after the rep shared the next available date. | Fix: Immediately capture name and callback number, then confirm service address before discussing dates. If the caller declines, still ask permission to text/email availability or add to a cancellation list.
-[high] When the caller objected to the availability (“nothing any sooner?”), the rep only said they were booked and did not offer alternatives (waitlist, cancellation call-back, different time windows, or any other option). | Fix: Acknowledge the concern, offer concrete alternatives (AM/PM windows, cancellation list, next-best date), and attempt to secure a tentative booking while offering to notify if something opens sooner.
-[medium] The rep did not set expectations for what the inspection/estimate includes (duration, what the customer receives, whether someone needs to be present, and next steps). | Fix: Briefly explain the inspection process, approximate duration, deliverables (written estimate), and what’s needed from the homeowner (access, presence).
-[high] The call ended without a clear close or next step (no attempt to book Monday, no follow-up plan, and no confirmation method). | Fix: Attempt to secure the appointment, summarize details, and confirm how they’ll receive confirmation (text/email). If they decline, ask permission to follow up and keep their info.</t>
+          <t>[high] When the customer indicated Monday was too late by saying 'Okay, nothing I need to do now', the rep agreed by saying 'No, unfortunately not' and ended the call without trying to save the lead. | Fix: Acknowledge the urgency and offer a potential alternative, such as a priority cancellation waitlist, to keep the customer engaged and capture their contact information.
+[high] The rep failed to ask for the caller's name and callback number during the Greeting &amp; Identification stage. | Fix: Always capture the caller's name and phone number immediately after the greeting and before answering their initial questions.
+[medium] The rep declined to review the buyer's report when the homeowner offered to send it over, insisting only on an inspection. | Fix: Accept any documentation the customer offers to send, as it provides valuable context for the sales and service teams to assess urgency and scope.</t>
         </is>
       </c>
       <c r="BY11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ11" s="5" t="inlineStr"/>
+      <c r="CA11" s="5" t="n">
+        <v>1484</v>
+      </c>
+      <c r="CB11" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="CC11" s="5" t="inlineStr">
+        <is>
+          <t>customer_rep, home_owner</t>
+        </is>
+      </c>
+      <c r="CD11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="BZ11" s="5" t="inlineStr">
-        <is>
-          <t>[Scheduling Conflicts] "okay um okay nothing any sooner?" (Unresolved, severity=medium)</t>
-        </is>
-      </c>
-      <c r="CA11" s="5" t="n">
-        <v>1617</v>
-      </c>
-      <c r="CB11" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="CC11" s="5" t="inlineStr">
-        <is>
-          <t>customer_rep, home_owner</t>
-        </is>
-      </c>
-      <c r="CD11" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="CE11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="CF11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CG11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="CH11" s="5" t="inlineStr">
         <is>
-          <t>[Medium] BANT Need: Score Delta — PROD=0.8 STAGING=0.5 delta=0.300 (threshold=0.2)
-[Medium] Qualification Status: Mismatch — PROD='hot' STAGING='warm'</t>
+          <t>[Medium] Objections Count: Missing in Staging — Present in PROD but missing/empty in STAGING</t>
         </is>
       </c>
       <c r="CI11" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="CJ11" s="5" t="n">
         <v>0.1</v>
       </c>
-      <c r="CJ11" s="5" t="n">
+      <c r="CK11" s="5" t="n">
         <v>0.05</v>
-      </c>
-      <c r="CK11" s="5" t="n">
-        <v>0.075</v>
       </c>
       <c r="CL11" s="5" t="inlineStr"/>
       <c r="CM11" s="8" t="inlineStr">
@@ -4086,7 +4191,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>scenario_test_1_88148c4c</t>
+          <t>gemini_cmp_11_b2e0d556</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -4094,7 +4199,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="n">
+        <v>276.1</v>
+      </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Tim called from Palm Creek Resort because he is in the process of possibly purchasing a small park model and believes the shingles need to be replaced; he wanted an estimate to understand the replacement cost. Nita confirmed the company services the area but explained that estimates are only free for current property owners, and that a $299 quotation fee applies when the property is still listed and the caller is the buyer. Tim expressed concern about paying the fee since he already paid an inspector, and the call ended with Nita suggesting he ask the current owner to cover or include the fee, with Tim saying he would talk to them and see what they can do.</t>
@@ -4235,38 +4342,35 @@
       </c>
       <c r="AS12" s="5" t="inlineStr">
         <is>
-          <t>Tim called from Palm Creek Resort because he is in the process of possibly purchasing a small park model and believes the shingles need to be replaced; he wanted an estimate to understand the replacement cost. Nita confirmed the company services the area but explained that estimates are only free for current property owners, and that a $299 quotation fee applies when the property is still listed and the caller is the buyer. Tim expressed concern about paying the fee since he already paid an inspector, and the call ended with Nita suggesting he ask the current owner to cover or include the fee, with Tim saying he would talk to them and see what they can do.</t>
+          <t>The caller is in the process of purchasing a park model home and requested an estimate to replace the shingles, as recommended by a home inspector. The representative explained that because the caller does not currently own the property, a $299 quotation fee applies, whereas estimates are free for current owners. The caller hesitated to pay the fee, stating they needed to think about it, and the representative suggested asking the current property owner to cover the cost.</t>
         </is>
       </c>
       <c r="AT12" s="5" t="inlineStr">
         <is>
-          <t>Caller (Tim) is considering purchasing a park model in Palm Creek Resort and thinks the shingles need to be redone/replaced.
-Rep stated the company services the area but charges a $299 quotation fee when the caller is not yet the owner and the property is still in listing; free estimates are for current owners.
-Tim did not schedule anything on the call and said he will talk to the current owner about possibly covering/including the quotation fee.</t>
+          <t>The caller is a potential buyer of a park model home seeking an estimate to replace the shingles.
+A home inspector previously checked the property and recommended the caller get a roof estimate.
+The company charges a $299 quotation fee for individuals who are purchasing a home, reserving free estimates for current owners.
+The caller declined to book immediately because they did not want to pay the $299 fee.
+The representative suggested the caller ask the current property owner to pay the fee as a gift for the house.</t>
         </is>
       </c>
       <c r="AU12" s="5" t="inlineStr"/>
       <c r="AV12" s="5" t="inlineStr">
         <is>
-          <t>Customer will speak with the current property owner about covering or including the $299 quotation fee.
-Customer may call back to proceed with a paid quotation or wait until ownership to request a free estimate.</t>
+          <t>The caller will think about the $299 fee and consider asking the current property owner to cover the cost of the estimate.</t>
         </is>
       </c>
       <c r="AW12" s="5" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="AX12" s="5" t="n">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="AY12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AZ12" s="5" t="inlineStr"/>
-      <c r="BA12" s="5" t="inlineStr">
-        <is>
-          <t>Tim</t>
-        </is>
-      </c>
+      <c r="BA12" s="5" t="n"/>
       <c r="BB12" s="5" t="inlineStr"/>
       <c r="BC12" s="5" t="inlineStr">
         <is>
@@ -4275,7 +4379,7 @@
       </c>
       <c r="BD12" s="5" t="inlineStr">
         <is>
-          <t>Roof shingle replacement estimate/quote</t>
+          <t>Shingle replacement estimate</t>
         </is>
       </c>
       <c r="BE12" s="5" t="inlineStr">
@@ -4311,7 +4415,7 @@
         </is>
       </c>
       <c r="BM12" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="BN12" s="5" t="n">
         <v>0.5</v>
@@ -4323,48 +4427,45 @@
         <v>0</v>
       </c>
       <c r="BQ12" s="5" t="n">
-        <v>0.45</v>
+        <v>0.325</v>
       </c>
       <c r="BR12" s="5" t="n"/>
       <c r="BS12" s="5" t="inlineStr"/>
       <c r="BT12" s="5" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="BU12" s="5" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="BV12" s="5" t="inlineStr">
         <is>
-          <t>Greeting</t>
+          <t>Qualifying, Setting Expectations</t>
         </is>
       </c>
       <c r="BW12" s="5" t="inlineStr">
         <is>
-          <t>Identification, Needs Discovery, Qualifying (BANT), Scheduling, Setting Expectations, Close &amp; Confirmation, Objection Handling</t>
+          <t>Greeting &amp; Identification, Needs Discovery, Objection Handling</t>
         </is>
       </c>
       <c r="BX12" s="5" t="inlineStr">
         <is>
-          <t>[high] After the caller explained they were considering purchasing a park model and suspected the shingles needed replacement, the rep moved directly to stating there is a $299 quotation fee without first gathering basic details (roof issue, urgency, property address, access, or what the customer needs the estimate for). | Fix: Use a short discovery sequence before discussing fees: confirm property type/location, what they’re seeing, whether there’s active leaking/damage, and what they need the estimate for (purchase decision vs repair). Then explain the fee with value framing tied to their goal.
-[high] When the caller objected to the $299 fee (“Oh goodness... I don't want to pay that”), the rep responded briefly (“All right.”) and did not explore the objection, offer options, or attempt to preserve the lead with a next step. | Fix: Acknowledge, probe, and present alternatives: ask what they need to decide, offer to coordinate with the seller/agent, propose scheduling a free estimate contingent on ownership/closing date, or provide a rough range with clear caveats and a follow-up plan.
-[medium] The rep did not complete identification and contact verification (did not confirm the caller’s name, phone number, email, or the exact property address) and did not set a follow-up action before ending the call. | Fix: Capture contact info early and set a follow-up commitment tied to the caller’s next action (talking to the owner). Offer to text/email the fee policy and what’s included, and schedule a callback time.
-[medium] The rep did not set expectations about what the paid quotation includes (inspection scope, deliverables, time on site, whether it’s credited toward work, or how it helps with a purchase decision). | Fix: Explain what happens during the visit, what the customer receives, and any crediting policy (if applicable). Tie it to the customer’s goal (purchase decision/negotiation).</t>
+          <t>[high] The rep skipped greeting, identification, and needs discovery, jumping straight into quoting a $299 fee when the customer asked if they service the area. | Fix: Start with a warm greeting, ask for their name, and ask a few questions about the roof to build value before explaining the real estate estimate policy.
+[high] When the customer objected to the $299 fee stating they had already paid an inspector and just wanted an estimate, the rep failed to build value for the fee and instead suggested the customer ask the current owner to pay for it. | Fix: Acknowledge the objection, explain the specific value of a paid real estate estimate, and frame it as a tool for their home purchase negotiation.</t>
         </is>
       </c>
       <c r="BY12" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BZ12" s="5" t="inlineStr">
         <is>
-          <t>[Service Fee Concerns] "Oh goodness. Hmm. Okay. Okay. Well, I'll have to think about that one because I, yeah, that's, that's, I don't want to pay that. I already paid a, I already paid an inspector to come check the place out, but." (Unresolved, severity=high)
-[In-Person Estimates Only] "Oh, you don't, it's not a free estimate?" (Unresolved, severity=medium)</t>
+          <t>[Service Fee Concerns] "Goodness. Hmm. Okay. Okay. Well, I will have to think about that one because I. Yeah, that's that's. I don't want to pay that. For sure. I already paid. I already paid an inspector to come check the place out, but. He suggested that we get a roof repair to get a good estimate or a good estimate until I. I'd like an estimate even to know what it's going to cost me to replace the shingles." (Unresolved, severity=high)</t>
         </is>
       </c>
       <c r="CA12" s="5" t="n">
-        <v>1992</v>
+        <v>1394</v>
       </c>
       <c r="CB12" s="5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="CC12" s="5" t="inlineStr">
         <is>
@@ -4372,26 +4473,30 @@
         </is>
       </c>
       <c r="CD12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="CF12" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CH12" s="5" t="inlineStr"/>
+      <c r="CH12" s="5" t="inlineStr">
+        <is>
+          <t>[Medium] BANT Budget: Score Delta — PROD=0.5 STAGING=0.0 delta=0.500 (threshold=0.2)</t>
+        </is>
+      </c>
       <c r="CI12" s="5" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="CJ12" s="5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="CK12" s="5" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="CL12" s="5" t="inlineStr"/>
       <c r="CM12" s="8" t="inlineStr">
@@ -4431,15 +4536,17 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>NOT SUBMITTED</t>
+          <t>gemini_cmp_12_d40a3a3c</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>17.4</v>
+      </c>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
       <c r="J13" s="5" t="inlineStr"/>
@@ -4477,43 +4584,143 @@
       <c r="AP13" s="5" t="inlineStr"/>
       <c r="AQ13" s="5" t="inlineStr"/>
       <c r="AR13" s="5" t="inlineStr"/>
-      <c r="AS13" s="5" t="inlineStr"/>
-      <c r="AT13" s="5" t="inlineStr"/>
+      <c r="AS13" s="5" t="inlineStr">
+        <is>
+          <t>Homeowner Chase Eatman called Arizona Roofers to request a roof repair because some tiles had fallen off his roof. He confirmed that there are no active leaks inside the home and that the roof is slightly over 10 years old. The representative collected property details, noting that the home is located in an HOA community in Surprise, AZ, and does not have solar panels. The call concluded with the representative successfully scheduling a service appointment for the upcoming Tuesday between 7:30 AM and 9:00 AM.</t>
+        </is>
+      </c>
+      <c r="AT13" s="5" t="inlineStr">
+        <is>
+          <t>Homeowner is calling for a roof repair because some tiles have fallen down.
+Customer confirmed there is no active water leaking inside the property.
+The roof is a little over 10 years old and does not have any solar panels installed.
+The property is located in an HOA community at 15227 West Bloomfield Road, Surprise, Arizona 85379.
+A service appointment was successfully scheduled for Tuesday between 7:30 AM and 9:00 AM.</t>
+        </is>
+      </c>
       <c r="AU13" s="5" t="inlineStr"/>
-      <c r="AV13" s="5" t="inlineStr"/>
-      <c r="AW13" s="5" t="inlineStr"/>
-      <c r="AX13" s="5" t="inlineStr"/>
-      <c r="AY13" s="5" t="inlineStr"/>
+      <c r="AV13" s="5" t="inlineStr">
+        <is>
+          <t>Arizona Roofers technician to visit the property on Tuesday between 7:30 AM and 9:00 AM for the scheduled service.</t>
+        </is>
+      </c>
+      <c r="AW13" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AX13" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AY13" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ13" s="5" t="inlineStr"/>
-      <c r="BA13" s="5" t="inlineStr"/>
+      <c r="BA13" s="5" t="inlineStr">
+        <is>
+          <t>Chase Eatmon</t>
+        </is>
+      </c>
       <c r="BB13" s="5" t="inlineStr"/>
-      <c r="BC13" s="5" t="inlineStr"/>
-      <c r="BD13" s="5" t="inlineStr"/>
-      <c r="BE13" s="5" t="inlineStr"/>
-      <c r="BF13" s="5" t="inlineStr"/>
-      <c r="BG13" s="5" t="inlineStr"/>
-      <c r="BH13" s="5" t="inlineStr"/>
-      <c r="BI13" s="5" t="inlineStr"/>
-      <c r="BJ13" s="5" t="inlineStr"/>
-      <c r="BK13" s="5" t="inlineStr"/>
-      <c r="BL13" s="5" t="inlineStr"/>
-      <c r="BM13" s="5" t="inlineStr"/>
-      <c r="BN13" s="5" t="inlineStr"/>
-      <c r="BO13" s="5" t="inlineStr"/>
-      <c r="BP13" s="5" t="inlineStr"/>
-      <c r="BQ13" s="5" t="inlineStr"/>
-      <c r="BR13" s="5" t="inlineStr"/>
+      <c r="BC13" s="5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="BD13" s="5" t="inlineStr">
+        <is>
+          <t>Roof repair</t>
+        </is>
+      </c>
+      <c r="BE13" s="5" t="inlineStr">
+        <is>
+          <t>booked</t>
+        </is>
+      </c>
+      <c r="BF13" s="5" t="inlineStr">
+        <is>
+          <t>new_inquiry</t>
+        </is>
+      </c>
+      <c r="BG13" s="5" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="BH13" s="5" t="inlineStr">
+        <is>
+          <t>qualified_and_booked</t>
+        </is>
+      </c>
+      <c r="BI13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ13" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-31T07:30:00</t>
+        </is>
+      </c>
+      <c r="BK13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL13" s="5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="BM13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO13" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BP13" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BQ13" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BR13" s="5" t="n"/>
       <c r="BS13" s="5" t="inlineStr"/>
-      <c r="BT13" s="5" t="inlineStr"/>
-      <c r="BU13" s="5" t="inlineStr"/>
-      <c r="BV13" s="5" t="inlineStr"/>
-      <c r="BW13" s="5" t="inlineStr"/>
-      <c r="BX13" s="5" t="inlineStr"/>
-      <c r="BY13" s="5" t="inlineStr"/>
+      <c r="BT13" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BU13" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BV13" s="5" t="inlineStr">
+        <is>
+          <t>Greeting &amp; Identification, Needs Discovery, Scheduling</t>
+        </is>
+      </c>
+      <c r="BW13" s="5" t="inlineStr">
+        <is>
+          <t>Qualifying, Setting Expectations, Close &amp; Confirmation</t>
+        </is>
+      </c>
+      <c r="BX13" s="5" t="inlineStr">
+        <is>
+          <t>[high] Rep severely misunderstood the property address, recording 'Bokaro Town Road Surat' and 'New South Wales' instead of 'Surprise, Arizona'. | Fix: If unfamiliar with the city name, ask the customer to spell it out. Maintain a list of local service areas to recognize standard cities.
+[medium] After asking how many stories the home has, the customer said 'Sorry' (indicating they didn't hear), and the rep just said 'Okay. Thank you.' and moved on without getting the answer. | Fix: Politely repeat the question to ensure the required data is collected.
+[high] Rep scheduled the appointment but failed to set expectations for what happens during the visit before abruptly ending the call. | Fix: Briefly explain the appointment process and confirm that the homeowner needs to be present before saying goodbye.</t>
+        </is>
+      </c>
+      <c r="BY13" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="BZ13" s="5" t="inlineStr"/>
-      <c r="CA13" s="5" t="inlineStr"/>
-      <c r="CB13" s="5" t="inlineStr"/>
-      <c r="CC13" s="5" t="inlineStr"/>
+      <c r="CA13" s="5" t="n">
+        <v>2682</v>
+      </c>
+      <c r="CB13" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="CC13" s="5" t="inlineStr">
+        <is>
+          <t>customer_rep, home_owner</t>
+        </is>
+      </c>
       <c r="CD13" s="5" t="n">
         <v>0</v>
       </c>
@@ -4531,14 +4738,14 @@
       <c r="CJ13" s="5" t="inlineStr"/>
       <c r="CK13" s="5" t="inlineStr"/>
       <c r="CL13" s="5" t="inlineStr"/>
-      <c r="CM13" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="CN13" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="CM13" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CN13" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="CO13" s="7" t="inlineStr">
@@ -4568,7 +4775,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>scenario_test_3_cc5d0fb9</t>
+          <t>gemini_cmp_13_96e7fdd6</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -4576,7 +4783,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="n">
+        <v>162.8</v>
+      </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
           <t>The homeowner called Arizona Rebirth to request a quote to repair/replace some missing roof tiles. The representative asked about the roof’s age (the homeowner was unsure), confirmed the caller is the property owner, and learned the home was purchased about five years ago. The homeowner said they were not experiencing other issues and only needed tiles replaced after receiving a message from “H-O-8” noting missing tiles. The representative explained that small tile repair jobs are currently out of Arizona Rebirth’s scope and referred the homeowner to a partner company, XRP, that specializes in smaller repairs; the homeowner agreed to look them up and call, and the call ended without an appointment being scheduled.</t>
@@ -4708,28 +4917,30 @@
       </c>
       <c r="AS14" s="5" t="inlineStr">
         <is>
-          <t>The homeowner called Arizona Rebirth to request a quote to repair/replace some missing roof tiles. The representative asked about the roof’s age (the homeowner was unsure), confirmed the caller is the property owner, and learned the home was purchased about five years ago. The homeowner said they were not experiencing other issues and only needed tiles replaced after receiving a message from “H-O-8” noting missing tiles. The representative explained that small tile repair jobs are currently out of Arizona Rebirth’s scope and referred the homeowner to a partner company, XRP, that specializes in smaller repairs; the homeowner agreed to look them up and call, and the call ended without an appointment being scheduled.</t>
+          <t>A homeowner called Arizona Roofers seeking a quote to replace missing roof tiles after receiving a message from their agent about the issue. The representative gathered basic information, confirming the caller was the property owner who purchased the home five years ago, and established there were no active issues other than the missing tiles. Because the repair was considered a small job and out of Arizona Roofers' current scope, the representative referred the customer to a different roofing company, XRP, that specializes in smaller repairs. The customer appreciated the recommendation and stated they would look up XRP.</t>
         </is>
       </c>
       <c r="AT14" s="5" t="inlineStr">
         <is>
-          <t>Homeowner requested a quote to repair/replace missing roof tiles.
-Caller confirmed they are the property owner and purchased the house about five years ago; they were unsure of the roof’s age.
-Arizona Rebirth stated small repair jobs are out of scope and referred the homeowner to a partner company named XRP for the repair.</t>
+          <t>The customer is the property owner and is calling to get a quote for replacing missing roof tiles.
+The owner purchased the home about five years ago but is unsure of the exact age of the roof.
+The missing tiles were brought to the customer's attention via a message from their agent today.
+The customer confirmed there are no other active issues with the roof besides the missing tiles.
+The requested repair was out of scope for Arizona Roofers due to its small size.
+The representative referred the customer to another company named XRP that specializes in smaller jobs and repairs.</t>
         </is>
       </c>
       <c r="AU14" s="5" t="inlineStr"/>
       <c r="AV14" s="5" t="inlineStr">
         <is>
-          <t>Homeowner to look up and contact XRP for a quote on replacing the missing roof tiles.
-No appointment scheduled with Arizona Rebirth due to the job being out of scope.</t>
+          <t>The customer will look up XRP and contact them to get a quote for the roof tile repair.</t>
         </is>
       </c>
       <c r="AW14" s="5" t="n">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="AX14" s="5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AY14" s="5" t="n">
         <v>0</v>
@@ -4739,12 +4950,12 @@
       <c r="BB14" s="5" t="inlineStr"/>
       <c r="BC14" s="5" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="BD14" s="5" t="inlineStr">
         <is>
-          <t>Roof tile repair/replacement (replace missing roof tiles; quote requested)</t>
+          <t>Replace missing roof tiles</t>
         </is>
       </c>
       <c r="BE14" s="5" t="inlineStr">
@@ -4754,7 +4965,7 @@
       </c>
       <c r="BF14" s="5" t="inlineStr">
         <is>
-          <t>quote_only</t>
+          <t>new_inquiry</t>
         </is>
       </c>
       <c r="BG14" s="5" t="inlineStr">
@@ -4789,35 +5000,32 @@
         <v>0.8</v>
       </c>
       <c r="BP14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ14" s="5" t="n">
-        <v>0.575</v>
+        <v>0.825</v>
       </c>
       <c r="BR14" s="5" t="n"/>
       <c r="BS14" s="5" t="inlineStr"/>
       <c r="BT14" s="5" t="n">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="BU14" s="5" t="n">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="BV14" s="5" t="inlineStr">
         <is>
-          <t>Greeting &amp; Identification, Understand the Need</t>
+          <t>Needs Discovery, Qualifying, Close &amp; Confirmation</t>
         </is>
       </c>
       <c r="BW14" s="5" t="inlineStr">
         <is>
-          <t>Educate on need for in-person assessment, Handle objections about inspection, Attempt to schedule (if appropriate), Close</t>
+          <t>Greeting &amp; Identification</t>
         </is>
       </c>
       <c r="BX14" s="5" t="inlineStr">
         <is>
-          <t>[high] After the customer asked for a quote on missing roof tiles, the rep quickly concluded the job was out of scope and referred the caller to another company without explaining pricing limitations or the need for an in-person assessment to provide an accurate quote. | Fix: Acknowledge the request, explain that roof repair pricing depends on on-site factors (tile type, underlayment, access, extent of damage), and offer an inspection/assessment if your company can handle it. If truly out of scope, still explain the assessment need and provide a warm handoff (offer to text the referral, confirm they can take the number, and invite them back if the scope is larger).
-[medium] The rep did not attempt to schedule an appointment or explore whether the situation could qualify for their services (e.g., inspection to confirm if there is underlying damage) before ending the call. | Fix: Before referring out, ask a few targeted questions to confirm scope and offer an inspection if there’s any chance it fits. If truly not a fit, still offer to help coordinate next steps and keep the door open for future work.
-[medium] The rep did not collect or verify the caller’s contact information (name, phone, address/email) at any point, even to support a referral or future follow-up. | Fix: Ask for the caller’s name and best callback number early, and confirm the property address if discussing service eligibility or scheduling/referral.
-[low] The close was abrupt and did not confirm the customer successfully received the referral information or offer to send it via text/email. | Fix: Confirm the referral details, offer to text/email the number, and invite the customer to call back if the scope changes or they need additional help.</t>
+          <t>[medium] After the customer stated they were looking for a quote on missing roof tiles, the rep moved straight into needs discovery without asking for the caller's name or verifying callback information. | Fix: Immediately after the customer explains their reason for calling, acknowledge their need and ask for their name and contact information before jumping into troubleshooting questions.</t>
         </is>
       </c>
       <c r="BY14" s="5" t="n">
@@ -4825,10 +5033,10 @@
       </c>
       <c r="BZ14" s="5" t="inlineStr"/>
       <c r="CA14" s="5" t="n">
-        <v>1295</v>
+        <v>1234</v>
       </c>
       <c r="CB14" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CC14" s="5" t="inlineStr">
         <is>
@@ -4836,26 +5044,35 @@
         </is>
       </c>
       <c r="CD14" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="CE14" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CF14" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CG14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CH14" s="5" t="inlineStr"/>
+      <c r="CH14" s="5" t="inlineStr">
+        <is>
+          <t>[High] Compliance Score: Score Delta — PROD=0.62 STAGING=0.8 delta=0.180 (threshold=0.15)
+[Medium] BANT Timeline: Score Delta — PROD=0.0 STAGING=1.0 delta=1.000 (threshold=0.2)
+[Medium] BANT Overall: Score Delta — PROD=0.575 STAGING=0.825 delta=0.250 (threshold=0.2)
+[Medium] Compliance Rate: Score Delta — PROD=0.62 STAGING=0.8 delta=0.180 (threshold=0.15)
+[High] Call Type: Mismatch — PROD='quote_only' STAGING='new_inquiry'
+[Medium] Qualification Status: Mismatch — PROD='warm' STAGING='hot'</t>
+        </is>
+      </c>
       <c r="CI14" s="5" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="CJ14" s="5" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="CK14" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="CL14" s="5" t="inlineStr"/>
       <c r="CM14" s="8" t="inlineStr">
@@ -4863,14 +5080,14 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="CN14" s="8" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="CO14" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="CN14" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CO14" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -4903,7 +5120,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="n">
+        <v>292.4</v>
+      </c>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="5" t="inlineStr"/>
@@ -5138,7 +5357,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>scenario_test_5_8b5c1e22</t>
+          <t>gemini_cmp_15_071d6575</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -5146,7 +5365,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="n">
+        <v>227.9</v>
+      </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Adam called Arizona Roofers to ask how much a square of a tiled roof costs. Bronte explained that she wasn’t sure and that the company usually does not provide pricing over the phone. Adam thanked her and ended the call without scheduling an inspection or estimate.</t>
@@ -5289,41 +5510,28 @@
       </c>
       <c r="AS16" s="5" t="inlineStr">
         <is>
-          <t>Adam called Arizona Roofers to ask how much a square of a tiled roof costs. Bronte explained that she wasn’t sure and that the company usually does not provide pricing over the phone. Adam thanked her and ended the call without scheduling an inspection or estimate.</t>
+          <t>A brief interaction where a caller named Adam contacted Arizona Roofers to inquire about the current cost of a square of a tile roof. The representative informed him that the company does not provide pricing estimates over the phone. Adam politely accepted the response and ended the call without booking an appointment or requesting an on-site estimate.</t>
         </is>
       </c>
       <c r="AT16" s="5" t="inlineStr">
         <is>
-          <t>Caller (Adam) asked for the current cost per square for a tiled roof.
-Rep (Bronte) stated she was not sure and that they usually don’t give prices over the phone.
-The call ended politely with no appointment, inspection, or follow-up scheduled.</t>
-        </is>
-      </c>
-      <c r="AU16" s="5" t="inlineStr">
-        <is>
-          <t>Provide pricing guidance to the customer for current cost per square of a tiled roof</t>
-        </is>
-      </c>
-      <c r="AV16" s="5" t="inlineStr">
-        <is>
-          <t>Customer would need to request an on-site estimate/inspection to receive pricing.
-If the customer calls back, collect property details and schedule an appointment.</t>
-        </is>
-      </c>
+          <t>The caller, Adam, specifically asked for the cost of a square of a tile roof.
+The representative declined to provide a cost, stating they usually do not give prices over the phone.
+The call ended without any contact information gathered or appointments scheduled.</t>
+        </is>
+      </c>
+      <c r="AU16" s="5" t="inlineStr"/>
+      <c r="AV16" s="5" t="inlineStr"/>
       <c r="AW16" s="5" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="AX16" s="5" t="n">
         <v>0.9</v>
       </c>
       <c r="AY16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ16" s="5" t="inlineStr">
-        <is>
-          <t>[send_info] Provide pricing guidance to the customer for current cost per square of a tiled roof (owner: customer_rep, due: None)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="5" t="inlineStr"/>
       <c r="BA16" s="5" t="inlineStr">
         <is>
           <t>Adam</t>
@@ -5337,7 +5545,7 @@
       </c>
       <c r="BD16" s="5" t="inlineStr">
         <is>
-          <t>Tiled roof pricing estimate (cost per square)</t>
+          <t>Tiled roof</t>
         </is>
       </c>
       <c r="BE16" s="5" t="inlineStr">
@@ -5365,7 +5573,7 @@
       </c>
       <c r="BJ16" s="5" t="n"/>
       <c r="BK16" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL16" s="5" t="inlineStr">
         <is>
@@ -5390,26 +5598,26 @@
       <c r="BR16" s="5" t="n"/>
       <c r="BS16" s="5" t="inlineStr"/>
       <c r="BT16" s="5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BU16" s="5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BV16" s="5" t="inlineStr">
         <is>
-          <t>Greeting &amp; Identification (partial: company + rep name)</t>
+          <t>Greeting &amp; Identification</t>
         </is>
       </c>
       <c r="BW16" s="5" t="inlineStr">
         <is>
-          <t>Greeting &amp; Identification (missing: capture/confirm caller info beyond name), Understand the Need, Educate on need for in-person assessment (WHY), Handle objections about inspection, Attempt to schedule (if appropriate), Close</t>
+          <t>Understand the Need, EDUCATE on need for in-person assessment, Attempt to schedule, Close</t>
         </is>
       </c>
       <c r="BX16" s="5" t="inlineStr">
         <is>
-          <t>[high] When the homeowner asked, "how much is a square of a tiled roof cost now?", the rep responded that they were not sure and that the company usually doesn't give prices over the phone, without providing any context or next step. | Fix: Acknowledge the question, explain that pricing depends on key factors, and clearly state why an on-site inspection is required to give an accurate quote. Then transition into scheduling an inspection/estimate.
-[high] After the customer accepted the no-phone-quote response and said, "Oh, okay. Thank you very much, then.", the rep did not attempt to save the call by asking discovery questions or offering to schedule an inspection. | Fix: Use a brief save: ask 1–2 qualifying questions and offer an inspection/estimate immediately, including availability options.
-[medium] The rep ended the call with an unclear/unprofessional closing: "Yeah, I'm a good one." | Fix: Use a clear, courteous close and offer a next step or contact option (e.g., call back if they want an estimate).</t>
+          <t>[high] When the customer asked for the cost of a square of tiled roof, the rep flatly stated they don't give prices over the phone without explaining why an inspection is needed. | Fix: Acknowledge the question, explain why an in-person assessment is required (e.g., roof pitch, underlayment condition), and pivot to offering a free inspection.
+[high] The rep did not ask any discovery questions to understand why the customer was asking for the price of a tile square. | Fix: Before addressing the pricing, ask qualifying questions to understand the scope and urgency of their roofing project.
+[high] The rep allowed the customer to end the call without making a single attempt to schedule an estimate or collect the caller's phone number. | Fix: Always attempt to book the appointment before letting the caller hang up.</t>
         </is>
       </c>
       <c r="BY16" s="5" t="n">
@@ -5417,7 +5625,7 @@
       </c>
       <c r="BZ16" s="5" t="inlineStr"/>
       <c r="CA16" s="5" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="CB16" s="5" t="n">
         <v>6</v>
@@ -5441,10 +5649,10 @@
       </c>
       <c r="CH16" s="5" t="inlineStr"/>
       <c r="CI16" s="5" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="CJ16" s="5" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="CK16" s="5" t="n">
         <v>0</v>
@@ -5487,15 +5695,17 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>NOT SUBMITTED</t>
+          <t>gemini_cmp_16_d37a1191</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1341.2</v>
+      </c>
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="5" t="inlineStr"/>
       <c r="J17" s="5" t="inlineStr"/>
@@ -5533,43 +5743,136 @@
       <c r="AP17" s="5" t="inlineStr"/>
       <c r="AQ17" s="5" t="inlineStr"/>
       <c r="AR17" s="5" t="inlineStr"/>
-      <c r="AS17" s="5" t="inlineStr"/>
-      <c r="AT17" s="5" t="inlineStr"/>
+      <c r="AS17" s="5" t="inlineStr">
+        <is>
+          <t>A home buyer called to schedule a roof inspection for a property they are currently purchasing in Gilbert, AZ. The representative quoted a $299 inspection fee since the caller does not yet own the home. When the customer requested an appointment for the following day, the representative explained they were fully booked for the week and that the earliest availability was the next Monday. The customer decided to consult with their realtor regarding the scheduling and stated they would call back.</t>
+        </is>
+      </c>
+      <c r="AT17" s="5" t="inlineStr">
+        <is>
+          <t>The customer is in the process of buying a home and requested a roof inspection.
+The service address is 6064 East Olive Avenue, Gilbert Arizona 85234.
+The representative quoted a $299 fee for the inspection because the caller is not the current property owner.
+The company has no availability for the current week, with the next opening on the following Monday.
+The customer did not book an appointment, choosing instead to consult their realtor about the timeline before committing.</t>
+        </is>
+      </c>
       <c r="AU17" s="5" t="inlineStr"/>
-      <c r="AV17" s="5" t="inlineStr"/>
-      <c r="AW17" s="5" t="inlineStr"/>
-      <c r="AX17" s="5" t="inlineStr"/>
-      <c r="AY17" s="5" t="inlineStr"/>
+      <c r="AV17" s="5" t="inlineStr">
+        <is>
+          <t>Customer will consult with their realtor regarding the inspection timeline and availability.
+Customer will call Arizona Roofers back if they decide to proceed with booking the appointment.</t>
+        </is>
+      </c>
+      <c r="AW17" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AX17" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AY17" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ17" s="5" t="inlineStr"/>
-      <c r="BA17" s="5" t="inlineStr"/>
+      <c r="BA17" s="5" t="n"/>
       <c r="BB17" s="5" t="inlineStr"/>
-      <c r="BC17" s="5" t="inlineStr"/>
-      <c r="BD17" s="5" t="inlineStr"/>
-      <c r="BE17" s="5" t="inlineStr"/>
-      <c r="BF17" s="5" t="inlineStr"/>
-      <c r="BG17" s="5" t="inlineStr"/>
-      <c r="BH17" s="5" t="inlineStr"/>
-      <c r="BI17" s="5" t="inlineStr"/>
-      <c r="BJ17" s="5" t="inlineStr"/>
-      <c r="BK17" s="5" t="inlineStr"/>
-      <c r="BL17" s="5" t="inlineStr"/>
-      <c r="BM17" s="5" t="inlineStr"/>
-      <c r="BN17" s="5" t="inlineStr"/>
-      <c r="BO17" s="5" t="inlineStr"/>
-      <c r="BP17" s="5" t="inlineStr"/>
-      <c r="BQ17" s="5" t="inlineStr"/>
-      <c r="BR17" s="5" t="inlineStr"/>
+      <c r="BC17" s="5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="BD17" s="5" t="inlineStr">
+        <is>
+          <t>Roof inspection</t>
+        </is>
+      </c>
+      <c r="BE17" s="5" t="inlineStr">
+        <is>
+          <t>not_booked</t>
+        </is>
+      </c>
+      <c r="BF17" s="5" t="inlineStr">
+        <is>
+          <t>new_inquiry</t>
+        </is>
+      </c>
+      <c r="BG17" s="5" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="BH17" s="5" t="inlineStr">
+        <is>
+          <t>qualified_but_unbooked</t>
+        </is>
+      </c>
+      <c r="BI17" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ17" s="5" t="n"/>
+      <c r="BK17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL17" s="5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="BM17" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN17" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BO17" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BP17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ17" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BR17" s="5" t="n"/>
       <c r="BS17" s="5" t="inlineStr"/>
-      <c r="BT17" s="5" t="inlineStr"/>
-      <c r="BU17" s="5" t="inlineStr"/>
-      <c r="BV17" s="5" t="inlineStr"/>
-      <c r="BW17" s="5" t="inlineStr"/>
-      <c r="BX17" s="5" t="inlineStr"/>
-      <c r="BY17" s="5" t="inlineStr"/>
+      <c r="BT17" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BU17" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BV17" s="5" t="inlineStr">
+        <is>
+          <t>Needs Discovery, Scheduling</t>
+        </is>
+      </c>
+      <c r="BW17" s="5" t="inlineStr">
+        <is>
+          <t>Greeting &amp; Identification, Qualifying, Setting Expectations, Objection Handling, Close &amp; Confirmation</t>
+        </is>
+      </c>
+      <c r="BX17" s="5" t="inlineStr">
+        <is>
+          <t>[high] During the greeting and throughout the entire call, the rep failed to ask for the caller's name or best callback phone number. | Fix: Always capture the caller's name and callback number immediately at the start of the call, or right after they state their initial need.
+[high] When the customer objected to the Monday availability and said 'Let me check and I'll get back to you', the rep immediately ended the call without attempting to save the deal. | Fix: Offer to pencil them in for the available slot to secure it while they check with their realtor, so they don't lose the spot.
+[medium] The rep learned the customer was buying a home but moved directly to quoting the fee without asking when the inspection period ends. | Fix: Ask about the real estate transaction timeline to properly qualify the prospect's needs.</t>
+        </is>
+      </c>
+      <c r="BY17" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="BZ17" s="5" t="inlineStr"/>
-      <c r="CA17" s="5" t="inlineStr"/>
-      <c r="CB17" s="5" t="inlineStr"/>
-      <c r="CC17" s="5" t="inlineStr"/>
+      <c r="CA17" s="5" t="n">
+        <v>1383</v>
+      </c>
+      <c r="CB17" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="CC17" s="5" t="inlineStr">
+        <is>
+          <t>customer_rep, home_owner</t>
+        </is>
+      </c>
       <c r="CD17" s="5" t="n">
         <v>0</v>
       </c>
@@ -5587,14 +5890,14 @@
       <c r="CJ17" s="5" t="inlineStr"/>
       <c r="CK17" s="5" t="inlineStr"/>
       <c r="CL17" s="5" t="inlineStr"/>
-      <c r="CM17" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="CN17" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="CM17" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CN17" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="CO17" s="7" t="inlineStr">
@@ -5624,15 +5927,17 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>scenario_test_7_b228486b</t>
+          <t>gemini_cmp_17_37b9a902</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>694.7</v>
+      </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Miranda called Arizona Roofers seeking to set up an independent roof inspection and estimate after storm damage from almost two years ago and ongoing issues following work arranged through Accuserve with USAA, including having skylights replaced twice. Travis gathered the property address (17128 W Calle Carmela, AZ 85653) and learned the roof was replaced last May. After checking service availability, Travis explained the location is outside their service area and offered a referral; Miranda agreed, and Travis provided Jonathan at XRP Roofing’s phone number for her to contact.</t>
@@ -5775,41 +6080,34 @@
       </c>
       <c r="AS18" s="5" t="inlineStr">
         <is>
-          <t>Miranda called Arizona Roofers seeking to set up an independent roof inspection and estimate after storm damage from almost two years ago and ongoing issues following work arranged through Accuserve with USAA, including having skylights replaced twice. Travis gathered the property address (17128 W Calle Carmela, AZ 85653) and learned the roof was replaced last May. After checking service availability, Travis explained the location is outside their service area and offered a referral; Miranda agreed, and Travis provided Jonathan at XRP Roofing’s phone number for her to contact.</t>
+          <t>Miranda called Arizona Roofers to request an independent roof inspection and estimate. Her roof was replaced less than a year ago after storm damage, but she has experienced ongoing issues and has had to replace her skylights twice since then. Her insurance intermediary, AccuServe, authorized her to find her own contractor. The representative, Travis, determined that her property in Marana, Arizona, is outside their service area. He apologized for her situation and referred her to Jonathan at XRP Roofing, providing his direct contact information, which Miranda accepted.</t>
         </is>
       </c>
       <c r="AT18" s="5" t="inlineStr">
         <is>
-          <t>Customer (Miranda) requested an inspection and estimate from a contractor of her choice after prior storm-damage work coordinated through Accuserve/USAA and repeated skylight replacements (twice).
-Property address provided: 17128 W Calle Carmela, AZ 85653; roof was changed out last May (less than a year old per caller).
-Arizona Roofers does not service the customer’s area, so the rep referred her to Jonathan at XRP Roofing (600-283-3761).</t>
-        </is>
-      </c>
-      <c r="AU18" s="5" t="inlineStr">
-        <is>
-          <t>Provide customer Miranda with referral contact details for Jonathan at XRP Roofing</t>
-        </is>
-      </c>
+          <t>Miranda is seeking an independent inspection and estimate for a roof that was replaced less than a year ago after storm damage.
+The homeowner has had to replace the property's skylights twice since the initial work was completed through AccuServe and USAA.
+The property is located in Marana, Arizona (zip code 85653).
+Arizona Roofers cannot take the job because the property is outside of their service area.
+The representative referred the customer to Jonathan at XRP Roofing and provided his phone number (602-833-7761).</t>
+        </is>
+      </c>
+      <c r="AU18" s="5" t="inlineStr"/>
       <c r="AV18" s="5" t="inlineStr">
         <is>
-          <t>Customer to call Jonathan at XRP Roofing (600-283-3761) to request an inspection/estimate.
-No further steps with Arizona Roofers were scheduled because the address is outside their service area.</t>
+          <t>Miranda will contact Jonathan at XRP Roofing to arrange for an inspection and estimate.</t>
         </is>
       </c>
       <c r="AW18" s="5" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="AX18" s="5" t="n">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="AY18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ18" s="5" t="inlineStr">
-        <is>
-          <t>[send_details] Provide customer Miranda with referral contact details for Jonathan at XRP Roofing (owner: customer_rep, due: None)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AZ18" s="5" t="inlineStr"/>
       <c r="BA18" s="5" t="inlineStr">
         <is>
           <t>Miranda</t>
@@ -5823,7 +6121,7 @@
       </c>
       <c r="BD18" s="5" t="inlineStr">
         <is>
-          <t>Roof/skylight inspection and estimate for storm damage/issues after recent roof replacement</t>
+          <t>Roof inspection and estimate</t>
         </is>
       </c>
       <c r="BE18" s="5" t="inlineStr">
@@ -5833,7 +6131,7 @@
       </c>
       <c r="BF18" s="5" t="inlineStr">
         <is>
-          <t>service_call</t>
+          <t>new_inquiry</t>
         </is>
       </c>
       <c r="BG18" s="5" t="inlineStr">
@@ -5876,26 +6174,25 @@
       <c r="BR18" s="5" t="n"/>
       <c r="BS18" s="5" t="inlineStr"/>
       <c r="BT18" s="5" t="n">
-        <v>0.72</v>
+        <v>0.85</v>
       </c>
       <c r="BU18" s="5" t="n">
-        <v>0.72</v>
+        <v>0.85</v>
       </c>
       <c r="BV18" s="5" t="inlineStr">
         <is>
-          <t>Greeting &amp; Identification, Understand the Issue, Empathy &amp; Acknowledgment, Propose Solution/Next Steps, Close</t>
+          <t>Greeting &amp; Identification, Needs Discovery, Close &amp; Confirmation</t>
         </is>
       </c>
       <c r="BW18" s="5" t="inlineStr">
         <is>
-          <t>Set Expectations</t>
+          <t>Contact Information Verification</t>
         </is>
       </c>
       <c r="BX18" s="5" t="inlineStr">
         <is>
-          <t>[high] After the customer provided an address that was confusing/inconsistent, the rep moved forward and then concluded the location was out of the service area without fully confirming the complete address (street, city, ZIP) or a callback number/email. | Fix: Use a structured address confirmation and capture best callback number before making a serviceability decision. Repeat the full address back and confirm city/ZIP, then confirm phone/email for follow-up.
-[medium] When providing the referral, the rep gave only a name and phone number and ended the call without setting expectations (what to say, what services to request, expected response time, or whether Arizona Roofers will follow up). | Fix: Set clear referral expectations: who the referral is, what to ask for (inspection/estimate for skylight/roof issues), what information to share (USAA/Accuserve context), and offer a follow-up plan.
-[low] The rep used negative/unprofessional phrasing while empathizing, which can come across as careless or inflammatory. | Fix: Keep empathy professional and customer-centered; acknowledge frustration without using derogatory terms.</t>
+          <t>[medium] After getting the customer's name at the start of the call, the rep immediately jumped into needs discovery without verifying a callback phone number. | Fix: Immediately after getting the caller's name, verify their phone number just in case the call disconnects.
+[medium] The rep addressed the customer as 'Brenda' instead of 'Miranda' when asking about the age of the roof. | Fix: Write the customer's name down immediately when they state it during the greeting, and reference your notes before using their name again.</t>
         </is>
       </c>
       <c r="BY18" s="5" t="n">
@@ -5903,10 +6200,10 @@
       </c>
       <c r="BZ18" s="5" t="inlineStr"/>
       <c r="CA18" s="5" t="n">
-        <v>1993</v>
+        <v>1943</v>
       </c>
       <c r="CB18" s="5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="CC18" s="5" t="inlineStr">
         <is>
@@ -5914,10 +6211,10 @@
         </is>
       </c>
       <c r="CD18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF18" s="5" t="n">
         <v>0</v>
@@ -5925,12 +6222,16 @@
       <c r="CG18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CH18" s="5" t="inlineStr"/>
+      <c r="CH18" s="5" t="inlineStr">
+        <is>
+          <t>[High] Call Type: Mismatch — PROD='service_call' STAGING='new_inquiry'</t>
+        </is>
+      </c>
       <c r="CI18" s="5" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="CJ18" s="5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="CK18" s="5" t="n">
         <v>0</v>
@@ -5941,14 +6242,14 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="CN18" s="8" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="CO18" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="CN18" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CO18" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -5973,15 +6274,17 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>NOT SUBMITTED</t>
+          <t>gemini_cmp_18_cba4ea9d</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>600.3</v>
+      </c>
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="5" t="inlineStr"/>
@@ -6019,43 +6322,147 @@
       <c r="AP19" s="5" t="inlineStr"/>
       <c r="AQ19" s="5" t="inlineStr"/>
       <c r="AR19" s="5" t="inlineStr"/>
-      <c r="AS19" s="5" t="inlineStr"/>
-      <c r="AT19" s="5" t="inlineStr"/>
-      <c r="AU19" s="5" t="inlineStr"/>
-      <c r="AV19" s="5" t="inlineStr"/>
-      <c r="AW19" s="5" t="inlineStr"/>
-      <c r="AX19" s="5" t="inlineStr"/>
-      <c r="AY19" s="5" t="inlineStr"/>
-      <c r="AZ19" s="5" t="inlineStr"/>
-      <c r="BA19" s="5" t="inlineStr"/>
+      <c r="AS19" s="5" t="inlineStr">
+        <is>
+          <t>Miles called Lyons Roofing to ask about a porch roof repair at his residence in South Tempe, specifically regarding the wood structure and fascia beneath the roof tiles. He repeatedly requested to speak directly with a technician or estimator to ensure they handle small structural repairs. The representative, Jackie, confirmed with a technician that they do perform this type of work and offered to schedule an estimate for the following day. However, Miles declined to provide his full information to create an account and opted not to schedule immediately, stating he needed to consult someone else first and would call back.</t>
+        </is>
+      </c>
+      <c r="AT19" s="5" t="inlineStr">
+        <is>
+          <t>The customer, Miles, needs repair work on the wood structure and fascia beneath the tiles of a porch roof at a residence in South Tempe.
+The customer preferred to speak directly with a technician or estimator before committing to scheduling an appointment.
+The representative confirmed the company can handle the repair and offered estimate availability for tomorrow (2026-03-27).
+The customer verified that technicians arrive with ladders in marked Lyons Roofing vehicles.
+The customer declined to create an account or schedule the estimate, deciding to consult with another party first before calling back.</t>
+        </is>
+      </c>
+      <c r="AU19" s="5" t="inlineStr">
+        <is>
+          <t>Follow up with Miles to schedule the porch roof/fascia estimate after he consults with the other decision maker</t>
+        </is>
+      </c>
+      <c r="AV19" s="5" t="inlineStr">
+        <is>
+          <t>Miles will consult with another individual regarding the porch roof repair.
+Miles will call Lyons Roofing back to create an account and schedule an estimate if he decides to proceed.</t>
+        </is>
+      </c>
+      <c r="AW19" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX19" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AY19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ19" s="5" t="inlineStr">
+        <is>
+          <t>[follow_up_call] Follow up with Miles to schedule the porch roof/fascia estimate after he consults with the other decision maker (owner: customer_rep, due: None)</t>
+        </is>
+      </c>
+      <c r="BA19" s="5" t="inlineStr">
+        <is>
+          <t>Miles</t>
+        </is>
+      </c>
       <c r="BB19" s="5" t="inlineStr"/>
-      <c r="BC19" s="5" t="inlineStr"/>
-      <c r="BD19" s="5" t="inlineStr"/>
-      <c r="BE19" s="5" t="inlineStr"/>
-      <c r="BF19" s="5" t="inlineStr"/>
-      <c r="BG19" s="5" t="inlineStr"/>
-      <c r="BH19" s="5" t="inlineStr"/>
-      <c r="BI19" s="5" t="inlineStr"/>
-      <c r="BJ19" s="5" t="inlineStr"/>
-      <c r="BK19" s="5" t="inlineStr"/>
-      <c r="BL19" s="5" t="inlineStr"/>
-      <c r="BM19" s="5" t="inlineStr"/>
-      <c r="BN19" s="5" t="inlineStr"/>
-      <c r="BO19" s="5" t="inlineStr"/>
-      <c r="BP19" s="5" t="inlineStr"/>
-      <c r="BQ19" s="5" t="inlineStr"/>
-      <c r="BR19" s="5" t="inlineStr"/>
+      <c r="BC19" s="5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="BD19" s="5" t="inlineStr">
+        <is>
+          <t>Porch roof structural repair</t>
+        </is>
+      </c>
+      <c r="BE19" s="5" t="inlineStr">
+        <is>
+          <t>not_booked</t>
+        </is>
+      </c>
+      <c r="BF19" s="5" t="inlineStr">
+        <is>
+          <t>new_inquiry</t>
+        </is>
+      </c>
+      <c r="BG19" s="5" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="BH19" s="5" t="inlineStr">
+        <is>
+          <t>qualified_but_unbooked</t>
+        </is>
+      </c>
+      <c r="BI19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ19" s="5" t="n"/>
+      <c r="BK19" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL19" s="5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="BM19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN19" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BO19" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BP19" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BQ19" s="5" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="BR19" s="5" t="n"/>
       <c r="BS19" s="5" t="inlineStr"/>
-      <c r="BT19" s="5" t="inlineStr"/>
-      <c r="BU19" s="5" t="inlineStr"/>
-      <c r="BV19" s="5" t="inlineStr"/>
-      <c r="BW19" s="5" t="inlineStr"/>
-      <c r="BX19" s="5" t="inlineStr"/>
-      <c r="BY19" s="5" t="inlineStr"/>
+      <c r="BT19" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BU19" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BV19" s="5" t="inlineStr">
+        <is>
+          <t>Greeting &amp; Identification, Needs Discovery, Scheduling, Setting Expectations</t>
+        </is>
+      </c>
+      <c r="BW19" s="5" t="inlineStr">
+        <is>
+          <t>Qualifying, Objection Handling, Close &amp; Confirmation</t>
+        </is>
+      </c>
+      <c r="BX19" s="5" t="inlineStr">
+        <is>
+          <t>[high] When the customer stated 'Let me call you back once I've consulted someone else', the rep responded with 'Alrighty' and let the call end without attempting to overcome the hesitation. | Fix: Acknowledge the customer's need to consult, but propose securing a tentative appointment slot to prevent them from losing their place in the schedule.
+[medium] During the Needs Discovery phase, the rep did not ask any qualifying questions about the timeline of the issue or whether there were active leaks. | Fix: Ask probing questions about the current state of the damage to build urgency and better qualify the lead before moving to scheduling.</t>
+        </is>
+      </c>
+      <c r="BY19" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="BZ19" s="5" t="inlineStr"/>
-      <c r="CA19" s="5" t="inlineStr"/>
-      <c r="CB19" s="5" t="inlineStr"/>
-      <c r="CC19" s="5" t="inlineStr"/>
+      <c r="CA19" s="5" t="n">
+        <v>3576</v>
+      </c>
+      <c r="CB19" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="CC19" s="5" t="inlineStr">
+        <is>
+          <t>customer_rep, home_owner</t>
+        </is>
+      </c>
       <c r="CD19" s="5" t="n">
         <v>0</v>
       </c>
@@ -6073,14 +6480,14 @@
       <c r="CJ19" s="5" t="inlineStr"/>
       <c r="CK19" s="5" t="inlineStr"/>
       <c r="CL19" s="5" t="inlineStr"/>
-      <c r="CM19" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="CN19" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="CM19" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CN19" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="CO19" s="7" t="inlineStr">
@@ -6110,15 +6517,17 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>scenario_test_9_e37ecbc8</t>
+          <t>gemini_cmp_19_dfa99492</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>614.6</v>
+      </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
           <t>The homeowner called to confirm whether this roofing company had performed an inspection at their property the prior week and to request the results, since they had not received any follow-up information. The customer service representative confirmed an inspection was completed on Tuesday, 2026-03-03, noted that London was the person who conducted it, and explained London was not in the office on the call date (2026-03-13). The representative committed to texting London and tagging him in the customer’s file so he can call the homeowner back and provide the inspection information, confirming the file is for Jagger before ending the call.</t>
@@ -6265,40 +6674,41 @@
       </c>
       <c r="AS20" s="5" t="inlineStr">
         <is>
-          <t>The homeowner called to confirm whether this roofing company had performed an inspection at their property the prior week and to request the results, since they had not received any follow-up information. The customer service representative confirmed an inspection was completed on Tuesday, 2026-03-03, noted that London was the person who conducted it, and explained London was not in the office on the call date (2026-03-13). The representative committed to texting London and tagging him in the customer’s file so he can call the homeowner back and provide the inspection information, confirming the file is for Jagger before ending the call.</t>
+          <t>Customer Jagger called to verify if the company performed a recent roof inspection at his property. The representative confirmed that a technician named London completed the inspection on March 3rd. Jagger stated he had not yet received the inspection results. The representative explained London is out of the office today (2026-03-26) but committed to texting him and tagging him in the system file so London can follow up and provide the missing information.</t>
         </is>
       </c>
       <c r="AT20" s="5" t="inlineStr">
         <is>
-          <t>Customer asked the company to look up whether they performed a roof inspection last week and requested the inspection information because they had not received anything back yet.
-Rep confirmed an inspection was completed on Tuesday, 2026-03-03, and that London was the inspector.
-Rep said London is not in the office on 2026-03-13 and will text him and tag him in the file so he can call the customer back; the account/file is for Jagger.</t>
+          <t>Customer Jagger called to confirm the identity of the roofing company that performed his recent inspection.
+The representative verified that a technician named London completed the roof inspection on Tuesday, March 3rd.
+Jagger stated he has not yet received any information or report following the inspection.
+London is out of the office today, but the representative will reach out to him to ensure the report is sent or a callback is made.</t>
         </is>
       </c>
       <c r="AU20" s="5" t="inlineStr">
         <is>
-          <t>Customer rep to text London and tag him in the customer file so he follows up with the customer about the 2026-03-03 inspection results.
-Contact London today and tag him in the customer file to ensure he calls the customer back about the prior inspection and next steps</t>
+          <t>London to contact Jagger to provide the missing inspection results from the March 3rd appointment.
+Send a text message to technician London and tag him in Jagger's file</t>
         </is>
       </c>
       <c r="AV20" s="5" t="inlineStr">
         <is>
-          <t>London to call the customer to review the inspection findings and provide the missing follow-up information.
-Customer to await London’s callback for the inspection details.</t>
+          <t>Representative to send a text message to London and update Jagger's file regarding the missing report.
+London to call Jagger back or send the pending inspection information.</t>
         </is>
       </c>
       <c r="AW20" s="5" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="AX20" s="5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AY20" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AZ20" s="5" t="inlineStr">
         <is>
-          <t>[follow_up_call] Contact London today and tag him in the customer file to ensure he calls the customer back about the prior inspection and next steps (owner: customer_rep, due: 2026-03-13T23:59:59Z)</t>
+          <t>[custom] Send a text message to technician London and tag him in Jagger's file (owner: customer_rep, due: None)</t>
         </is>
       </c>
       <c r="BA20" s="5" t="inlineStr">
@@ -6309,12 +6719,12 @@
       <c r="BB20" s="5" t="inlineStr"/>
       <c r="BC20" s="5" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>cold</t>
         </is>
       </c>
       <c r="BD20" s="5" t="inlineStr">
         <is>
-          <t>Roof inspection</t>
+          <t>Roof inspection results</t>
         </is>
       </c>
       <c r="BE20" s="5" t="inlineStr">
@@ -6356,36 +6766,35 @@
         <v>1</v>
       </c>
       <c r="BO20" s="5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="BP20" s="5" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="BQ20" s="5" t="n">
-        <v>0.575</v>
+        <v>0.45</v>
       </c>
       <c r="BR20" s="5" t="n"/>
       <c r="BS20" s="5" t="inlineStr"/>
       <c r="BT20" s="5" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="BU20" s="5" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="BV20" s="5" t="inlineStr">
         <is>
-          <t>Greeting &amp; Identification, Confirm Project Details, Address Questions/Concerns, Close Professionally</t>
+          <t>Confirm Project Details, Set Expectations for Next Steps, Address Questions/Concerns, Close Professionally</t>
         </is>
       </c>
       <c r="BW20" s="5" t="inlineStr">
         <is>
-          <t>Set Expectations for Next Steps</t>
+          <t>Greeting &amp; Identification</t>
         </is>
       </c>
       <c r="BX20" s="5" t="inlineStr">
         <is>
-          <t>[medium] After the homeowner said they had not received any information from the inspection, the rep said they would text London and tag the file, but did not set a timeframe or explain what the customer should expect next (callback vs. email, and by when). | Fix: When committing to follow up, give a specific timeframe, the communication channel, and a contingency plan if the customer doesn’t hear back. Confirm the best callback number/email to ensure the update reaches them.
-[low] The call opened with a generic question and did not include the company name or a structured identification step; the rep also did not proactively verify contact information before ending the call. | Fix: Start with company + name, then confirm the caller’s name and best callback number/email early in the call, especially on follow-ups where the purpose is status and coordination.</t>
+          <t>[medium] The rep answered the phone by simply saying 'Hello.' without stating the company name or introducing themselves. | Fix: Always answer inbound calls with a standard, branded greeting that clearly identifies the company and yourself.</t>
         </is>
       </c>
       <c r="BY20" s="5" t="n">
@@ -6393,14 +6802,14 @@
       </c>
       <c r="BZ20" s="5" t="inlineStr">
         <is>
-          <t>[Inefficient Agent Communication] "I haven't received any information back from that as of yet." (Resolved, severity=low)</t>
+          <t>[Inefficient Agent Communication] "I was wondering I haven't gotten I haven't received any information back from that as of yet" (Resolved, severity=low)</t>
         </is>
       </c>
       <c r="CA20" s="5" t="n">
-        <v>1402</v>
+        <v>1128</v>
       </c>
       <c r="CB20" s="5" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="CC20" s="5" t="inlineStr">
         <is>
@@ -6408,26 +6817,32 @@
         </is>
       </c>
       <c r="CD20" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CE20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="CF20" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CG20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CH20" s="5" t="inlineStr"/>
+      <c r="CH20" s="5" t="inlineStr">
+        <is>
+          <t>[Medium] BANT Need: Score Delta — PROD=0.5 STAGING=0.8 delta=0.300 (threshold=0.2)
+[Medium] BANT Timeline: Score Delta — PROD=0.8 STAGING=0.0 delta=0.800 (threshold=0.2)
+[Medium] Qualification Status: Mismatch — PROD='warm' STAGING='cold'</t>
+        </is>
+      </c>
       <c r="CI20" s="5" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="CJ20" s="5" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="CK20" s="5" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="CL20" s="5" t="inlineStr"/>
       <c r="CM20" s="8" t="inlineStr">
@@ -6440,9 +6855,9 @@
           <t>MATCH</t>
         </is>
       </c>
-      <c r="CO20" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="CO20" s="9" t="inlineStr">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
     </row>
@@ -6467,15 +6882,17 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>NOT SUBMITTED</t>
+          <t>gemini_cmp_20_c3d162d8</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>614.3</v>
+      </c>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="5" t="inlineStr"/>
@@ -6513,43 +6930,148 @@
       <c r="AP21" s="5" t="inlineStr"/>
       <c r="AQ21" s="5" t="inlineStr"/>
       <c r="AR21" s="5" t="inlineStr"/>
-      <c r="AS21" s="5" t="inlineStr"/>
-      <c r="AT21" s="5" t="inlineStr"/>
-      <c r="AU21" s="5" t="inlineStr"/>
-      <c r="AV21" s="5" t="inlineStr"/>
-      <c r="AW21" s="5" t="inlineStr"/>
-      <c r="AX21" s="5" t="inlineStr"/>
-      <c r="AY21" s="5" t="inlineStr"/>
-      <c r="AZ21" s="5" t="inlineStr"/>
-      <c r="BA21" s="5" t="inlineStr"/>
+      <c r="AS21" s="5" t="inlineStr">
+        <is>
+          <t>The homeowner called to address an unexpected appointment confirmation he received for today between 11:30 and 12:30 in Tucson, noting he had been coordinating directly with a team member named Rich and hadn't agreed to that time. The homeowner explained that Rich had suggested an appointment for tomorrow, but the homeowner is leaving town tomorrow and will be unavailable until the end of the month. The homeowner clarified that he is actually available for the unexpected 11:30-12:30 time slot today if Rich can make it. The representative, Jeeva, could not see the event on the calendar and suspected a system glitch. Both agreed to reach out to Rich directly to confirm his availability for today; if Rich is unavailable, the homeowner will introduce him to a backup contact to handle the appointment.</t>
+        </is>
+      </c>
+      <c r="AT21" s="5" t="inlineStr">
+        <is>
+          <t>The homeowner received an uncoordinated appointment confirmation for today (2026-03-26) between 11:30 and 12:30 at a property in Tucson.
+The homeowner is leaving town tomorrow (2026-03-27) and will be unavailable until the end of the month.
+The homeowner is available for the unexpected 11:30-12:30 time slot today if the technician, Rich, is able to attend.
+If Rich cannot make it today, the homeowner will connect him with a backup person who can coordinate the appointment in his absence.
+The representative could not see the appointment on the calendar and suspected the confirmation was a system glitch.</t>
+        </is>
+      </c>
+      <c r="AU21" s="5" t="inlineStr">
+        <is>
+          <t>Jeeva must contact Rich immediately to confirm if he can attend the 11:30-12:30 appointment today before the homeowner leaves town.
+Contact technician Rich to address the appointment glitch, ensure he does not travel to the property unnecessarily, and inform him of the customer's availability today.</t>
+        </is>
+      </c>
+      <c r="AV21" s="5" t="inlineStr">
+        <is>
+          <t>Jeeva will contact Rich to inform him of the homeowner's availability for today between 11:30 and 12:30.
+The homeowner will text Rich directly to offer today's time slot.
+The homeowner will connect Rich with his backup contact if Rich is unavailable today.</t>
+        </is>
+      </c>
+      <c r="AW21" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX21" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AY21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ21" s="5" t="inlineStr">
+        <is>
+          <t>[verify_details] Contact technician Rich to address the appointment glitch, ensure he does not travel to the property unnecessarily, and inform him of the customer's availability today. (owner: customer_rep, due: 2026-03-26T23:59:59)</t>
+        </is>
+      </c>
+      <c r="BA21" s="5" t="inlineStr">
+        <is>
+          <t>Doraemon</t>
+        </is>
+      </c>
       <c r="BB21" s="5" t="inlineStr"/>
-      <c r="BC21" s="5" t="inlineStr"/>
-      <c r="BD21" s="5" t="inlineStr"/>
-      <c r="BE21" s="5" t="inlineStr"/>
-      <c r="BF21" s="5" t="inlineStr"/>
-      <c r="BG21" s="5" t="inlineStr"/>
-      <c r="BH21" s="5" t="inlineStr"/>
-      <c r="BI21" s="5" t="inlineStr"/>
-      <c r="BJ21" s="5" t="inlineStr"/>
-      <c r="BK21" s="5" t="inlineStr"/>
-      <c r="BL21" s="5" t="inlineStr"/>
-      <c r="BM21" s="5" t="inlineStr"/>
-      <c r="BN21" s="5" t="inlineStr"/>
-      <c r="BO21" s="5" t="inlineStr"/>
-      <c r="BP21" s="5" t="inlineStr"/>
-      <c r="BQ21" s="5" t="inlineStr"/>
-      <c r="BR21" s="5" t="inlineStr"/>
+      <c r="BC21" s="5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="BD21" s="5" t="n"/>
+      <c r="BE21" s="5" t="inlineStr">
+        <is>
+          <t>not_booked</t>
+        </is>
+      </c>
+      <c r="BF21" s="5" t="inlineStr">
+        <is>
+          <t>confirmation</t>
+        </is>
+      </c>
+      <c r="BG21" s="5" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="BH21" s="5" t="inlineStr">
+        <is>
+          <t>qualified_but_unbooked</t>
+        </is>
+      </c>
+      <c r="BI21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ21" s="5" t="n"/>
+      <c r="BK21" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL21" s="5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="BM21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO21" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BP21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ21" s="5" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="BR21" s="5" t="n"/>
       <c r="BS21" s="5" t="inlineStr"/>
-      <c r="BT21" s="5" t="inlineStr"/>
-      <c r="BU21" s="5" t="inlineStr"/>
-      <c r="BV21" s="5" t="inlineStr"/>
-      <c r="BW21" s="5" t="inlineStr"/>
-      <c r="BX21" s="5" t="inlineStr"/>
-      <c r="BY21" s="5" t="inlineStr"/>
-      <c r="BZ21" s="5" t="inlineStr"/>
-      <c r="CA21" s="5" t="inlineStr"/>
-      <c r="CB21" s="5" t="inlineStr"/>
-      <c r="CC21" s="5" t="inlineStr"/>
+      <c r="BT21" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BU21" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BV21" s="5" t="inlineStr">
+        <is>
+          <t>Greeting &amp; Identification, Answer Questions, Close Professionally</t>
+        </is>
+      </c>
+      <c r="BW21" s="5" t="inlineStr">
+        <is>
+          <t>Confirm Appointment Details</t>
+        </is>
+      </c>
+      <c r="BX21" s="5" t="inlineStr">
+        <is>
+          <t>[medium] When the customer stated they could actually accommodate the 11:30-12:30 appointment if the technician was available, the rep responded passively, suggesting they 'play it by ear and see what goes on' rather than taking ownership to get a definitive answer. | Fix: Take immediate ownership of the communication gap. Assure the customer you will contact the technician immediately and give the customer a firm callback with a definitive 'yes' or 'no' regarding the appointment time.</t>
+        </is>
+      </c>
+      <c r="BY21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ21" s="5" t="inlineStr">
+        <is>
+          <t>[Scheduling Conflicts] "Yes, hi. I just received a confirmation about a meeting, an appointment rather today between 11:30 and 12:30 here in Tucson, and that I've never coordinated that, and I've been talking directly to Rich, and we're trying to find a time that we could all meet. He didn't tell me that that time was available." (Resolved, severity=medium)</t>
+        </is>
+      </c>
+      <c r="CA21" s="5" t="n">
+        <v>2714</v>
+      </c>
+      <c r="CB21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="CC21" s="5" t="inlineStr">
+        <is>
+          <t>customer_rep, home_owner</t>
+        </is>
+      </c>
       <c r="CD21" s="5" t="n">
         <v>0</v>
       </c>
@@ -6567,14 +7089,14 @@
       <c r="CJ21" s="5" t="inlineStr"/>
       <c r="CK21" s="5" t="inlineStr"/>
       <c r="CL21" s="5" t="inlineStr"/>
-      <c r="CM21" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="CN21" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="CM21" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CN21" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="CO21" s="7" t="inlineStr">
@@ -6604,15 +7126,17 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>NOT SUBMITTED</t>
+          <t>gemini_cmp_21_7a1836b9</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>390.8</v>
+      </c>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
@@ -6650,43 +7174,125 @@
       <c r="AP22" s="5" t="inlineStr"/>
       <c r="AQ22" s="5" t="inlineStr"/>
       <c r="AR22" s="5" t="inlineStr"/>
-      <c r="AS22" s="5" t="inlineStr"/>
-      <c r="AT22" s="5" t="inlineStr"/>
+      <c r="AS22" s="5" t="inlineStr">
+        <is>
+          <t>The homeowner, Claire Hughey, called to express severe frustration regarding an incomplete roofing project at her property in Tucson. After waiting three months and paying $10,000, she returned home to find the job less than half finished, with the carport and part of the main roof completely untouched despite assurances it would be completed. The customer service representative initially offered to have the project team follow up the next day, but the homeowner refused this option and strongly demanded an immediate transfer to someone in the office to resolve the issue.</t>
+        </is>
+      </c>
+      <c r="AT22" s="5" t="inlineStr">
+        <is>
+          <t>Homeowner Claire Hughey reported that her roofing job was left less than half finished today despite assurances it would be completed.
+The customer stated she has been waiting three months and has already paid $10,000 for the project.
+Specific areas of the property remain completely untouched, including the carport roof and part of the main roof.
+The customer rejected a next-day callback from the project team and demanded to speak with an office representative immediately.</t>
+        </is>
+      </c>
       <c r="AU22" s="5" t="inlineStr"/>
       <c r="AV22" s="5" t="inlineStr"/>
-      <c r="AW22" s="5" t="inlineStr"/>
-      <c r="AX22" s="5" t="inlineStr"/>
-      <c r="AY22" s="5" t="inlineStr"/>
+      <c r="AW22" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX22" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AY22" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ22" s="5" t="inlineStr"/>
-      <c r="BA22" s="5" t="inlineStr"/>
+      <c r="BA22" s="5" t="n"/>
       <c r="BB22" s="5" t="inlineStr"/>
-      <c r="BC22" s="5" t="inlineStr"/>
-      <c r="BD22" s="5" t="inlineStr"/>
-      <c r="BE22" s="5" t="inlineStr"/>
-      <c r="BF22" s="5" t="inlineStr"/>
-      <c r="BG22" s="5" t="inlineStr"/>
-      <c r="BH22" s="5" t="inlineStr"/>
-      <c r="BI22" s="5" t="inlineStr"/>
-      <c r="BJ22" s="5" t="inlineStr"/>
-      <c r="BK22" s="5" t="inlineStr"/>
-      <c r="BL22" s="5" t="inlineStr"/>
-      <c r="BM22" s="5" t="inlineStr"/>
-      <c r="BN22" s="5" t="inlineStr"/>
-      <c r="BO22" s="5" t="inlineStr"/>
-      <c r="BP22" s="5" t="inlineStr"/>
-      <c r="BQ22" s="5" t="inlineStr"/>
-      <c r="BR22" s="5" t="inlineStr"/>
+      <c r="BC22" s="5" t="inlineStr">
+        <is>
+          <t>unqualified</t>
+        </is>
+      </c>
+      <c r="BD22" s="5" t="n"/>
+      <c r="BE22" s="5" t="inlineStr">
+        <is>
+          <t>not_booked</t>
+        </is>
+      </c>
+      <c r="BF22" s="5" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="BG22" s="5" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="BH22" s="5" t="inlineStr">
+        <is>
+          <t>unqualified</t>
+        </is>
+      </c>
+      <c r="BI22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ22" s="5" t="n"/>
+      <c r="BK22" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL22" s="5" t="inlineStr">
+        <is>
+          <t>OUT_OF_SCOPE</t>
+        </is>
+      </c>
+      <c r="BM22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" s="5" t="n"/>
       <c r="BS22" s="5" t="inlineStr"/>
-      <c r="BT22" s="5" t="inlineStr"/>
-      <c r="BU22" s="5" t="inlineStr"/>
-      <c r="BV22" s="5" t="inlineStr"/>
-      <c r="BW22" s="5" t="inlineStr"/>
-      <c r="BX22" s="5" t="inlineStr"/>
-      <c r="BY22" s="5" t="inlineStr"/>
+      <c r="BT22" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BU22" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BV22" s="5" t="inlineStr">
+        <is>
+          <t>Confirm Project Details, Set Expectations for Next Steps</t>
+        </is>
+      </c>
+      <c r="BW22" s="5" t="inlineStr">
+        <is>
+          <t>Greeting &amp; Identification, Address Questions/Concerns, Close Professionally</t>
+        </is>
+      </c>
+      <c r="BX22" s="5" t="inlineStr">
+        <is>
+          <t>[medium] The rep answered the phone with just 'How can I help?' missing the standard professional greeting, company name, and rep identification. | Fix: Always answer the phone with a standardized greeting that includes the company name and your own name.
+[high] When the customer became highly agitated about a half-finished $10,000 job and demanded to speak to someone immediately, the rep failed to initiate a warm transfer, get a manager, or clearly explain the escalation path. | Fix: Acknowledge the severity of the problem with strong empathy, and immediately initiate a warm transfer to a supervisor or project manager. If no one is available, explain exactly who will call them back and in what timeframe (e.g., within the hour).</t>
+        </is>
+      </c>
+      <c r="BY22" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="BZ22" s="5" t="inlineStr"/>
-      <c r="CA22" s="5" t="inlineStr"/>
-      <c r="CB22" s="5" t="inlineStr"/>
-      <c r="CC22" s="5" t="inlineStr"/>
+      <c r="CA22" s="5" t="n">
+        <v>1485</v>
+      </c>
+      <c r="CB22" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="CC22" s="5" t="inlineStr">
+        <is>
+          <t>customer_rep, home_owner</t>
+        </is>
+      </c>
       <c r="CD22" s="5" t="n">
         <v>0</v>
       </c>
@@ -6704,14 +7310,14 @@
       <c r="CJ22" s="5" t="inlineStr"/>
       <c r="CK22" s="5" t="inlineStr"/>
       <c r="CL22" s="5" t="inlineStr"/>
-      <c r="CM22" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="CN22" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="CM22" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CN22" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="CO22" s="7" t="inlineStr">
@@ -6741,7 +7347,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>audio_test_2_f5b5e2dd</t>
+          <t>gemini_cmp_22_eb46a252</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -6749,7 +7355,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="n">
+        <v>163.7</v>
+      </c>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr"/>
@@ -6789,40 +7397,42 @@
       <c r="AR23" s="5" t="inlineStr"/>
       <c r="AS23" s="5" t="inlineStr">
         <is>
-          <t>Tracey Johnson called Areeza One Go First after playing phone tag to request a quote for replacing her roof. The representative gathered property and contact details, confirming the address as 1356 East Sequoia Drive, Phoenix, AZ 85024, and asked about roof specifics. Tracey stated the roof is about 20 years old and is an asphalt shingle roof. She also confirmed the home is one-story, not in an HOA, and has no solar panels. The rep confirmed Tracey’s phone number and email, then ended the call indicating they would call her back.</t>
+          <t>Tracey Johnson called to request a quote for a roof replacement after previously playing phone tag with the company. The representative collected her property details, noting it is a 20-year-old, single-story home with asphalt shingles, no solar panels, and no HOA. The representative confirmed her contact information and informed the customer they would call her back to proceed with the scheduling.</t>
         </is>
       </c>
       <c r="AT23" s="5" t="inlineStr">
         <is>
-          <t>Customer (Tracey Johnson) requested a quote to replace her roof and mentioned they had been playing phone tag.
-Property details provided: 1356 East Sequoia Drive, Phoenix, AZ 85024; one-story home; asphalt shingle roof; roof age about 20 years.
-Customer stated there is no HOA and no solar panels; rep collected contact info (phone 623-284-7274 and email doggiedentalaz@yahoo.com) and said they would call back.</t>
+          <t>Customer requested a quote for a full roof replacement.
+The customer noted they had been playing 'phone tag' with the company prior to this call.
+The current roof is 20 years old and features asphalt shingles.
+The property is a single-story home located at 1356 East Sequoia Drive, Phoenix, AZ 85024.
+The home has no HOA, is not in a gated community, and has no solar panels.</t>
         </is>
       </c>
       <c r="AU23" s="5" t="inlineStr">
         <is>
-          <t>Customer_rep to call Tracey Johnson back to proceed with the roof replacement quote.
-Call the customer back to continue the roof replacement quote intake and move the estimate forward</t>
+          <t>Sales representative must call Tracey Johnson back at 623-284-7274 to schedule the roof replacement quote and prevent losing the lead.
+Call the customer back</t>
         </is>
       </c>
       <c r="AV23" s="5" t="inlineStr">
         <is>
-          <t>Contact Tracey Johnson at 623-284-7274 to continue the estimate process for a roof replacement.
-Use the provided address (1356 E Sequoia Dr, Phoenix, AZ 85024) and roof details (asphalt shingles, ~20 years old, one-story, no HOA, no solar) to prepare for quoting/inspection scheduling.</t>
+          <t>Call the customer back.
+Schedule an onsite appointment for the roof replacement estimate.</t>
         </is>
       </c>
       <c r="AW23" s="5" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="AX23" s="5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AY23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="AZ23" s="5" t="inlineStr">
         <is>
-          <t>[call_back] Call the customer back to continue the roof replacement quote intake and move the estimate forward (owner: customer_rep, due: None)</t>
+          <t>[call_back] Call the customer back (owner: customer_rep, due: None)</t>
         </is>
       </c>
       <c r="BA23" s="5" t="inlineStr">
@@ -6838,7 +7448,7 @@
       </c>
       <c r="BD23" s="5" t="inlineStr">
         <is>
-          <t>Roof replacement quote</t>
+          <t>Roof replacement</t>
         </is>
       </c>
       <c r="BE23" s="5" t="inlineStr">
@@ -6891,27 +7501,26 @@
       <c r="BR23" s="5" t="n"/>
       <c r="BS23" s="5" t="inlineStr"/>
       <c r="BT23" s="5" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="BU23" s="5" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="BV23" s="5" t="inlineStr">
         <is>
-          <t>Greeting &amp; Identification, Needs Discovery (partial)</t>
+          <t>Greeting &amp; Identification, Needs Discovery</t>
         </is>
       </c>
       <c r="BW23" s="5" t="inlineStr">
         <is>
-          <t>Qualifying (BANT), Scheduling, Setting Expectations, Close &amp; Confirmation, Objection Handling (not applicable—no objections)</t>
+          <t>Qualifying, Scheduling, Setting Expectations, Close &amp; Confirmation</t>
         </is>
       </c>
       <c r="BX23" s="5" t="inlineStr">
         <is>
-          <t>[high] After gathering details, the rep abruptly ended the call by asking the customer to hang up and saying they would call back, without booking an inspection/estimate time or giving a specific callback timeframe. | Fix: Transition from info-gathering to scheduling: offer two appointment windows, confirm who should be present, and lock the inspection/estimate on the calendar. If a callback is truly required, provide a specific timeframe and confirm the best time to reach the customer.
-[medium] The rep did not ask any qualifying (BANT) questions—no confirmation that Tracey is the homeowner/decision maker, no timeline/urgency for replacement, no mention of other quotes, and no budget/financing discussion. | Fix: Add a short qualification sequence before scheduling: confirm decision maker, understand timing, and ask about other bids and financing needs.
-[medium] Needs discovery stayed limited to roof age/type and property attributes; the rep never asked why the roof is being replaced (leak/damage/insurance/age), whether there is active leaking, or how long the issue has been present. | Fix: After the customer requests a quote, ask 2–3 diagnostic questions about the reason and urgency, plus any prior inspections.
-[low] The rep did not set expectations for the appointment/estimate process (what happens during inspection, how long it takes, what the customer will receive, and next steps). | Fix: Once scheduling is initiated, explain the inspection flow, duration, and deliverables, and confirm who should be present.</t>
+          <t>[high] Instead of scheduling the estimate or inspection on the call, the rep abruptly stated they would call the customer back and ended the interaction. | Fix: Transition directly into scheduling the inspection while you have the customer on the phone.
+[medium] The rep did not ask any qualifying questions (BANT), such as the customer's timeline to replace the roof, budget, or if there were other decision-makers. | Fix: After gathering the property details, ask 1-2 qualifying questions before moving to schedule.
+[medium] The rep completely missed the 'Setting Expectations' stage by not explaining what the callback or quote process would look like. | Fix: Clearly outline what happens next, including timelines and what the customer should prepare for.</t>
         </is>
       </c>
       <c r="BY23" s="5" t="n">
@@ -6919,7 +7528,7 @@
       </c>
       <c r="BZ23" s="5" t="inlineStr"/>
       <c r="CA23" s="5" t="n">
-        <v>1948</v>
+        <v>1972</v>
       </c>
       <c r="CB23" s="5" t="n">
         <v>26</v>
@@ -6983,15 +7592,17 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>NOT SUBMITTED</t>
+          <t>gemini_cmp_23_c7637404</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>244.2</v>
+      </c>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr"/>
@@ -7029,43 +7640,139 @@
       <c r="AP24" s="5" t="inlineStr"/>
       <c r="AQ24" s="5" t="inlineStr"/>
       <c r="AR24" s="5" t="inlineStr"/>
-      <c r="AS24" s="5" t="inlineStr"/>
-      <c r="AT24" s="5" t="inlineStr"/>
+      <c r="AS24" s="5" t="inlineStr">
+        <is>
+          <t>Rodney, a former roofer calling from Colorado, inquired on behalf of a friend in Arizona (zip code 85212) whose home is under contract for sale. The friend received a $35,000 quote for a roof replacement following a home inspection, and Rodney wanted to know if a second inspection could determine if monsoon or storm damage might qualify for an insurance claim. The representative explained that real estate-related inspections carry a $399 fee, which would be applied toward any future repair or replacement. Rodney declined to book the appointment due to the fee, noting his expectation of free estimates based on his past industry experience, and stated he would conduct further research.</t>
+        </is>
+      </c>
+      <c r="AT24" s="5" t="inlineStr">
+        <is>
+          <t>Caller is inquiring on behalf of a friend in Arizona (zip 85212) whose home is currently in the contract stage of a sale.
+The friend was told they need a roof replacement and was quoted $35,000 by another party.
+Caller wanted an inspection to see if Arizona weather events like monsoons caused damage that could be covered by an insurance claim to save the homeowner money.
+Representative stated there is a $399 one-time fee for real estate type inspections, which goes toward the repair or replacement.
+Caller declined to schedule the inspection because he did not want to pay the fee, expecting free estimates based on his past roofing experience.</t>
+        </is>
+      </c>
       <c r="AU24" s="5" t="inlineStr"/>
       <c r="AV24" s="5" t="inlineStr"/>
-      <c r="AW24" s="5" t="inlineStr"/>
-      <c r="AX24" s="5" t="inlineStr"/>
-      <c r="AY24" s="5" t="inlineStr"/>
+      <c r="AW24" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AX24" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AY24" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ24" s="5" t="inlineStr"/>
-      <c r="BA24" s="5" t="inlineStr"/>
+      <c r="BA24" s="5" t="inlineStr">
+        <is>
+          <t>Rodney</t>
+        </is>
+      </c>
       <c r="BB24" s="5" t="inlineStr"/>
-      <c r="BC24" s="5" t="inlineStr"/>
-      <c r="BD24" s="5" t="inlineStr"/>
-      <c r="BE24" s="5" t="inlineStr"/>
-      <c r="BF24" s="5" t="inlineStr"/>
-      <c r="BG24" s="5" t="inlineStr"/>
-      <c r="BH24" s="5" t="inlineStr"/>
-      <c r="BI24" s="5" t="inlineStr"/>
-      <c r="BJ24" s="5" t="inlineStr"/>
-      <c r="BK24" s="5" t="inlineStr"/>
-      <c r="BL24" s="5" t="inlineStr"/>
-      <c r="BM24" s="5" t="inlineStr"/>
-      <c r="BN24" s="5" t="inlineStr"/>
-      <c r="BO24" s="5" t="inlineStr"/>
-      <c r="BP24" s="5" t="inlineStr"/>
-      <c r="BQ24" s="5" t="inlineStr"/>
-      <c r="BR24" s="5" t="inlineStr"/>
+      <c r="BC24" s="5" t="inlineStr">
+        <is>
+          <t>cold</t>
+        </is>
+      </c>
+      <c r="BD24" s="5" t="inlineStr">
+        <is>
+          <t>Roof inspection</t>
+        </is>
+      </c>
+      <c r="BE24" s="5" t="inlineStr">
+        <is>
+          <t>not_booked</t>
+        </is>
+      </c>
+      <c r="BF24" s="5" t="inlineStr">
+        <is>
+          <t>new_inquiry</t>
+        </is>
+      </c>
+      <c r="BG24" s="5" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="BH24" s="5" t="inlineStr">
+        <is>
+          <t>unqualified</t>
+        </is>
+      </c>
+      <c r="BI24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ24" s="5" t="n"/>
+      <c r="BK24" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL24" s="5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="BM24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BP24" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BQ24" s="5" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BR24" s="5" t="n"/>
       <c r="BS24" s="5" t="inlineStr"/>
-      <c r="BT24" s="5" t="inlineStr"/>
-      <c r="BU24" s="5" t="inlineStr"/>
-      <c r="BV24" s="5" t="inlineStr"/>
-      <c r="BW24" s="5" t="inlineStr"/>
-      <c r="BX24" s="5" t="inlineStr"/>
-      <c r="BY24" s="5" t="inlineStr"/>
-      <c r="BZ24" s="5" t="inlineStr"/>
-      <c r="CA24" s="5" t="inlineStr"/>
-      <c r="CB24" s="5" t="inlineStr"/>
-      <c r="CC24" s="5" t="inlineStr"/>
+      <c r="BT24" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BU24" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BV24" s="5" t="inlineStr">
+        <is>
+          <t>Greeting &amp; Identification, Needs Discovery, Qualifying, Setting Expectations</t>
+        </is>
+      </c>
+      <c r="BW24" s="5" t="inlineStr">
+        <is>
+          <t>Objection Handling, Scheduling, Close &amp; Confirmation</t>
+        </is>
+      </c>
+      <c r="BX24" s="5" t="inlineStr">
+        <is>
+          <t>[high] When the caller asked about local weather impacts that insurance might cover, the rep said they didn't know, weren't in the insurance department, and told the caller to 'just look online'. | Fix: Acknowledge the question, provide a high-level localized answer, and offer to connect them with the specialized team who can give exact details.
+[high] The rep learned early in the call that the caller was inquiring on behalf of a friend (the actual homeowner) who needed a $35,000 roof replacement, but the rep never asked for the homeowner's name, phone number, or exact property address (only got the zip code). | Fix: As soon as a third party mentions they are calling for a homeowner, immediately capture the decision-maker's contact information and the property address.
+[medium] When the caller indirectly objected to the $399 inspection fee by comparing it to 'free' estimates they used to do as a roofer, the rep did not defend the value of the fee or try to overcome the objection, resulting in a lost appointment. | Fix: Explain the specific value of a real estate/insurance inspection report to justify the cost before re-emphasizing the credit toward the repair.</t>
+        </is>
+      </c>
+      <c r="BY24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ24" s="5" t="inlineStr">
+        <is>
+          <t>[Service Fee Concerns] "No, because I'm I'm not gonna pay for that for for him. You know, you know, save your money. And then they did say they already have somebody to to pay for the roof, or that that somebody is gonna do the roof for them. That's gonna charge them the thirty five thousand dollars. But I told them let me make this call. See if somebody is out there willing to do it." (Unresolved, severity=high)</t>
+        </is>
+      </c>
+      <c r="CA24" s="5" t="n">
+        <v>4727</v>
+      </c>
+      <c r="CB24" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="CC24" s="5" t="inlineStr">
+        <is>
+          <t>customer_rep, home_owner</t>
+        </is>
+      </c>
       <c r="CD24" s="5" t="n">
         <v>0</v>
       </c>
@@ -7083,14 +7790,14 @@
       <c r="CJ24" s="5" t="inlineStr"/>
       <c r="CK24" s="5" t="inlineStr"/>
       <c r="CL24" s="5" t="inlineStr"/>
-      <c r="CM24" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="CN24" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="CM24" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CN24" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="CO24" s="7" t="inlineStr">
@@ -7120,7 +7827,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>audio_test_4_59a6536b</t>
+          <t>gemini_cmp_24_ab171baf</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -7128,7 +7835,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="n">
+        <v>130.4</v>
+      </c>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr"/>
@@ -7168,33 +7877,43 @@
       <c r="AR25" s="5" t="inlineStr"/>
       <c r="AS25" s="5" t="inlineStr">
         <is>
-          <t>Tony Garcia returned a call from Maddy to schedule a roof inspection. He initially thought the call was a reminder for an appointment he had already set with another company, but confirmed he still wants this company to come out. Maddy offered the next availability on Friday, and Tony booked the 10 AM–12 PM window. Tony explained he wants the technician to review notes from a home inspection report from when he bought the house about a year ago, check areas that were flagged, and also inspect the attic for a back unit on his multi-family property where he has a tenant; he also mentioned a termite-related item in the report that he wants looked at. He estimated the roof was last replaced around 2012/2013. Maddy confirmed contact details, obtained permission to text appointment updates, collected an email, and gathered property details (single-story, shingle roof, no HOA, no solar). She then explained what to expect during the 1–2 hour inspection and confirmed Tony should receive a confirmation text and that they will see him Friday.</t>
+          <t>Tony Garcia returned a call to schedule a roof inspection for a multi-family property he purchased a year ago. He requested that the technician review specific areas mentioned in an old home inspection report, including a minor termite issue, and also inspect the attic of a tenant-occupied back unit. The representative, Maddy, collected property details, noting it is a single-story home with a shingle roof, no HOA, and no solar panels. The roof was last replaced around 2012. Maddy successfully scheduled the inspection for this Friday between 10:00 AM and 12:00 PM and walked Tony through what to expect during the appointment.</t>
         </is>
       </c>
       <c r="AT25" s="5" t="inlineStr">
         <is>
-          <t>Roof inspection scheduled for Friday (2026-03-20) between 10:00 AM and 12:00 PM, and Tony confirmed he will be present.
-Customer wants the technician to review a prior inspection report from when he bought the home about a year ago, including flagged areas and a termite-related item, and also check the attic for the back unit where a tenant lives.
-Property details provided: address 1925 W Montevista Rd, Phoenix; single-story home; shingle roof; no HOA; no solar panels; roof last replaced around 2012/2013.</t>
-        </is>
-      </c>
-      <c r="AU25" s="5" t="inlineStr"/>
+          <t>Customer Tony Garcia scheduled a roof inspection for this Friday between 10:00 AM and 12:00 PM and will be present.
+Property Details: Single-story, shingle roof, no HOA, no solar panels, located at 1925 West Montevista Road, Phoenix.
+The roof is estimated to be 14 years old (last replaced around 2012).
+Field Tech Note: The property is a multi-family home with a tenant-occupied back unit. The customer specifically requested the inside of the back unit's attic be inspected.
+Field Tech Note: The customer wants the technician to look at specific areas highlighted in a year-old home inspection report, including a minor termite issue.</t>
+        </is>
+      </c>
+      <c r="AU25" s="5" t="inlineStr">
+        <is>
+          <t>Perform roof inspection, ensuring to review the 1-year-old inspection report, check the tenant-occupied back unit attic, and evaluate the prior termite issue.</t>
+        </is>
+      </c>
       <c r="AV25" s="5" t="inlineStr">
         <is>
-          <t>Technician to arrive during the scheduled 10:00 AM–12:00 PM window on 2026-03-20 to perform the roof inspection and review findings with Tony.
-Send/maintain text updates and confirmation to Tony at the provided phone number and email regarding the appointment.</t>
+          <t>Technician to arrive at the property this Friday between 10:00 AM and 12:00 PM.
+Technician to inspect the main roof and the back unit's attic, document any damage with 50-200 photos, and review the findings and options with the homeowner.</t>
         </is>
       </c>
       <c r="AW25" s="5" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AX25" s="5" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AY25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" s="5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AZ25" s="5" t="inlineStr">
+        <is>
+          <t>[inspection] Perform roof inspection, ensuring to review the 1-year-old inspection report, check the tenant-occupied back unit attic, and evaluate the prior termite issue. (owner: technician, due: None)</t>
+        </is>
+      </c>
       <c r="BA25" s="5" t="inlineStr">
         <is>
           <t>Tony Garcia</t>
@@ -7208,7 +7927,7 @@
       </c>
       <c r="BD25" s="5" t="inlineStr">
         <is>
-          <t>Roof inspection</t>
+          <t>roof and attic inspection</t>
         </is>
       </c>
       <c r="BE25" s="5" t="inlineStr">
@@ -7236,7 +7955,7 @@
       </c>
       <c r="BJ25" s="5" t="inlineStr">
         <is>
-          <t>2026-03-20T10:00:00</t>
+          <t>2026-03-27T10:00:00</t>
         </is>
       </c>
       <c r="BK25" s="5" t="b">
@@ -7254,21 +7973,21 @@
         <v>1</v>
       </c>
       <c r="BO25" s="5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="BP25" s="5" t="n">
         <v>0.8</v>
       </c>
       <c r="BQ25" s="5" t="n">
-        <v>0.575</v>
+        <v>0.65</v>
       </c>
       <c r="BR25" s="5" t="n"/>
       <c r="BS25" s="5" t="inlineStr"/>
       <c r="BT25" s="5" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="BU25" s="5" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="BV25" s="5" t="inlineStr">
         <is>
@@ -7277,15 +7996,13 @@
       </c>
       <c r="BW25" s="5" t="inlineStr">
         <is>
-          <t>Qualifying (BANT), Objection Handling</t>
+          <t>Qualifying</t>
         </is>
       </c>
       <c r="BX25" s="5" t="inlineStr">
         <is>
-          <t>[low] At the beginning of the call, the rep did not provide a professional greeting that included the company name; the interaction started with a transfer attempt and then a personal greeting only. | Fix: Open with a standard greeting that includes the company name, the rep’s name, and a quick purpose statement before moving into questions or transfers.
-[medium] After the customer explained they wanted a roof inspection and referenced prior inspection notes, the rep did not ask core diagnostic questions like whether there is an active leak/damage, how long symptoms have been occurring, or if any contractor has already inspected the roof recently. | Fix: Add a short needs-discovery sequence before/while scheduling: confirm current symptoms, duration, and any prior evaluations beyond the old report.
-[medium] The rep did not complete qualifying (BANT): they did not confirm Tony is the homeowner/decision maker, did not ask timeline/urgency for repairs, and did not explore whether other quotes were being gathered beyond the brief mention, nor any budget/financing considerations. | Fix: Add quick qualifying questions after scheduling the window (or before confirming) to ensure the right person will be present and to understand intent and competitive landscape.
-[low] When the customer mentioned they were reaching out to other providers, the rep did not acknowledge the concern or provide reassurance/differentiation (e.g., what makes their inspection valuable, why keep the appointment). | Fix: Acknowledge comparison shopping and reinforce a clear value proposition tied to the inspection deliverables and next steps.</t>
+          <t>[medium] When the customer explicitly stated 'I've been reaching out to other people as well', the rep ignored this comment and immediately jumped to providing schedule availability without asking any qualifying questions about competitors. | Fix: Acknowledge the customer's comment about shopping around and ask a gentle probing question to gather competitive intelligence before moving on to scheduling.
+[medium] During the qualification stage, the rep did not ask any questions regarding the customer's budget, payment plans, or whether they would be interested in financing. | Fix: Introduce the topic of budget gently by mentioning financing options as a benefit to the customer.</t>
         </is>
       </c>
       <c r="BY25" s="5" t="n">
@@ -7293,10 +8010,10 @@
       </c>
       <c r="BZ25" s="5" t="inlineStr"/>
       <c r="CA25" s="5" t="n">
-        <v>5033</v>
+        <v>5014</v>
       </c>
       <c r="CB25" s="5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="CC25" s="5" t="inlineStr">
         <is>
@@ -7357,15 +8074,17 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>NOT SUBMITTED</t>
+          <t>gemini_cmp_25_a7167aa2</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>346.2</v>
+      </c>
       <c r="H26" s="5" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="5" t="inlineStr"/>
@@ -7403,43 +8122,146 @@
       <c r="AP26" s="5" t="inlineStr"/>
       <c r="AQ26" s="5" t="inlineStr"/>
       <c r="AR26" s="5" t="inlineStr"/>
-      <c r="AS26" s="5" t="inlineStr"/>
-      <c r="AT26" s="5" t="inlineStr"/>
-      <c r="AU26" s="5" t="inlineStr"/>
-      <c r="AV26" s="5" t="inlineStr"/>
-      <c r="AW26" s="5" t="inlineStr"/>
-      <c r="AX26" s="5" t="inlineStr"/>
-      <c r="AY26" s="5" t="inlineStr"/>
+      <c r="AS26" s="5" t="inlineStr">
+        <is>
+          <t>Brenda Ankrom, the property owner, called Arizona Roofers to request an urgent quote for roof repairs due to a collapsed section in her garage, a failing section in her living room, and a roof rat issue. Her home is 4,200 square feet with a red clay tile roof that is a mix of 40-year-old original and 20-year-old remodeled sections. The representative scheduled an experienced technician for a free inspection on March 27, 2026, between 1:00 PM and 3:00 PM. The customer stressed the urgency of securing the living room area immediately to prevent further leak damage, and the rep advised her to discuss an immediate temporary fix with the technician on-site.</t>
+        </is>
+      </c>
+      <c r="AT26" s="5" t="inlineStr">
+        <is>
+          <t>Customer is property owner Brenda Ankrom, reachable at 480-892-9506 (home landline, cannot receive text messages).
+Property address is 191 North Sierra Court, Gilbert, AZ 85234 (located in an HOA neighborhood, not gated).
+Roof type is red clay tile on a 4,200 sq ft home; sections are 40 years old (original) and 20 years old (remodeled). There are no solar panels.
+Major property damage: The roof has already fallen through in the garage, and the living room ceiling is currently breaking through with debris on the floor and recent leak issues.
+Customer specifically requested an immediate fix to secure the living room area to prevent the collapse from worsening.
+Customer mentioned they currently have an active issue with roof rats.
+Technician access note: Technician will call 30 minutes prior to arrival from a personal device, and the customer has been warned to answer unrecognized numbers during the appointment window.</t>
+        </is>
+      </c>
+      <c r="AU26" s="5" t="inlineStr">
+        <is>
+          <t>Technician must evaluate and potentially provide an immediate emergency securement/tarping for the living room roof during the March 27 inspection to address the active collapse hazard and secure the sale.</t>
+        </is>
+      </c>
+      <c r="AV26" s="5" t="inlineStr">
+        <is>
+          <t>Technician will call Brenda from a personal device 30 minutes prior to the appointment.
+Technician will conduct a full roof inspection on March 27, 2026, between 1:00 PM and 3:00 PM.
+Technician will provide a full report, 50-100 photos, and discuss options for immediate repair and full-scale work.</t>
+        </is>
+      </c>
+      <c r="AW26" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AX26" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AY26" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ26" s="5" t="inlineStr"/>
-      <c r="BA26" s="5" t="inlineStr"/>
+      <c r="BA26" s="5" t="inlineStr">
+        <is>
+          <t>Brenda Ankrom</t>
+        </is>
+      </c>
       <c r="BB26" s="5" t="inlineStr"/>
-      <c r="BC26" s="5" t="inlineStr"/>
-      <c r="BD26" s="5" t="inlineStr"/>
-      <c r="BE26" s="5" t="inlineStr"/>
-      <c r="BF26" s="5" t="inlineStr"/>
-      <c r="BG26" s="5" t="inlineStr"/>
-      <c r="BH26" s="5" t="inlineStr"/>
-      <c r="BI26" s="5" t="inlineStr"/>
-      <c r="BJ26" s="5" t="inlineStr"/>
-      <c r="BK26" s="5" t="inlineStr"/>
-      <c r="BL26" s="5" t="inlineStr"/>
-      <c r="BM26" s="5" t="inlineStr"/>
-      <c r="BN26" s="5" t="inlineStr"/>
-      <c r="BO26" s="5" t="inlineStr"/>
-      <c r="BP26" s="5" t="inlineStr"/>
-      <c r="BQ26" s="5" t="inlineStr"/>
-      <c r="BR26" s="5" t="inlineStr"/>
+      <c r="BC26" s="5" t="inlineStr">
+        <is>
+          <t>hot</t>
+        </is>
+      </c>
+      <c r="BD26" s="5" t="inlineStr">
+        <is>
+          <t>Roof repair</t>
+        </is>
+      </c>
+      <c r="BE26" s="5" t="inlineStr">
+        <is>
+          <t>booked</t>
+        </is>
+      </c>
+      <c r="BF26" s="5" t="inlineStr">
+        <is>
+          <t>new_inquiry</t>
+        </is>
+      </c>
+      <c r="BG26" s="5" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="BH26" s="5" t="inlineStr">
+        <is>
+          <t>qualified_and_booked</t>
+        </is>
+      </c>
+      <c r="BI26" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ26" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-27T13:00:00</t>
+        </is>
+      </c>
+      <c r="BK26" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL26" s="5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="BM26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ26" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BR26" s="5" t="n"/>
       <c r="BS26" s="5" t="inlineStr"/>
-      <c r="BT26" s="5" t="inlineStr"/>
-      <c r="BU26" s="5" t="inlineStr"/>
-      <c r="BV26" s="5" t="inlineStr"/>
+      <c r="BT26" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BU26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV26" s="5" t="inlineStr">
+        <is>
+          <t>Greeting &amp; Identification, Needs Discovery, Qualifying, Scheduling, Setting Expectations, Objection Handling, Close &amp; Confirmation</t>
+        </is>
+      </c>
       <c r="BW26" s="5" t="inlineStr"/>
-      <c r="BX26" s="5" t="inlineStr"/>
-      <c r="BY26" s="5" t="inlineStr"/>
+      <c r="BX26" s="5" t="inlineStr">
+        <is>
+          <t>[high] When the customer described severe damage (the roof falling through in the garage and living room), the rep responded dismissively with 'Okay, no worries' instead of showing empathy or urgency. | Fix: Acknowledge the severity of the situation immediately, show empathy, and use it to transition into urgent scheduling.
+[medium] When the customer stated their phone was a landline and couldn't receive text confirmations, the rep told the customer they would 'just have to remember' instead of ensuring the appointment was documented. | Fix: Prompt the customer to write the details down and have them confirm they've recorded the correct date and time window.</t>
+        </is>
+      </c>
+      <c r="BY26" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="BZ26" s="5" t="inlineStr"/>
-      <c r="CA26" s="5" t="inlineStr"/>
-      <c r="CB26" s="5" t="inlineStr"/>
-      <c r="CC26" s="5" t="inlineStr"/>
+      <c r="CA26" s="5" t="n">
+        <v>7913</v>
+      </c>
+      <c r="CB26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CC26" s="5" t="inlineStr">
+        <is>
+          <t>customer_rep</t>
+        </is>
+      </c>
       <c r="CD26" s="5" t="n">
         <v>0</v>
       </c>
@@ -7457,14 +8279,14 @@
       <c r="CJ26" s="5" t="inlineStr"/>
       <c r="CK26" s="5" t="inlineStr"/>
       <c r="CL26" s="5" t="inlineStr"/>
-      <c r="CM26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="CN26" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="CM26" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CN26" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="CO26" s="7" t="inlineStr">
@@ -7494,15 +8316,17 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>NOT SUBMITTED</t>
+          <t>gemini_cmp_26_c96ee667</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>341</v>
+      </c>
       <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="5" t="inlineStr"/>
@@ -7540,43 +8364,145 @@
       <c r="AP27" s="5" t="inlineStr"/>
       <c r="AQ27" s="5" t="inlineStr"/>
       <c r="AR27" s="5" t="inlineStr"/>
-      <c r="AS27" s="5" t="inlineStr"/>
-      <c r="AT27" s="5" t="inlineStr"/>
-      <c r="AU27" s="5" t="inlineStr"/>
-      <c r="AV27" s="5" t="inlineStr"/>
-      <c r="AW27" s="5" t="inlineStr"/>
-      <c r="AX27" s="5" t="inlineStr"/>
-      <c r="AY27" s="5" t="inlineStr"/>
+      <c r="AS27" s="5" t="inlineStr">
+        <is>
+          <t>The customer, Shailesh, called to follow up on a roof repair estimate that needs to be rescheduled. He also inquired about an unresolved deposit issue, stating he previously canceled a job, received only half of his deposit back, and has not heard from the company since. The representative collected his phone number (602-391-8311) and assured him that customer support would contact him to address the estimate and the deposit follow-up.</t>
+        </is>
+      </c>
+      <c r="AT27" s="5" t="inlineStr">
+        <is>
+          <t>Customer is calling to reschedule a roof repair estimate after not receiving a follow-up.
+Customer previously paid a deposit, canceled, and only received half of the deposit back.
+Customer's contact number was recorded as 602-391-8311.</t>
+        </is>
+      </c>
+      <c r="AU27" s="5" t="inlineStr">
+        <is>
+          <t>Customer Support Representative to call Shailesh at 602-391-8311 to resolve the partial deposit refund issue and reschedule the roof repair estimate.</t>
+        </is>
+      </c>
+      <c r="AV27" s="5" t="inlineStr">
+        <is>
+          <t>Customer support team to contact the customer via phone.
+Address the remaining deposit issue and schedule the new roof repair estimate.</t>
+        </is>
+      </c>
+      <c r="AW27" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AX27" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AY27" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ27" s="5" t="inlineStr"/>
-      <c r="BA27" s="5" t="inlineStr"/>
+      <c r="BA27" s="5" t="inlineStr">
+        <is>
+          <t>Shailesh Amar</t>
+        </is>
+      </c>
       <c r="BB27" s="5" t="inlineStr"/>
-      <c r="BC27" s="5" t="inlineStr"/>
-      <c r="BD27" s="5" t="inlineStr"/>
-      <c r="BE27" s="5" t="inlineStr"/>
-      <c r="BF27" s="5" t="inlineStr"/>
-      <c r="BG27" s="5" t="inlineStr"/>
-      <c r="BH27" s="5" t="inlineStr"/>
-      <c r="BI27" s="5" t="inlineStr"/>
-      <c r="BJ27" s="5" t="inlineStr"/>
-      <c r="BK27" s="5" t="inlineStr"/>
-      <c r="BL27" s="5" t="inlineStr"/>
-      <c r="BM27" s="5" t="inlineStr"/>
-      <c r="BN27" s="5" t="inlineStr"/>
-      <c r="BO27" s="5" t="inlineStr"/>
-      <c r="BP27" s="5" t="inlineStr"/>
-      <c r="BQ27" s="5" t="inlineStr"/>
-      <c r="BR27" s="5" t="inlineStr"/>
+      <c r="BC27" s="5" t="inlineStr">
+        <is>
+          <t>warm</t>
+        </is>
+      </c>
+      <c r="BD27" s="5" t="inlineStr">
+        <is>
+          <t>Roof repair</t>
+        </is>
+      </c>
+      <c r="BE27" s="5" t="inlineStr">
+        <is>
+          <t>booked</t>
+        </is>
+      </c>
+      <c r="BF27" s="5" t="inlineStr">
+        <is>
+          <t>follow_up</t>
+        </is>
+      </c>
+      <c r="BG27" s="5" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="BH27" s="5" t="inlineStr">
+        <is>
+          <t>follow_up_inquiry</t>
+        </is>
+      </c>
+      <c r="BI27" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ27" s="5" t="n"/>
+      <c r="BK27" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL27" s="5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="BM27" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO27" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BP27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ27" s="5" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="BR27" s="5" t="n"/>
       <c r="BS27" s="5" t="inlineStr"/>
-      <c r="BT27" s="5" t="inlineStr"/>
-      <c r="BU27" s="5" t="inlineStr"/>
-      <c r="BV27" s="5" t="inlineStr"/>
-      <c r="BW27" s="5" t="inlineStr"/>
-      <c r="BX27" s="5" t="inlineStr"/>
-      <c r="BY27" s="5" t="inlineStr"/>
-      <c r="BZ27" s="5" t="inlineStr"/>
-      <c r="CA27" s="5" t="inlineStr"/>
-      <c r="CB27" s="5" t="inlineStr"/>
-      <c r="CC27" s="5" t="inlineStr"/>
+      <c r="BT27" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BU27" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BV27" s="5" t="inlineStr">
+        <is>
+          <t>Greeting &amp; Identification, Confirm Project Details, Address Questions/Concerns, Close Professionally</t>
+        </is>
+      </c>
+      <c r="BW27" s="5" t="inlineStr">
+        <is>
+          <t>Set Expectations for Next Steps</t>
+        </is>
+      </c>
+      <c r="BX27" s="5" t="inlineStr">
+        <is>
+          <t>[high] After the customer expressed frustration about not hearing back on a canceled deposit and estimate, the rep promised a callback but failed to provide a specific timeframe. | Fix: Provide a definitive timeframe for the callback and assure the customer that the issue is being escalated.
+[low] The rep started the call abruptly by asking for details without providing a professional greeting or stating the company name. | Fix: Always open the call with a standard, branded greeting before asking for the customer's information.</t>
+        </is>
+      </c>
+      <c r="BY27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ27" s="5" t="inlineStr">
+        <is>
+          <t>[Inefficient Agent Communication] "I didn't heard back on a roof repair estimate. Try and get that rescheduled. Previously paid a deposit canceled. Got half the deposit back, but I haven't heard back on the issue." (Resolved, severity=high)</t>
+        </is>
+      </c>
+      <c r="CA27" s="5" t="n">
+        <v>920</v>
+      </c>
+      <c r="CB27" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="CC27" s="5" t="inlineStr">
+        <is>
+          <t>customer_rep, home_owner</t>
+        </is>
+      </c>
       <c r="CD27" s="5" t="n">
         <v>0</v>
       </c>
@@ -7594,14 +8520,14 @@
       <c r="CJ27" s="5" t="inlineStr"/>
       <c r="CK27" s="5" t="inlineStr"/>
       <c r="CL27" s="5" t="inlineStr"/>
-      <c r="CM27" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="CN27" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="CM27" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CN27" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="CO27" s="7" t="inlineStr">
@@ -7631,7 +8557,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>audio_test_7_e3cb63ba</t>
+          <t>gemini_cmp_27_a0e3938a</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -7639,7 +8565,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr"/>
+      <c r="G28" s="5" t="n">
+        <v>1.2</v>
+      </c>
       <c r="H28" s="5" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="5" t="inlineStr"/>
@@ -7679,23 +8607,23 @@
       <c r="AR28" s="5" t="inlineStr"/>
       <c r="AS28" s="5" t="inlineStr">
         <is>
-          <t>The representative asked for the reason for the call and contact information for a callback. The homeowner requested the company’s mailing address so they could send in a payment and provided a callback number (7018331113), asking the company to call them back.</t>
+          <t>The customer left a message requesting the company's mailing address so they can send in a payment. They asked for customer support to call them back at 701-833-1113 to provide this information.</t>
         </is>
       </c>
       <c r="AT28" s="5" t="inlineStr">
         <is>
-          <t>Customer requested the company’s mailing address to send in a payment.
-Customer asked for a callback and provided the phone number 7018331113.
-No roofing service request, scheduling, or property/roof details were discussed in this call.</t>
+          <t>The customer needs the company's mailing address.
+The customer is trying to send in a payment.
+The customer requested a callback and provided their phone number as 701-833-1113.</t>
         </is>
       </c>
       <c r="AU28" s="5" t="inlineStr"/>
       <c r="AV28" s="5" t="inlineStr"/>
       <c r="AW28" s="5" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="AX28" s="5" t="n">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="AY28" s="5" t="n">
         <v>0</v>
@@ -7759,10 +8687,10 @@
       <c r="BR28" s="5" t="n"/>
       <c r="BS28" s="5" t="inlineStr"/>
       <c r="BT28" s="5" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="BU28" s="5" t="n">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
       <c r="BV28" s="5" t="inlineStr">
         <is>
@@ -7776,9 +8704,7 @@
       </c>
       <c r="BX28" s="5" t="inlineStr">
         <is>
-          <t>[high] After the homeowner stated they needed the company’s mailing address to send a payment and provided a callback number, the rep did not acknowledge the request, confirm details, or provide the address/next steps; the call ends without resolution. | Fix: Acknowledge the request, confirm what information is needed (mailing address and any attention line/account/project identifier), and either provide the mailing address immediately or give a specific callback/fulfillment timeframe and method (text/email/callback).
-[medium] The rep did not set expectations for next steps (who will call back, when, and how) after requesting contact information for customer support to return the call. | Fix: State who will follow up, the expected timeframe, and confirm the best callback number; offer an alternate channel (text/email) if appropriate.
-[low] The rep did not close the interaction professionally by summarizing the request and confirming the next step before ending. | Fix: End with a recap, confirmation of contact details, and a polite closing line inviting further questions.</t>
+          <t>[medium] The automated greeting or representative failed to include the company name or a standard professional welcome at the very beginning of the prompt. | Fix: Update the initial greeting to clearly state the business name and offer a professional welcome before demanding caller details.</t>
         </is>
       </c>
       <c r="BY28" s="5" t="n">
@@ -7786,10 +8712,10 @@
       </c>
       <c r="BZ28" s="5" t="inlineStr"/>
       <c r="CA28" s="5" t="n">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="CB28" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CC28" s="5" t="inlineStr">
         <is>
@@ -7850,15 +8776,17 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>NOT SUBMITTED</t>
+          <t>gemini_cmp_28_c78777b5</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>212.2</v>
+      </c>
       <c r="H29" s="5" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="5" t="inlineStr"/>
@@ -7896,43 +8824,148 @@
       <c r="AP29" s="5" t="inlineStr"/>
       <c r="AQ29" s="5" t="inlineStr"/>
       <c r="AR29" s="5" t="inlineStr"/>
-      <c r="AS29" s="5" t="inlineStr"/>
-      <c r="AT29" s="5" t="inlineStr"/>
-      <c r="AU29" s="5" t="inlineStr"/>
-      <c r="AV29" s="5" t="inlineStr"/>
-      <c r="AW29" s="5" t="inlineStr"/>
-      <c r="AX29" s="5" t="inlineStr"/>
-      <c r="AY29" s="5" t="inlineStr"/>
+      <c r="AS29" s="5" t="inlineStr">
+        <is>
+          <t>Cassie Gibson called to request an estimate for roof repairs on her single-story manufactured home in Congress, Arizona. The roof, which is approximately 16 years old, sustained wind and rain damage, and an insurance adjuster has already assessed the property. Although the home currently has asphalt shingles, Cassie explicitly requested an estimate to upgrade to a metal roof. The representative gathered property access details, noting a 10-mile bumpy dirt road, and successfully scheduled an inspection appointment for Monday, March 23rd between 10 AM and 12 PM.</t>
+        </is>
+      </c>
+      <c r="AT29" s="5" t="inlineStr">
+        <is>
+          <t>Customer needs an estimate for roof repair/replacement due to wind and rain damage, noting severe damage specifically over the porches.
+An insurance claim has already been filed, and an adjuster measured the total roof area (including porches) at 2632 square feet.
+The property currently has 16-year-old asphalt composition laminate shingles, but the customer specifically requested a quote for a metal roof option.
+Access instructions for the field technician: The property is a single-story manufactured home with no HOA or gate codes, but access requires driving down a bumpy 10-mile dirt road.
+Customer is the sole property owner and an appointment was booked for Monday, March 23rd from 10 AM to 12 PM.</t>
+        </is>
+      </c>
+      <c r="AU29" s="5" t="inlineStr">
+        <is>
+          <t>Assigned field technician must prepare pricing options for both asphalt shingle replacement and a metal roof upgrade to present at the appointment.</t>
+        </is>
+      </c>
+      <c r="AV29" s="5" t="inlineStr">
+        <is>
+          <t>Send automated text message confirmation of the scheduled appointment to the customer.
+Assigned technician to call the customer 30 minutes before arriving on the day of the appointment.
+Technician to perform a full roof inspection and review material options and pricing with the customer onsite.</t>
+        </is>
+      </c>
+      <c r="AW29" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX29" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AY29" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ29" s="5" t="inlineStr"/>
-      <c r="BA29" s="5" t="inlineStr"/>
+      <c r="BA29" s="5" t="inlineStr">
+        <is>
+          <t>Cassi Gibson</t>
+        </is>
+      </c>
       <c r="BB29" s="5" t="inlineStr"/>
-      <c r="BC29" s="5" t="inlineStr"/>
-      <c r="BD29" s="5" t="inlineStr"/>
-      <c r="BE29" s="5" t="inlineStr"/>
-      <c r="BF29" s="5" t="inlineStr"/>
-      <c r="BG29" s="5" t="inlineStr"/>
-      <c r="BH29" s="5" t="inlineStr"/>
-      <c r="BI29" s="5" t="inlineStr"/>
-      <c r="BJ29" s="5" t="inlineStr"/>
-      <c r="BK29" s="5" t="inlineStr"/>
-      <c r="BL29" s="5" t="inlineStr"/>
-      <c r="BM29" s="5" t="inlineStr"/>
-      <c r="BN29" s="5" t="inlineStr"/>
-      <c r="BO29" s="5" t="inlineStr"/>
-      <c r="BP29" s="5" t="inlineStr"/>
-      <c r="BQ29" s="5" t="inlineStr"/>
-      <c r="BR29" s="5" t="inlineStr"/>
+      <c r="BC29" s="5" t="inlineStr">
+        <is>
+          <t>hot</t>
+        </is>
+      </c>
+      <c r="BD29" s="5" t="inlineStr">
+        <is>
+          <t>Roof repair estimate</t>
+        </is>
+      </c>
+      <c r="BE29" s="5" t="inlineStr">
+        <is>
+          <t>booked</t>
+        </is>
+      </c>
+      <c r="BF29" s="5" t="inlineStr">
+        <is>
+          <t>new_inquiry</t>
+        </is>
+      </c>
+      <c r="BG29" s="5" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="BH29" s="5" t="inlineStr">
+        <is>
+          <t>qualified_and_booked</t>
+        </is>
+      </c>
+      <c r="BI29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ29" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-23T10:00:00</t>
+        </is>
+      </c>
+      <c r="BK29" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL29" s="5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="BM29" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO29" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BP29" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BQ29" s="5" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="BR29" s="5" t="n"/>
       <c r="BS29" s="5" t="inlineStr"/>
-      <c r="BT29" s="5" t="inlineStr"/>
-      <c r="BU29" s="5" t="inlineStr"/>
-      <c r="BV29" s="5" t="inlineStr"/>
-      <c r="BW29" s="5" t="inlineStr"/>
-      <c r="BX29" s="5" t="inlineStr"/>
-      <c r="BY29" s="5" t="inlineStr"/>
+      <c r="BT29" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BU29" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BV29" s="5" t="inlineStr">
+        <is>
+          <t>Greeting &amp; Identification, Needs Discovery, Scheduling, Setting Expectations, Close &amp; Confirmation</t>
+        </is>
+      </c>
+      <c r="BW29" s="5" t="inlineStr">
+        <is>
+          <t>Qualifying</t>
+        </is>
+      </c>
+      <c r="BX29" s="5" t="inlineStr">
+        <is>
+          <t>[medium] After the customer mentioned submitting an insurance claim and needing estimates, the rep did not probe to see if other companies were quoting or inquire about the budget/deductible. | Fix: When a customer mentions getting estimates for an insurance claim, ask if they've already received other quotes and what their deductible looks like.
+[low] The rep did not ask for the caller's name during the initial Greeting &amp; Identification stage, waiting until the middle of the Needs Discovery to get it. | Fix: Ask for the caller's name immediately after the initial greeting and before diving into the issue.</t>
+        </is>
+      </c>
+      <c r="BY29" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="BZ29" s="5" t="inlineStr"/>
-      <c r="CA29" s="5" t="inlineStr"/>
-      <c r="CB29" s="5" t="inlineStr"/>
-      <c r="CC29" s="5" t="inlineStr"/>
+      <c r="CA29" s="5" t="n">
+        <v>4651</v>
+      </c>
+      <c r="CB29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CC29" s="5" t="inlineStr">
+        <is>
+          <t>customer_rep</t>
+        </is>
+      </c>
       <c r="CD29" s="5" t="n">
         <v>0</v>
       </c>
@@ -7950,14 +8983,14 @@
       <c r="CJ29" s="5" t="inlineStr"/>
       <c r="CK29" s="5" t="inlineStr"/>
       <c r="CL29" s="5" t="inlineStr"/>
-      <c r="CM29" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="CN29" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="CM29" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CN29" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="CO29" s="7" t="inlineStr">
@@ -7987,7 +9020,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>audio_test_9_201497df</t>
+          <t>gemini_cmp_29_a44a9dc7</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -7995,7 +9028,9 @@
           <t>completed</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="n">
+        <v>49.8</v>
+      </c>
       <c r="H30" s="5" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="5" t="inlineStr"/>
@@ -8035,28 +9070,32 @@
       <c r="AR30" s="5" t="inlineStr"/>
       <c r="AS30" s="5" t="inlineStr">
         <is>
-          <t>Tony called to request service for his clay tile patio roofs, stating he has three patio roofs and wants to replace them. The representative gathered Tony’s contact details, asked about the roof type and age, and confirmed the roofs are clay tile and approximately 26 years old; Tony also shared he wants to replace them with metal. Tony provided his phone number, email, and property address, and the representative concluded by advising that a team member would reach out shortly, with no additional requests from Tony.</t>
+          <t>Tony called to request a replacement for his three 26-year-old clay tile patio roofs. He expressed a specific desire to replace the current clay tiles with metal roofing. The representative gathered his contact information, including phone number, email, and property address in Cape Creek, Arizona, and advised that a team member will reach out shortly to assist further.</t>
         </is>
       </c>
       <c r="AT30" s="5" t="inlineStr">
         <is>
-          <t>Customer (Tony) wants to replace three clay tile patio roofs and switch to a metal roof.
-The existing patio roofs are clay tile and are 26 years old.
-Contact details were collected: phone 60233071155, email TURKPERK@KITCHENER.COM, and address 42214 N 67th St, Cave Creek, Arizona.</t>
-        </is>
-      </c>
-      <c r="AU30" s="5" t="inlineStr"/>
+          <t>Customer wants to replace three 26-year-old clay tile patio roofs.
+Customer specifically requested to replace the existing clay tiles with metal roofing.
+Property address provided is 42214 North 67th Street, Cape Creek, Arizona.
+Contact information collected includes phone number 60233071155 and email TURKPERK@KITCHENER.COM.</t>
+        </is>
+      </c>
+      <c r="AU30" s="5" t="inlineStr">
+        <is>
+          <t>Customer support team must call Tony back at 60233071155 to schedule an estimate for the metal patio roof replacements to secure the sale.</t>
+        </is>
+      </c>
       <c r="AV30" s="5" t="inlineStr">
         <is>
-          <t>Company team member to call Tony back using 60233071155 to discuss replacing the three clay tile patio roofs with metal.
-Use the provided address (42214 N 67th St, Cave Creek, AZ) and email (TURKPERK@KITCHENER.COM) for follow-up and any appointment/estimate coordination.</t>
+          <t>A team member will reach out to the customer shortly to follow up on the roof replacement request.</t>
         </is>
       </c>
       <c r="AW30" s="5" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="AX30" s="5" t="n">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="AY30" s="5" t="n">
         <v>0</v>
@@ -8075,7 +9114,7 @@
       </c>
       <c r="BD30" s="5" t="inlineStr">
         <is>
-          <t>Roof replacement (replace clay tile patio roofs with metal)</t>
+          <t>Roof replacement</t>
         </is>
       </c>
       <c r="BE30" s="5" t="inlineStr">
@@ -8128,28 +9167,27 @@
       <c r="BR30" s="5" t="n"/>
       <c r="BS30" s="5" t="inlineStr"/>
       <c r="BT30" s="5" t="n">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="BU30" s="5" t="n">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="BV30" s="5" t="inlineStr">
         <is>
-          <t>Greeting &amp; Identification, Needs Discovery</t>
+          <t>Greeting &amp; Identification, Needs Discovery, Close &amp; Confirmation</t>
         </is>
       </c>
       <c r="BW30" s="5" t="inlineStr">
         <is>
-          <t>Qualifying (BANT), Scheduling, Setting Expectations, Close &amp; Confirmation</t>
+          <t>Qualifying, Setting Expectations</t>
         </is>
       </c>
       <c r="BX30" s="5" t="inlineStr">
         <is>
-          <t>[high] After learning the customer wants to replace three 26-year-old clay tile patio roofs with metal, the rep ended the call by saying a team member will reach out, without offering or booking an inspection/estimate appointment. | Fix: Transition from needs discovery into scheduling by offering specific appointment windows and confirming who should be present and access details.
-[medium] The rep did not ask any qualifying (BANT) questions—no confirmation that Tony is the homeowner/decision maker, no timeline for replacement, and no budget/financing or competitive quote context. | Fix: Add a short qualification set after the issue is identified: decision maker, timing, and whether they’re comparing bids; optionally introduce financing if relevant.
-[medium] The rep did not set expectations for the next step (what the callback/appointment will include, how long it takes, what the customer will receive, or a timeframe for contact). | Fix: Provide a clear next-step summary with timing and deliverables (inspection/estimate, options, approximate duration) and confirm the best way/time to reach the customer.
-[low] The customer provided an address unprompted, but the rep did not confirm or read it back to ensure accuracy (and did not explicitly tie it to the service location). | Fix: Always confirm the full service address by repeating it back and asking for any access notes (gate code, pets, HOA requirements).
-[low] Close did not include a recap/confirmation of captured contact details or a confirmation message (text/email) and did not confirm the best callback number/time. | Fix: End with a concise recap (name, phone, email, address, next step) and ask permission to text/email confirmation.</t>
+          <t>[medium] The rep started the call by immediately stating their role but failed to mention the company name in the greeting. | Fix: Always open the call by thanking the customer for calling and clearly stating the company name before explaining the purpose of the call.
+[high] After the customer stated they wanted to replace three 26-year-old clay roofs with metal, the rep skipped all qualifying (BANT) questions, such as timeline or if the caller is the homeowner. | Fix: Before moving to collect the email address, ask 1-2 qualifying questions regarding urgency and homeownership.
+[low] The rep asked the customer what type of roof they currently have, even though the customer explicitly stated 'I have a clay tile patio roof' two turns prior. | Fix: Use the information the customer already provided to confirm details rather than asking the question from scratch.
+[medium] The rep set a vague expectation for next steps by simply stating a team member would reach out 'shortly'. | Fix: Provide a specific, standard timeframe for the callback to anchor the customer's expectations.</t>
         </is>
       </c>
       <c r="BY30" s="5" t="n">
@@ -8157,10 +9195,10 @@
       </c>
       <c r="BZ30" s="5" t="inlineStr"/>
       <c r="CA30" s="5" t="n">
-        <v>1192</v>
+        <v>1179</v>
       </c>
       <c r="CB30" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CC30" s="5" t="inlineStr">
         <is>
@@ -8221,15 +9259,17 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>NOT SUBMITTED</t>
+          <t>gemini_cmp_30_15e679cd</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>not_found</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr"/>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>325.9</v>
+      </c>
       <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="5" t="inlineStr"/>
@@ -8267,43 +9307,143 @@
       <c r="AP31" s="5" t="inlineStr"/>
       <c r="AQ31" s="5" t="inlineStr"/>
       <c r="AR31" s="5" t="inlineStr"/>
-      <c r="AS31" s="5" t="inlineStr"/>
-      <c r="AT31" s="5" t="inlineStr"/>
+      <c r="AS31" s="5" t="inlineStr">
+        <is>
+          <t>Wayland Dixon called Arizona Roofers to request an inspection and estimate for an active leak in the tile roof over his garage. The representative, Maddy, gathered the necessary property details, confirming it is a two-story home built in 2011, located in a gated HOA community with no solar panels. Maddy successfully scheduled a free comprehensive roof inspection for the following day between 10:00 AM and 12:00 PM, and thoroughly explained the inspection process to the customer.</t>
+        </is>
+      </c>
+      <c r="AT31" s="5" t="inlineStr">
+        <is>
+          <t>Customer reported an active leak in the tile roof above his long, single-car garage.
+The property is a two-story home built in 2011 and is part of an HOA.
+Access instructions: The property is in a gated community and the gate code is #7070.
+Customer confirmed there are no solar panels on the roof.
+A comprehensive roof inspection was booked for tomorrow (2026-03-27) between 10:00 AM and 12:00 PM.</t>
+        </is>
+      </c>
       <c r="AU31" s="5" t="inlineStr"/>
-      <c r="AV31" s="5" t="inlineStr"/>
-      <c r="AW31" s="5" t="inlineStr"/>
-      <c r="AX31" s="5" t="inlineStr"/>
-      <c r="AY31" s="5" t="inlineStr"/>
+      <c r="AV31" s="5" t="inlineStr">
+        <is>
+          <t>The automated system will send a confirmation text message to the customer regarding the upcoming appointment.
+A technician will arrive on 2026-03-27 between 10:00 AM and 12:00 PM to conduct the 1-1.5 hour inspection, take photos, and discuss repair options with the homeowner.</t>
+        </is>
+      </c>
+      <c r="AW31" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AX31" s="5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AY31" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ31" s="5" t="inlineStr"/>
-      <c r="BA31" s="5" t="inlineStr"/>
+      <c r="BA31" s="5" t="inlineStr">
+        <is>
+          <t>Wayland Dixon</t>
+        </is>
+      </c>
       <c r="BB31" s="5" t="inlineStr"/>
-      <c r="BC31" s="5" t="inlineStr"/>
-      <c r="BD31" s="5" t="inlineStr"/>
-      <c r="BE31" s="5" t="inlineStr"/>
-      <c r="BF31" s="5" t="inlineStr"/>
-      <c r="BG31" s="5" t="inlineStr"/>
-      <c r="BH31" s="5" t="inlineStr"/>
-      <c r="BI31" s="5" t="inlineStr"/>
-      <c r="BJ31" s="5" t="inlineStr"/>
-      <c r="BK31" s="5" t="inlineStr"/>
-      <c r="BL31" s="5" t="inlineStr"/>
-      <c r="BM31" s="5" t="inlineStr"/>
-      <c r="BN31" s="5" t="inlineStr"/>
-      <c r="BO31" s="5" t="inlineStr"/>
-      <c r="BP31" s="5" t="inlineStr"/>
-      <c r="BQ31" s="5" t="inlineStr"/>
-      <c r="BR31" s="5" t="inlineStr"/>
+      <c r="BC31" s="5" t="inlineStr">
+        <is>
+          <t>hot</t>
+        </is>
+      </c>
+      <c r="BD31" s="5" t="inlineStr">
+        <is>
+          <t>Roof inspection and estimate for leaking roof</t>
+        </is>
+      </c>
+      <c r="BE31" s="5" t="inlineStr">
+        <is>
+          <t>booked</t>
+        </is>
+      </c>
+      <c r="BF31" s="5" t="inlineStr">
+        <is>
+          <t>new_inquiry</t>
+        </is>
+      </c>
+      <c r="BG31" s="5" t="inlineStr">
+        <is>
+          <t>Existing</t>
+        </is>
+      </c>
+      <c r="BH31" s="5" t="inlineStr">
+        <is>
+          <t>qualified_and_booked</t>
+        </is>
+      </c>
+      <c r="BI31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="BJ31" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-27T10:00:00</t>
+        </is>
+      </c>
+      <c r="BK31" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="BL31" s="5" t="inlineStr">
+        <is>
+          <t>IN_SCOPE</t>
+        </is>
+      </c>
+      <c r="BM31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ31" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BR31" s="5" t="n"/>
       <c r="BS31" s="5" t="inlineStr"/>
-      <c r="BT31" s="5" t="inlineStr"/>
-      <c r="BU31" s="5" t="inlineStr"/>
-      <c r="BV31" s="5" t="inlineStr"/>
-      <c r="BW31" s="5" t="inlineStr"/>
-      <c r="BX31" s="5" t="inlineStr"/>
-      <c r="BY31" s="5" t="inlineStr"/>
+      <c r="BT31" s="5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BU31" s="5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BV31" s="5" t="inlineStr">
+        <is>
+          <t>Greeting &amp; Identification, Scheduling, Setting Expectations, Close &amp; Confirmation</t>
+        </is>
+      </c>
+      <c r="BW31" s="5" t="inlineStr">
+        <is>
+          <t>Needs Discovery, Qualifying</t>
+        </is>
+      </c>
+      <c r="BX31" s="5" t="inlineStr">
+        <is>
+          <t>[high] After the customer mentioned a leaking roof in the garage, the rep moved directly to asking about the roof type and scheduling without asking how long the leak has been happening or assessing its severity. | Fix: Immediately express empathy and ask questions to gauge the severity and timeline of the leak before moving to property details.
+[high] The rep skipped the Qualifying stage entirely, failing to ask if Wayland is the sole decision-maker/homeowner, or if he has received other quotes. | Fix: Before confirming the appointment time, ask who is on the deed and ensure all decision-makers will be present for the post-inspection consultation.</t>
+        </is>
+      </c>
+      <c r="BY31" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="BZ31" s="5" t="inlineStr"/>
-      <c r="CA31" s="5" t="inlineStr"/>
-      <c r="CB31" s="5" t="inlineStr"/>
-      <c r="CC31" s="5" t="inlineStr"/>
+      <c r="CA31" s="5" t="n">
+        <v>4108</v>
+      </c>
+      <c r="CB31" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="CC31" s="5" t="inlineStr">
+        <is>
+          <t>customer_rep, home_owner</t>
+        </is>
+      </c>
       <c r="CD31" s="5" t="n">
         <v>0</v>
       </c>
@@ -8321,14 +9461,14 @@
       <c r="CJ31" s="5" t="inlineStr"/>
       <c r="CK31" s="5" t="inlineStr"/>
       <c r="CL31" s="5" t="inlineStr"/>
-      <c r="CM31" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="CN31" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="CM31" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+      <c r="CN31" s="6" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
         </is>
       </c>
       <c r="CO31" s="7" t="inlineStr">
@@ -8357,357 +9497,357 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>GEMINI MIGRATION — EXECUTIVE SUMMARY</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr"/>
-      <c r="C1" s="10" t="inlineStr"/>
+      <c r="B1" s="12" t="inlineStr"/>
+      <c r="C1" s="12" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Generated</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-26 16:44:52</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr"/>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>2026-03-26 17:27:42</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr"/>
-      <c r="B3" s="10" t="inlineStr"/>
-      <c r="C3" s="10" t="inlineStr"/>
+      <c r="A3" s="12" t="inlineStr"/>
+      <c r="B3" s="12" t="inlineStr"/>
+      <c r="C3" s="12" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>METRIC</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>VALUE</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Total Calls Tested</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="C5" s="10" t="inlineStr"/>
+      <c r="C5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Production Baseline Found</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>13/30</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Staging Processed Successfully</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>19/30</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr"/>
-      <c r="B8" s="10" t="inlineStr"/>
-      <c r="C8" s="10" t="inlineStr"/>
+      <c r="A8" s="12" t="inlineStr"/>
+      <c r="B8" s="12" t="inlineStr"/>
+      <c r="C8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>VERDICT BREAKDOWN</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr"/>
-      <c r="C9" s="11" t="inlineStr"/>
+      <c r="B9" s="13" t="inlineStr"/>
+      <c r="C9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="C10" s="10" t="inlineStr"/>
+      <c r="B10" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="10" t="inlineStr"/>
+      <c r="B11" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="B12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="10" t="inlineStr"/>
+      <c r="B12" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr"/>
-      <c r="B13" s="10" t="inlineStr"/>
-      <c r="C13" s="10" t="inlineStr"/>
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="B13" s="12" t="inlineStr"/>
+      <c r="C13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>ISSUES BREAKDOWN</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr"/>
-      <c r="C14" s="11" t="inlineStr"/>
+      <c r="B14" s="13" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>High Severity Issues (Total)</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="B15" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Medium Severity Issues (Total)</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="10" t="inlineStr"/>
+      <c r="B16" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Low Severity Issues (Total)</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="10" t="inlineStr"/>
+      <c r="B17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr"/>
-      <c r="B18" s="10" t="inlineStr"/>
-      <c r="C18" s="10" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr"/>
+      <c r="B18" s="12" t="inlineStr"/>
+      <c r="C18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>AVERAGE SCORES</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>PRODUCTION</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>STAGING</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Compliance Score</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B20" s="12" t="n">
         <v>0.5177</v>
       </c>
-      <c r="C20" s="10" t="n">
-        <v>0.5432</v>
+      <c r="C20" s="12" t="n">
+        <v>0.591</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Sentiment Score</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" s="12" t="n">
         <v>0.67</v>
       </c>
-      <c r="C21" s="10" t="n">
-        <v>0.6667999999999999</v>
+      <c r="C21" s="12" t="n">
+        <v>0.6032999999999999</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Confidence Score</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="12" t="n">
         <v>0.8692</v>
       </c>
-      <c r="C22" s="10" t="n">
-        <v>0.8758</v>
+      <c r="C22" s="12" t="n">
+        <v>0.9383</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>BANT Overall</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" s="12" t="n">
         <v>0.3596</v>
       </c>
-      <c r="C23" s="10" t="n">
-        <v>0.3434</v>
+      <c r="C23" s="12" t="n">
+        <v>0.4367</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Lead Score</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr"/>
-      <c r="B25" s="10" t="inlineStr"/>
-      <c r="C25" s="10" t="inlineStr"/>
+      <c r="A25" s="12" t="inlineStr"/>
+      <c r="B25" s="12" t="inlineStr"/>
+      <c r="C25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>MATCH RATES</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>COUNT</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>RATE</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Booking Status Match</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>13/19</t>
+      <c r="B27" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>11/30</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>Call Type Match</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>13/19</t>
+      <c r="B28" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>10/30</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr"/>
-      <c r="B29" s="10" t="inlineStr"/>
-      <c r="C29" s="10" t="inlineStr"/>
+      <c r="A29" s="12" t="inlineStr"/>
+      <c r="B29" s="12" t="inlineStr"/>
+      <c r="C29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>RECOMMENDATION</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr"/>
-      <c r="C30" s="11" t="inlineStr"/>
+      <c r="B30" s="13" t="inlineStr"/>
+      <c r="C30" s="13" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>GO — Gemini outputs are at parity with OpenAI production</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr"/>
-      <c r="C31" s="10" t="inlineStr"/>
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>NO-GO — Significant quality issues found, needs investigation</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="inlineStr"/>
+      <c r="C31" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8720,7 +9860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8770,72 +9910,702 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/b9a3deca-d3e1-47ad-a2ad-875e58c0b7dc/4058565425.mp3</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>audio_test_10_56469bfa</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>BANT Need</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>Score Delta</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>PROD=0.8 STAGING=0.5 delta=0.300 (threshold=0.2)</t>
+      <c r="A2" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/1fd7bea5-9ace-4e8f-a31f-152ea8269927/4015296617.mp3</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_2_d4879ffd</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Customer Type</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>PROD='new' STAGING='existing'</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="n">
+      <c r="A3" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/1fd7bea5-9ace-4e8f-a31f-152ea8269927/4015296617.mp3</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_2_d4879ffd</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Scope Classification</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>PROD='none' STAGING='in_scope'</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/1fd7bea5-9ace-4e8f-a31f-152ea8269927/4015296617.mp3</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_2_d4879ffd</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Objections Count</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Missing in Staging</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Present in PROD but missing/empty in STAGING</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/1fd7bea5-9ace-4e8f-a31f-152ea8269927/4015296617.mp3</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_2_d4879ffd</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Objections Count</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Count Delta</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>PROD=4 STAGING=0 delta=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/bc946fa9-1e8a-4f1e-920c-64c4369fe778/4049722733.mp3</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_3_f8eebd74</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Booking Status</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>PROD='not_booked' STAGING='booked'</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/e2b0dab7-a05b-4448-8c13-fa3753f405ae/4036836500.mp3</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_4_da5ef94f</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>BANT Timeline</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Score Delta</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>PROD=0.5 STAGING=0.8 delta=0.300 (threshold=0.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/8c6b15ee-5675-4e01-8b31-ff3658126353/4049722733.mp3</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_5_76f5b613</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Booking Status</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>PROD='not_booked' STAGING='booked'</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/8c6b15ee-5675-4e01-8b31-ff3658126353/4049722733.mp3</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_5_76f5b613</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Call Type</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>PROD='fresh_sales' STAGING='follow_up'</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/b9a3deca-d3e1-47ad-a2ad-875e58c0b7dc/4058565425.mp3</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>audio_test_10_56469bfa</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_10_797392b8</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Objections Count</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Missing in Staging</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Present in PROD but missing/empty in STAGING</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/bd24a254-fe4e-48ef-9c3e-3c3f3adfd68c/4082148782.mp3</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_11_b2e0d556</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>BANT Budget</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Score Delta</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>PROD=0.5 STAGING=0.0 delta=0.500 (threshold=0.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/c0183543-60e4-434f-a247-89ec9ef8e1e3/4081871096.mp3</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_13_96e7fdd6</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Compliance Score</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Score Delta</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>PROD=0.62 STAGING=0.8 delta=0.180 (threshold=0.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/c0183543-60e4-434f-a247-89ec9ef8e1e3/4081871096.mp3</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_13_96e7fdd6</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>BANT Timeline</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Score Delta</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>PROD=0.0 STAGING=1.0 delta=1.000 (threshold=0.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/c0183543-60e4-434f-a247-89ec9ef8e1e3/4081871096.mp3</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_13_96e7fdd6</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>BANT Overall</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Score Delta</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>PROD=0.575 STAGING=0.825 delta=0.250 (threshold=0.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/c0183543-60e4-434f-a247-89ec9ef8e1e3/4081871096.mp3</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_13_96e7fdd6</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Compliance Rate</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Score Delta</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>PROD=0.62 STAGING=0.8 delta=0.180 (threshold=0.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/c0183543-60e4-434f-a247-89ec9ef8e1e3/4081871096.mp3</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_13_96e7fdd6</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Call Type</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>PROD='quote_only' STAGING='new_inquiry'</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/c0183543-60e4-434f-a247-89ec9ef8e1e3/4081871096.mp3</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_13_96e7fdd6</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Qualification Status</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Mismatch</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>PROD='hot' STAGING='warm'</t>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>PROD='warm' STAGING='hot'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/ddccb9c0-fce8-4eb5-81bd-5e738cb95979/4078581674.mp3</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_17_37b9a902</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Call Type</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>PROD='service_call' STAGING='new_inquiry'</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/df6c19b0-5d39-457b-8053-4dd83f4407cf/4076546354.mp3</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_19_dfa99492</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>BANT Need</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>Score Delta</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>PROD=0.5 STAGING=0.8 delta=0.300 (threshold=0.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/df6c19b0-5d39-457b-8053-4dd83f4407cf/4076546354.mp3</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_19_dfa99492</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>BANT Timeline</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>Score Delta</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>PROD=0.8 STAGING=0.0 delta=0.800 (threshold=0.2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>https://ottoaudio.s3.ap-southeast-2.amazonaws.com/recordings/df6c19b0-5d39-457b-8053-4dd83f4407cf/4076546354.mp3</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>gemini_cmp_19_dfa99492</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Qualification Status</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>PROD='warm' STAGING='cold'</t>
         </is>
       </c>
     </row>
